--- a/registers/NEK_Master_Registers.xlsx
+++ b/registers/NEK_Master_Registers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude Cowork\NEK\registers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A539BC3-4BA2-47DC-84E6-EC7DEA8A7D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F338D5D4-5712-47B7-8FF2-48EE030FAD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2227" uniqueCount="707">
   <si>
     <t>NEK GROUP — MASTER REGISTER WORKBOOK</t>
   </si>
@@ -1244,45 +1244,6 @@
     <t>Contract Expiry</t>
   </si>
   <si>
-    <t>V-001</t>
-  </si>
-  <si>
-    <t>NEKMY01</t>
-  </si>
-  <si>
-    <t>200866000173</t>
-  </si>
-  <si>
-    <t>Account Services</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>15454</t>
-  </si>
-  <si>
-    <t>On statement</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>Tan A</t>
-  </si>
-  <si>
-    <t>Telephone to known no.</t>
-  </si>
-  <si>
-    <t>Account 123456789</t>
-  </si>
-  <si>
-    <t>EXAMPLE ROW — delete before use</t>
-  </si>
-  <si>
     <t>COMPLIANCE &amp; FILING CALENDAR</t>
   </si>
   <si>
@@ -1790,21 +1751,12 @@
     <t>INV</t>
   </si>
   <si>
-    <t>Supplier invoice (payable)</t>
-  </si>
-  <si>
     <t>Vendor code</t>
   </si>
   <si>
     <t>Occupied / Vacant / Notice Given / Under Renovation</t>
   </si>
   <si>
-    <t>SIV</t>
-  </si>
-  <si>
-    <t>Sales invoice issued (receivable)</t>
-  </si>
-  <si>
     <t>Customer / tenant</t>
   </si>
   <si>
@@ -2148,6 +2100,72 @@
   </si>
   <si>
     <t>Shared account with NCL (spouses) - Sha Tin rental. Same physical account as NCL|BOCOM; two entity keys, one account.</t>
+  </si>
+  <si>
+    <t>Timothy Ng</t>
+  </si>
+  <si>
+    <t>Invoice issued by us (receivable)</t>
+  </si>
+  <si>
+    <t>PINV</t>
+  </si>
+  <si>
+    <t>Supplier invoice received (payable)</t>
+  </si>
+  <si>
+    <t>CAVATINA</t>
+  </si>
+  <si>
+    <t>Seeded from 04 Recurring Payments 2026-07-31. Confirm registration no., contact details and payment terms.</t>
+  </si>
+  <si>
+    <t>EXCELIZ</t>
+  </si>
+  <si>
+    <t>HHIL, MDL, NCLCAP, NEK, NEKGV, NGCS, SBOXAI, SBOXCAP</t>
+  </si>
+  <si>
+    <t>HONGYIP</t>
+  </si>
+  <si>
+    <t>KBLOH</t>
+  </si>
+  <si>
+    <t>KCK-AUD</t>
+  </si>
+  <si>
+    <t>KCK-TAX</t>
+  </si>
+  <si>
+    <t>KRAJA</t>
+  </si>
+  <si>
+    <t>HHIL, NEK</t>
+  </si>
+  <si>
+    <t>Business License / Land Tax</t>
+  </si>
+  <si>
+    <t>HHIL, MDL</t>
+  </si>
+  <si>
+    <t>MTR</t>
+  </si>
+  <si>
+    <t>PLO</t>
+  </si>
+  <si>
+    <t>QUAYSIDE-JMB</t>
+  </si>
+  <si>
+    <t>RVD</t>
+  </si>
+  <si>
+    <t>TMUNIFI</t>
+  </si>
+  <si>
+    <t>TNB</t>
   </si>
 </sst>
 </file>
@@ -2379,8 +2397,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2893,16 +2911,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
@@ -2911,6 +2919,16 @@
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2937,44 +2955,44 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>672</v>
+        <v>656</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
-        <v>673</v>
+        <v>657</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>50</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>62</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>394</v>
@@ -2982,26 +3000,26 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="25" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
       <c r="B5" s="25" t="s">
         <v>66</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="D5" s="25"/>
       <c r="E5" s="26" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="G5" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>77</v>
@@ -3011,26 +3029,26 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
-        <v>686</v>
+        <v>670</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>687</v>
+        <v>671</v>
       </c>
       <c r="D6" s="25"/>
       <c r="E6" s="26" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="G6" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>688</v>
+        <v>672</v>
       </c>
       <c r="I6" s="25" t="s">
         <v>77</v>
@@ -3040,20 +3058,20 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>80</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="26" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>71</v>
@@ -3067,20 +3085,20 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>84</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="26" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="G8" s="25" t="s">
         <v>71</v>
@@ -3094,26 +3112,26 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>88</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="26" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>691</v>
+        <v>675</v>
       </c>
       <c r="I9" s="25" t="s">
         <v>77</v>
@@ -3123,20 +3141,20 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
-        <v>692</v>
+        <v>676</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>693</v>
+        <v>677</v>
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="26" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>71</v>
@@ -3150,20 +3168,20 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="25" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>99</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="26" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>71</v>
@@ -3177,20 +3195,20 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="D12" s="25"/>
       <c r="E12" s="26" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="G12" s="25" t="s">
         <v>71</v>
@@ -3204,20 +3222,20 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="25" t="s">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="B13" s="25" t="s">
         <v>108</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="26" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="G13" s="25" t="s">
         <v>71</v>
@@ -3231,26 +3249,26 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
-        <v>694</v>
+        <v>678</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>112</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>695</v>
+        <v>679</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="26" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="G14" s="25" t="s">
         <v>92</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>696</v>
+        <v>680</v>
       </c>
       <c r="I14" s="25" t="s">
         <v>77</v>
@@ -3260,26 +3278,26 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
-        <v>697</v>
+        <v>681</v>
       </c>
       <c r="B15" s="25" t="s">
         <v>118</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="26" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="G15" s="25" t="s">
         <v>121</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>698</v>
+        <v>682</v>
       </c>
       <c r="I15" s="25" t="s">
         <v>77</v>
@@ -3289,32 +3307,36 @@
     </row>
     <row r="16" spans="1:11" ht="57.5" x14ac:dyDescent="0.35">
       <c r="A16" s="25" t="s">
-        <v>694</v>
+        <v>678</v>
       </c>
       <c r="B16" s="25" t="s">
         <v>116</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>695</v>
+        <v>679</v>
       </c>
       <c r="D16" s="25"/>
       <c r="E16" s="26" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="G16" s="25" t="s">
         <v>92</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>700</v>
+        <v>684</v>
       </c>
       <c r="I16" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="J16" s="27"/>
-      <c r="K16" s="26"/>
+      <c r="J16" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K16" s="26" t="s">
+        <v>685</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="28"/>
@@ -3409,7 +3431,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="35" t="s">
-        <v>699</v>
+        <v>683</v>
       </c>
       <c r="B25" s="35"/>
       <c r="C25" s="35"/>
@@ -4375,7 +4397,7 @@
       </c>
       <c r="N5" s="15">
         <f t="shared" ref="N5:N44" ca="1" si="0">IFERROR(IF(M5="","",M5-TODAY()),"")</f>
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="O5" s="15" t="str">
         <f t="shared" ref="O5:O44" ca="1" si="1">IFERROR(IF(M5="","",IF(M5-TODAY()&lt;0,"EXPIRED",IF(M5-TODAY()&lt;=90,"RENEW NOW",IF(M5-TODAY()&lt;=180,"Prepare","")))),"")</f>
@@ -4449,7 +4471,7 @@
       </c>
       <c r="N6" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="O6" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4523,7 +4545,7 @@
       </c>
       <c r="N7" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="O7" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4597,7 +4619,7 @@
       </c>
       <c r="N8" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="O8" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4671,7 +4693,7 @@
       </c>
       <c r="N9" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="O9" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4743,7 +4765,7 @@
       </c>
       <c r="N10" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="O10" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -10982,466 +11004,700 @@
     </row>
     <row r="5" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
-        <v>399</v>
+        <v>689</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>293</v>
+        <v>356</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>292</v>
+        <v>355</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>400</v>
+        <v>112</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>401</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="I5" s="19" t="s">
-        <v>404</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
       <c r="J5" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="K5" s="19" t="s">
-        <v>405</v>
-      </c>
-      <c r="L5" s="19" t="s">
-        <v>406</v>
-      </c>
-      <c r="M5" s="19" t="s">
-        <v>407</v>
-      </c>
-      <c r="N5" s="19" t="s">
-        <v>408</v>
-      </c>
-      <c r="O5" s="19" t="s">
-        <v>409</v>
-      </c>
-      <c r="P5" s="20">
-        <f t="shared" ref="P5:P45" ca="1" si="0">IFERROR(IF(M5="","",TODAY()-M5),"")</f>
-        <v>193</v>
-      </c>
-      <c r="Q5" s="19" t="s">
-        <v>410</v>
-      </c>
-      <c r="R5" s="19" t="s">
-        <v>114</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="20" t="str">
+        <f ca="1">IFERROR(IF(M5="","",TODAY()-M5),"")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
       <c r="S5" s="19" t="s">
         <v>77</v>
       </c>
       <c r="T5" s="19" t="s">
-        <v>411</v>
+        <v>690</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="A6" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="J6" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="13"/>
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
       <c r="P6" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M6="","",TODAY()-M6),"")</f>
         <v/>
       </c>
       <c r="Q6" s="9"/>
       <c r="R6" s="13"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
+      <c r="S6" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="A7" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="J7" s="9" t="s">
+        <v>92</v>
+      </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="13"/>
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
       <c r="P7" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M7="","",TODAY()-M7),"")</f>
         <v/>
       </c>
       <c r="Q7" s="9"/>
       <c r="R7" s="13"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
+      <c r="S7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="A8" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="J8" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
       <c r="M8" s="13"/>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
       <c r="P8" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M8="","",TODAY()-M8),"")</f>
         <v/>
       </c>
       <c r="Q8" s="9"/>
       <c r="R8" s="13"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
+      <c r="S8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="A9" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="J9" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
       <c r="M9" s="13"/>
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
       <c r="P9" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M9="","",TODAY()-M9),"")</f>
         <v/>
       </c>
       <c r="Q9" s="9"/>
       <c r="R9" s="13"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
+      <c r="S9" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="A10" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="J10" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
       <c r="M10" s="13"/>
       <c r="N10" s="9"/>
       <c r="O10" s="9"/>
       <c r="P10" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M10="","",TODAY()-M10),"")</f>
         <v/>
       </c>
       <c r="Q10" s="9"/>
       <c r="R10" s="13"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
+      <c r="S10" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="A11" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="J11" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="13"/>
       <c r="N11" s="9"/>
       <c r="O11" s="9"/>
       <c r="P11" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M11="","",TODAY()-M11),"")</f>
         <v/>
       </c>
       <c r="Q11" s="9"/>
       <c r="R11" s="13"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
+      <c r="S11" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="A12" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="J12" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="13"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
       <c r="P12" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M12="","",TODAY()-M12),"")</f>
         <v/>
       </c>
       <c r="Q12" s="9"/>
       <c r="R12" s="13"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
+      <c r="S12" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T12" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+      <c r="A13" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="J13" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="M13" s="13"/>
       <c r="N13" s="9"/>
       <c r="O13" s="9"/>
       <c r="P13" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M13="","",TODAY()-M13),"")</f>
         <v/>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="13"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
+      <c r="S13" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T13" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="A14" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="J14" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
       <c r="M14" s="13"/>
       <c r="N14" s="9"/>
       <c r="O14" s="9"/>
       <c r="P14" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M14="","",TODAY()-M14),"")</f>
         <v/>
       </c>
       <c r="Q14" s="9"/>
       <c r="R14" s="13"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
+      <c r="S14" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="A15" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="J15" s="9" t="s">
+        <v>92</v>
+      </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="M15" s="13"/>
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
       <c r="P15" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M15="","",TODAY()-M15),"")</f>
         <v/>
       </c>
       <c r="Q15" s="9"/>
       <c r="R15" s="13"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
+      <c r="S15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+      <c r="A16" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="J16" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
       <c r="M16" s="13"/>
       <c r="N16" s="9"/>
       <c r="O16" s="9"/>
       <c r="P16" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M16="","",TODAY()-M16),"")</f>
         <v/>
       </c>
       <c r="Q16" s="9"/>
       <c r="R16" s="13"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
+      <c r="S16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="A17" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="J17" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="M17" s="13"/>
       <c r="N17" s="9"/>
       <c r="O17" s="9"/>
       <c r="P17" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M17="","",TODAY()-M17),"")</f>
         <v/>
       </c>
       <c r="Q17" s="9"/>
       <c r="R17" s="13"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
+      <c r="S17" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T17" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="A18" s="9" t="s">
+        <v>703</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
+      <c r="J18" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="13"/>
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>
       <c r="P18" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M18="","",TODAY()-M18),"")</f>
         <v/>
       </c>
       <c r="Q18" s="9"/>
       <c r="R18" s="13"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
+      <c r="S18" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T18" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="A19" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="J19" s="9" t="s">
+        <v>92</v>
+      </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
       <c r="M19" s="13"/>
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
       <c r="P19" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M19="","",TODAY()-M19),"")</f>
         <v/>
       </c>
       <c r="Q19" s="9"/>
       <c r="R19" s="13"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
+      <c r="S19" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T19" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="A20" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="J20" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
       <c r="M20" s="13"/>
       <c r="N20" s="9"/>
       <c r="O20" s="9"/>
       <c r="P20" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M20="","",TODAY()-M20),"")</f>
         <v/>
       </c>
       <c r="Q20" s="9"/>
       <c r="R20" s="13"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
+      <c r="S20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T20" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="A21" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
+      <c r="J21" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
       <c r="M21" s="13"/>
       <c r="N21" s="9"/>
       <c r="O21" s="9"/>
       <c r="P21" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(IF(M21="","",TODAY()-M21),"")</f>
         <v/>
       </c>
       <c r="Q21" s="9"/>
       <c r="R21" s="13"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="9"/>
+      <c r="S21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T21" s="9" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9"/>
@@ -11459,10 +11715,7 @@
       <c r="M22" s="13"/>
       <c r="N22" s="9"/>
       <c r="O22" s="9"/>
-      <c r="P22" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P22" s="15"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="13"/>
       <c r="S22" s="9"/>
@@ -11484,10 +11737,7 @@
       <c r="M23" s="13"/>
       <c r="N23" s="9"/>
       <c r="O23" s="9"/>
-      <c r="P23" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P23" s="15"/>
       <c r="Q23" s="9"/>
       <c r="R23" s="13"/>
       <c r="S23" s="9"/>
@@ -11509,10 +11759,7 @@
       <c r="M24" s="13"/>
       <c r="N24" s="9"/>
       <c r="O24" s="9"/>
-      <c r="P24" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P24" s="15"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="13"/>
       <c r="S24" s="9"/>
@@ -11534,10 +11781,7 @@
       <c r="M25" s="13"/>
       <c r="N25" s="9"/>
       <c r="O25" s="9"/>
-      <c r="P25" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P25" s="15"/>
       <c r="Q25" s="9"/>
       <c r="R25" s="13"/>
       <c r="S25" s="9"/>
@@ -11559,10 +11803,7 @@
       <c r="M26" s="13"/>
       <c r="N26" s="9"/>
       <c r="O26" s="9"/>
-      <c r="P26" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P26" s="15"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="13"/>
       <c r="S26" s="9"/>
@@ -11584,10 +11825,7 @@
       <c r="M27" s="13"/>
       <c r="N27" s="9"/>
       <c r="O27" s="9"/>
-      <c r="P27" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P27" s="15"/>
       <c r="Q27" s="9"/>
       <c r="R27" s="13"/>
       <c r="S27" s="9"/>
@@ -11609,10 +11847,7 @@
       <c r="M28" s="13"/>
       <c r="N28" s="9"/>
       <c r="O28" s="9"/>
-      <c r="P28" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P28" s="15"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="13"/>
       <c r="S28" s="9"/>
@@ -11634,10 +11869,7 @@
       <c r="M29" s="13"/>
       <c r="N29" s="9"/>
       <c r="O29" s="9"/>
-      <c r="P29" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P29" s="15"/>
       <c r="Q29" s="9"/>
       <c r="R29" s="13"/>
       <c r="S29" s="9"/>
@@ -11659,10 +11891,7 @@
       <c r="M30" s="13"/>
       <c r="N30" s="9"/>
       <c r="O30" s="9"/>
-      <c r="P30" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P30" s="15"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="13"/>
       <c r="S30" s="9"/>
@@ -11684,10 +11913,7 @@
       <c r="M31" s="13"/>
       <c r="N31" s="9"/>
       <c r="O31" s="9"/>
-      <c r="P31" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P31" s="15"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="13"/>
       <c r="S31" s="9"/>
@@ -11709,10 +11935,7 @@
       <c r="M32" s="13"/>
       <c r="N32" s="9"/>
       <c r="O32" s="9"/>
-      <c r="P32" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P32" s="15"/>
       <c r="Q32" s="9"/>
       <c r="R32" s="13"/>
       <c r="S32" s="9"/>
@@ -11734,10 +11957,7 @@
       <c r="M33" s="13"/>
       <c r="N33" s="9"/>
       <c r="O33" s="9"/>
-      <c r="P33" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P33" s="15"/>
       <c r="Q33" s="9"/>
       <c r="R33" s="13"/>
       <c r="S33" s="9"/>
@@ -11759,10 +11979,7 @@
       <c r="M34" s="13"/>
       <c r="N34" s="9"/>
       <c r="O34" s="9"/>
-      <c r="P34" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P34" s="15"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="13"/>
       <c r="S34" s="9"/>
@@ -11784,10 +12001,7 @@
       <c r="M35" s="13"/>
       <c r="N35" s="9"/>
       <c r="O35" s="9"/>
-      <c r="P35" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P35" s="15"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="13"/>
       <c r="S35" s="9"/>
@@ -11809,10 +12023,7 @@
       <c r="M36" s="13"/>
       <c r="N36" s="9"/>
       <c r="O36" s="9"/>
-      <c r="P36" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P36" s="15"/>
       <c r="Q36" s="9"/>
       <c r="R36" s="13"/>
       <c r="S36" s="9"/>
@@ -11834,10 +12045,7 @@
       <c r="M37" s="13"/>
       <c r="N37" s="9"/>
       <c r="O37" s="9"/>
-      <c r="P37" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P37" s="15"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="13"/>
       <c r="S37" s="9"/>
@@ -11859,10 +12067,7 @@
       <c r="M38" s="13"/>
       <c r="N38" s="9"/>
       <c r="O38" s="9"/>
-      <c r="P38" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P38" s="15"/>
       <c r="Q38" s="9"/>
       <c r="R38" s="13"/>
       <c r="S38" s="9"/>
@@ -11884,10 +12089,7 @@
       <c r="M39" s="13"/>
       <c r="N39" s="9"/>
       <c r="O39" s="9"/>
-      <c r="P39" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P39" s="15"/>
       <c r="Q39" s="9"/>
       <c r="R39" s="13"/>
       <c r="S39" s="9"/>
@@ -11909,10 +12111,7 @@
       <c r="M40" s="13"/>
       <c r="N40" s="9"/>
       <c r="O40" s="9"/>
-      <c r="P40" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P40" s="15"/>
       <c r="Q40" s="9"/>
       <c r="R40" s="13"/>
       <c r="S40" s="9"/>
@@ -11934,10 +12133,7 @@
       <c r="M41" s="13"/>
       <c r="N41" s="9"/>
       <c r="O41" s="9"/>
-      <c r="P41" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P41" s="15"/>
       <c r="Q41" s="9"/>
       <c r="R41" s="13"/>
       <c r="S41" s="9"/>
@@ -11959,10 +12155,7 @@
       <c r="M42" s="13"/>
       <c r="N42" s="9"/>
       <c r="O42" s="9"/>
-      <c r="P42" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P42" s="15"/>
       <c r="Q42" s="9"/>
       <c r="R42" s="13"/>
       <c r="S42" s="9"/>
@@ -11984,10 +12177,7 @@
       <c r="M43" s="13"/>
       <c r="N43" s="9"/>
       <c r="O43" s="9"/>
-      <c r="P43" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P43" s="15"/>
       <c r="Q43" s="9"/>
       <c r="R43" s="13"/>
       <c r="S43" s="9"/>
@@ -12009,10 +12199,7 @@
       <c r="M44" s="13"/>
       <c r="N44" s="9"/>
       <c r="O44" s="9"/>
-      <c r="P44" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P44" s="15"/>
       <c r="Q44" s="9"/>
       <c r="R44" s="13"/>
       <c r="S44" s="9"/>
@@ -12034,10 +12221,7 @@
       <c r="M45" s="13"/>
       <c r="N45" s="9"/>
       <c r="O45" s="9"/>
-      <c r="P45" s="15" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="P45" s="15"/>
       <c r="Q45" s="9"/>
       <c r="R45" s="13"/>
       <c r="S45" s="9"/>
@@ -12076,12 +12260,12 @@
   <sheetData>
     <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12095,46 +12279,46 @@
         <v>52</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>223</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="R4" s="8" t="s">
         <v>63</v>
@@ -12142,7 +12326,7 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>66</v>
@@ -12151,10 +12335,10 @@
         <v>68</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>238</v>
@@ -12163,14 +12347,14 @@
         <v>238</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="I5" s="13">
         <v>46249</v>
       </c>
       <c r="J5" s="15">
         <f t="shared" ref="J5:J36" ca="1" si="0">IFERROR(IF(I5="","",I5-TODAY()),"")</f>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K5" s="15" t="str">
         <f t="shared" ref="K5:K10" ca="1" si="1">IFERROR(IF(I5="","",IF(I5-TODAY()&lt;0,"OVERDUE",IF(I5-TODAY()&lt;=14,"DUE NOW",IF(I5-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -12188,7 +12372,7 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>66</v>
@@ -12197,10 +12381,10 @@
         <v>68</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>238</v>
@@ -12209,14 +12393,14 @@
         <v>238</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="I6" s="13">
         <v>46249</v>
       </c>
       <c r="J6" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K6" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -12234,7 +12418,7 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>66</v>
@@ -12255,14 +12439,14 @@
         <v>238</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="I7" s="13">
         <v>46249</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K7" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -12280,7 +12464,7 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>66</v>
@@ -12289,16 +12473,16 @@
         <v>68</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>106</v>
@@ -12308,7 +12492,7 @@
       </c>
       <c r="J8" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -12326,7 +12510,7 @@
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>66</v>
@@ -12335,16 +12519,16 @@
         <v>68</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>106</v>
@@ -12354,7 +12538,7 @@
       </c>
       <c r="J9" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -12372,7 +12556,7 @@
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>66</v>
@@ -12381,7 +12565,7 @@
         <v>68</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>251</v>
@@ -12390,24 +12574,24 @@
         <v>259</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="I10" s="13">
         <v>46366</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K10" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
       <c r="L10" s="9" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="9"/>
@@ -12418,7 +12602,7 @@
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>66</v>
@@ -12427,7 +12611,7 @@
         <v>68</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>251</v>
@@ -12436,7 +12620,7 @@
         <v>259</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>106</v>
@@ -12446,7 +12630,7 @@
       </c>
       <c r="J11" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="K11" s="15"/>
       <c r="L11" s="9" t="s">
@@ -12461,7 +12645,7 @@
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>66</v>
@@ -12470,7 +12654,7 @@
         <v>68</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>251</v>
@@ -12479,17 +12663,17 @@
         <v>259</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="I12" s="13">
         <v>46477</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K12" s="15"/>
       <c r="L12" s="9" t="s">
@@ -12504,7 +12688,7 @@
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>66</v>
@@ -12513,7 +12697,7 @@
         <v>68</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>235</v>
@@ -12522,17 +12706,17 @@
         <v>259</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="I13" s="13">
         <v>46477</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K13" s="15"/>
       <c r="L13" s="9" t="s">
@@ -12547,7 +12731,7 @@
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>84</v>
@@ -12556,7 +12740,7 @@
         <v>68</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>313</v>
@@ -12565,7 +12749,7 @@
         <v>259</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>70</v>
@@ -12575,7 +12759,7 @@
       </c>
       <c r="J14" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K14" s="15"/>
       <c r="L14" s="9" t="s">
@@ -12590,7 +12774,7 @@
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>84</v>
@@ -12599,7 +12783,7 @@
         <v>68</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>251</v>
@@ -12608,7 +12792,7 @@
         <v>259</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>106</v>
@@ -12618,7 +12802,7 @@
       </c>
       <c r="J15" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="K15" s="15"/>
       <c r="L15" s="9" t="s">
@@ -12633,7 +12817,7 @@
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>84</v>
@@ -12642,7 +12826,7 @@
         <v>68</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>251</v>
@@ -12651,17 +12835,17 @@
         <v>259</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="I16" s="13">
         <v>46477</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K16" s="15"/>
       <c r="L16" s="9" t="s">
@@ -12676,7 +12860,7 @@
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>84</v>
@@ -12685,16 +12869,16 @@
         <v>68</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>106</v>
@@ -12704,7 +12888,7 @@
       </c>
       <c r="J17" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K17" s="15" t="str">
         <f ca="1">IFERROR(IF(I17="","",IF(I17-TODAY()&lt;0,"OVERDUE",IF(I17-TODAY()&lt;=14,"DUE NOW",IF(I17-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -12722,7 +12906,7 @@
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>84</v>
@@ -12731,16 +12915,16 @@
         <v>68</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>106</v>
@@ -12750,7 +12934,7 @@
       </c>
       <c r="J18" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" s="15" t="str">
         <f ca="1">IFERROR(IF(I18="","",IF(I18-TODAY()&lt;0,"OVERDUE",IF(I18-TODAY()&lt;=14,"DUE NOW",IF(I18-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -12768,7 +12952,7 @@
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>95</v>
@@ -12777,7 +12961,7 @@
         <v>68</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>251</v>
@@ -12786,7 +12970,7 @@
         <v>259</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>106</v>
@@ -12796,7 +12980,7 @@
       </c>
       <c r="J19" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="K19" s="15"/>
       <c r="L19" s="9" t="s">
@@ -12811,7 +12995,7 @@
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>95</v>
@@ -12820,7 +13004,7 @@
         <v>68</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>251</v>
@@ -12829,17 +13013,17 @@
         <v>259</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="I20" s="13">
         <v>46477</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K20" s="15"/>
       <c r="L20" s="9" t="s">
@@ -12854,7 +13038,7 @@
     </row>
     <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>95</v>
@@ -12863,16 +13047,16 @@
         <v>68</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>106</v>
@@ -12882,7 +13066,7 @@
       </c>
       <c r="J21" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K21" s="15" t="str">
         <f ca="1">IFERROR(IF(I21="","",IF(I21-TODAY()&lt;0,"OVERDUE",IF(I21-TODAY()&lt;=14,"DUE NOW",IF(I21-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -12900,7 +13084,7 @@
     </row>
     <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>95</v>
@@ -12909,16 +13093,16 @@
         <v>68</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>106</v>
@@ -12928,7 +13112,7 @@
       </c>
       <c r="J22" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K22" s="15" t="str">
         <f ca="1">IFERROR(IF(I22="","",IF(I22-TODAY()&lt;0,"OVERDUE",IF(I22-TODAY()&lt;=14,"DUE NOW",IF(I22-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -12946,7 +13130,7 @@
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>99</v>
@@ -12955,7 +13139,7 @@
         <v>68</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>251</v>
@@ -12964,7 +13148,7 @@
         <v>259</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>106</v>
@@ -12974,7 +13158,7 @@
       </c>
       <c r="J23" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="K23" s="15"/>
       <c r="L23" s="9" t="s">
@@ -12989,7 +13173,7 @@
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>99</v>
@@ -12998,7 +13182,7 @@
         <v>68</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>251</v>
@@ -13007,17 +13191,17 @@
         <v>259</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="I24" s="13">
         <v>46477</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K24" s="15"/>
       <c r="L24" s="9" t="s">
@@ -13032,7 +13216,7 @@
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>99</v>
@@ -13041,16 +13225,16 @@
         <v>68</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>106</v>
@@ -13060,7 +13244,7 @@
       </c>
       <c r="J25" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K25" s="15" t="str">
         <f ca="1">IFERROR(IF(I25="","",IF(I25-TODAY()&lt;0,"OVERDUE",IF(I25-TODAY()&lt;=14,"DUE NOW",IF(I25-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13078,7 +13262,7 @@
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>99</v>
@@ -13087,16 +13271,16 @@
         <v>68</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>106</v>
@@ -13106,7 +13290,7 @@
       </c>
       <c r="J26" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K26" s="15" t="str">
         <f ca="1">IFERROR(IF(I26="","",IF(I26-TODAY()&lt;0,"OVERDUE",IF(I26-TODAY()&lt;=14,"DUE NOW",IF(I26-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13124,7 +13308,7 @@
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>80</v>
@@ -13133,7 +13317,7 @@
         <v>68</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>251</v>
@@ -13142,7 +13326,7 @@
         <v>259</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>106</v>
@@ -13152,7 +13336,7 @@
       </c>
       <c r="J27" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="K27" s="15"/>
       <c r="L27" s="9" t="s">
@@ -13167,7 +13351,7 @@
     </row>
     <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>80</v>
@@ -13176,7 +13360,7 @@
         <v>68</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>251</v>
@@ -13185,17 +13369,17 @@
         <v>259</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="I28" s="13">
         <v>46477</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K28" s="15"/>
       <c r="L28" s="9" t="s">
@@ -13210,7 +13394,7 @@
     </row>
     <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>80</v>
@@ -13219,16 +13403,16 @@
         <v>68</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>106</v>
@@ -13238,7 +13422,7 @@
       </c>
       <c r="J29" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K29" s="15" t="str">
         <f ca="1">IFERROR(IF(I29="","",IF(I29-TODAY()&lt;0,"OVERDUE",IF(I29-TODAY()&lt;=14,"DUE NOW",IF(I29-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13256,7 +13440,7 @@
     </row>
     <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>80</v>
@@ -13265,16 +13449,16 @@
         <v>68</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>106</v>
@@ -13284,7 +13468,7 @@
       </c>
       <c r="J30" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K30" s="15" t="str">
         <f ca="1">IFERROR(IF(I30="","",IF(I30-TODAY()&lt;0,"OVERDUE",IF(I30-TODAY()&lt;=14,"DUE NOW",IF(I30-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13302,7 +13486,7 @@
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>103</v>
@@ -13311,7 +13495,7 @@
         <v>68</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>251</v>
@@ -13320,17 +13504,17 @@
         <v>259</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="I31" s="13">
         <v>46446</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="K31" s="15"/>
       <c r="L31" s="9" t="s">
@@ -13342,12 +13526,12 @@
       <c r="P31" s="13"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="9" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>103</v>
@@ -13356,7 +13540,7 @@
         <v>68</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>251</v>
@@ -13365,17 +13549,17 @@
         <v>259</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="I32" s="13">
         <v>46477</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K32" s="15"/>
       <c r="L32" s="9" t="s">
@@ -13390,7 +13574,7 @@
     </row>
     <row r="33" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>103</v>
@@ -13399,16 +13583,16 @@
         <v>68</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>106</v>
@@ -13418,7 +13602,7 @@
       </c>
       <c r="J33" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K33" s="15" t="str">
         <f ca="1">IFERROR(IF(I33="","",IF(I33-TODAY()&lt;0,"OVERDUE",IF(I33-TODAY()&lt;=14,"DUE NOW",IF(I33-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13436,7 +13620,7 @@
     </row>
     <row r="34" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>103</v>
@@ -13445,16 +13629,16 @@
         <v>68</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>106</v>
@@ -13464,7 +13648,7 @@
       </c>
       <c r="J34" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K34" s="15" t="str">
         <f ca="1">IFERROR(IF(I34="","",IF(I34-TODAY()&lt;0,"OVERDUE",IF(I34-TODAY()&lt;=14,"DUE NOW",IF(I34-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13482,7 +13666,7 @@
     </row>
     <row r="35" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>108</v>
@@ -13491,7 +13675,7 @@
         <v>68</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>251</v>
@@ -13500,17 +13684,17 @@
         <v>259</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="I35" s="13">
         <v>46446</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="K35" s="15"/>
       <c r="L35" s="9" t="s">
@@ -13522,12 +13706,12 @@
       <c r="P35" s="13"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="9" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>108</v>
@@ -13536,7 +13720,7 @@
         <v>68</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>251</v>
@@ -13545,17 +13729,17 @@
         <v>259</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="I36" s="13">
         <v>46477</v>
       </c>
       <c r="J36" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K36" s="15"/>
       <c r="L36" s="9" t="s">
@@ -13570,7 +13754,7 @@
     </row>
     <row r="37" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>108</v>
@@ -13579,16 +13763,16 @@
         <v>68</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>106</v>
@@ -13598,7 +13782,7 @@
       </c>
       <c r="J37" s="15">
         <f t="shared" ref="J37:J65" ca="1" si="2">IFERROR(IF(I37="","",I37-TODAY()),"")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K37" s="15" t="str">
         <f t="shared" ref="K37:K43" ca="1" si="3">IFERROR(IF(I37="","",IF(I37-TODAY()&lt;0,"OVERDUE",IF(I37-TODAY()&lt;=14,"DUE NOW",IF(I37-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13616,7 +13800,7 @@
     </row>
     <row r="38" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>108</v>
@@ -13625,16 +13809,16 @@
         <v>68</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>106</v>
@@ -13644,7 +13828,7 @@
       </c>
       <c r="J38" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K38" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -13662,7 +13846,7 @@
     </row>
     <row r="39" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>88</v>
@@ -13671,26 +13855,26 @@
         <v>90</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="I39" s="13">
         <v>46265</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K39" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -13708,7 +13892,7 @@
     </row>
     <row r="40" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>88</v>
@@ -13717,26 +13901,26 @@
         <v>90</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="I40" s="13">
         <v>46536</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="K40" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -13754,7 +13938,7 @@
     </row>
     <row r="41" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>88</v>
@@ -13763,26 +13947,26 @@
         <v>90</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="I41" s="13">
         <v>46356</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="K41" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -13800,7 +13984,7 @@
     </row>
     <row r="42" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>88</v>
@@ -13809,16 +13993,16 @@
         <v>90</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>259</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>106</v>
@@ -13828,7 +14012,7 @@
       </c>
       <c r="J42" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K42" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -13846,7 +14030,7 @@
     </row>
     <row r="43" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>88</v>
@@ -13855,7 +14039,7 @@
         <v>68</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>251</v>
@@ -13864,17 +14048,17 @@
         <v>259</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="I43" s="13">
         <v>46366</v>
       </c>
       <c r="J43" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K43" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -13892,7 +14076,7 @@
     </row>
     <row r="44" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>88</v>
@@ -13901,7 +14085,7 @@
         <v>68</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>251</v>
@@ -13910,7 +14094,7 @@
         <v>259</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>106</v>
@@ -13920,7 +14104,7 @@
       </c>
       <c r="J44" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="K44" s="15"/>
       <c r="L44" s="9" t="s">
@@ -13935,7 +14119,7 @@
     </row>
     <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>88</v>
@@ -13944,7 +14128,7 @@
         <v>68</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>251</v>
@@ -13953,17 +14137,17 @@
         <v>259</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="I45" s="13">
         <v>46477</v>
       </c>
       <c r="J45" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K45" s="15"/>
       <c r="L45" s="9" t="s">
@@ -13978,7 +14162,7 @@
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>88</v>
@@ -13987,7 +14171,7 @@
         <v>68</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>235</v>
@@ -13996,17 +14180,17 @@
         <v>259</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="I46" s="13">
         <v>46477</v>
       </c>
       <c r="J46" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K46" s="15"/>
       <c r="L46" s="9" t="s">
@@ -14021,7 +14205,7 @@
     </row>
     <row r="47" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>118</v>
@@ -14030,7 +14214,7 @@
         <v>120</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>120</v>
@@ -14039,17 +14223,17 @@
         <v>259</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="I47" s="13">
         <v>46295</v>
       </c>
       <c r="J47" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K47" s="15" t="str">
         <f t="shared" ref="K47:K65" ca="1" si="4">IFERROR(IF(I47="","",IF(I47-TODAY()&lt;0,"OVERDUE",IF(I47-TODAY()&lt;=14,"DUE NOW",IF(I47-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -14067,7 +14251,7 @@
     </row>
     <row r="48" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>118</v>
@@ -14076,7 +14260,7 @@
         <v>120</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>120</v>
@@ -14085,17 +14269,17 @@
         <v>259</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="I48" s="13">
         <v>46265</v>
       </c>
       <c r="J48" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K48" s="15" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14571,357 +14755,357 @@
   <sheetData>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="34" t="s">
-        <v>503</v>
-      </c>
-      <c r="C5" s="34"/>
+      <c r="B5" s="33" t="s">
+        <v>490</v>
+      </c>
+      <c r="C5" s="33"/>
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="22" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="22" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="22" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="22" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="22" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="22" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="8" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="23" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="23" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="23" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="23" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="23" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="23" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="23" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="23" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="32" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="C28" s="32"/>
     </row>
     <row r="29" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="32" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="C29" s="32"/>
     </row>
     <row r="30" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="32" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="C30" s="32"/>
     </row>
     <row r="31" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="32" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="C31" s="32"/>
     </row>
     <row r="32" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="32" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="C32" s="32"/>
     </row>
     <row r="33" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="32" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="C33" s="32"/>
     </row>
     <row r="34" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="32" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="C34" s="32"/>
     </row>
     <row r="36" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="4" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="34" t="s">
+        <v>534</v>
+      </c>
+      <c r="C37" s="34"/>
+    </row>
+    <row r="38" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="34" t="s">
+        <v>535</v>
+      </c>
+      <c r="C38" s="34"/>
+    </row>
+    <row r="39" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="34" t="s">
+        <v>536</v>
+      </c>
+      <c r="C39" s="34"/>
+    </row>
+    <row r="40" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="C40" s="34"/>
+    </row>
+    <row r="41" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="34" t="s">
+        <v>538</v>
+      </c>
+      <c r="C41" s="34"/>
+    </row>
+    <row r="42" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="34" t="s">
+        <v>539</v>
+      </c>
+      <c r="C42" s="34"/>
+    </row>
+    <row r="43" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="34" t="s">
+        <v>540</v>
+      </c>
+      <c r="C43" s="34"/>
+    </row>
+    <row r="44" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="34" t="s">
+        <v>541</v>
+      </c>
+      <c r="C44" s="34"/>
+    </row>
+    <row r="45" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="34" t="s">
+        <v>542</v>
+      </c>
+      <c r="C45" s="34"/>
+    </row>
+    <row r="46" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="34" t="s">
+        <v>543</v>
+      </c>
+      <c r="C46" s="34"/>
+    </row>
+    <row r="47" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="34" t="s">
+        <v>544</v>
+      </c>
+      <c r="C47" s="34"/>
+    </row>
+    <row r="48" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="C48" s="34"/>
+    </row>
+    <row r="49" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="34" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="37" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="33" t="s">
+      <c r="C49" s="34"/>
+    </row>
+    <row r="50" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="34" t="s">
         <v>547</v>
       </c>
-      <c r="C37" s="33"/>
-    </row>
-    <row r="38" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="33" t="s">
+      <c r="C50" s="34"/>
+    </row>
+    <row r="51" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="34" t="s">
         <v>548</v>
       </c>
-      <c r="C38" s="33"/>
-    </row>
-    <row r="39" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="33" t="s">
+      <c r="C51" s="34"/>
+    </row>
+    <row r="52" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="34" t="s">
         <v>549</v>
       </c>
-      <c r="C39" s="33"/>
-    </row>
-    <row r="40" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="33" t="s">
+      <c r="C52" s="34"/>
+    </row>
+    <row r="53" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="34" t="s">
         <v>550</v>
       </c>
-      <c r="C40" s="33"/>
-    </row>
-    <row r="41" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="33" t="s">
+      <c r="C53" s="34"/>
+    </row>
+    <row r="54" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="34" t="s">
         <v>551</v>
       </c>
-      <c r="C41" s="33"/>
-    </row>
-    <row r="42" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="33" t="s">
+      <c r="C54" s="34"/>
+    </row>
+    <row r="55" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="34" t="s">
         <v>552</v>
       </c>
-      <c r="C42" s="33"/>
-    </row>
-    <row r="43" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="33" t="s">
+      <c r="C55" s="34"/>
+    </row>
+    <row r="56" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="34" t="s">
         <v>553</v>
       </c>
-      <c r="C43" s="33"/>
-    </row>
-    <row r="44" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="33" t="s">
-        <v>554</v>
-      </c>
-      <c r="C44" s="33"/>
-    </row>
-    <row r="45" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="33" t="s">
-        <v>555</v>
-      </c>
-      <c r="C45" s="33"/>
-    </row>
-    <row r="46" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="33" t="s">
-        <v>556</v>
-      </c>
-      <c r="C46" s="33"/>
-    </row>
-    <row r="47" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="33" t="s">
-        <v>557</v>
-      </c>
-      <c r="C47" s="33"/>
-    </row>
-    <row r="48" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="33" t="s">
-        <v>558</v>
-      </c>
-      <c r="C48" s="33"/>
-    </row>
-    <row r="49" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="33" t="s">
-        <v>559</v>
-      </c>
-      <c r="C49" s="33"/>
-    </row>
-    <row r="50" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="33" t="s">
-        <v>560</v>
-      </c>
-      <c r="C50" s="33"/>
-    </row>
-    <row r="51" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="33" t="s">
-        <v>561</v>
-      </c>
-      <c r="C51" s="33"/>
-    </row>
-    <row r="52" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="33" t="s">
-        <v>562</v>
-      </c>
-      <c r="C52" s="33"/>
-    </row>
-    <row r="53" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="33" t="s">
-        <v>563</v>
-      </c>
-      <c r="C53" s="33"/>
-    </row>
-    <row r="54" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="33" t="s">
-        <v>564</v>
-      </c>
-      <c r="C54" s="33"/>
-    </row>
-    <row r="55" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="33" t="s">
-        <v>565</v>
-      </c>
-      <c r="C55" s="33"/>
-    </row>
-    <row r="56" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="33" t="s">
-        <v>566</v>
-      </c>
-      <c r="C56" s="33"/>
+      <c r="C56" s="34"/>
     </row>
     <row r="58" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="4" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
     </row>
     <row r="59" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="32" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="C59" s="32"/>
     </row>
     <row r="60" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="32" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="C60" s="32"/>
     </row>
     <row r="61" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="32" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="C61" s="32"/>
     </row>
     <row r="62" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="32" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="C62" s="32"/>
     </row>
@@ -14931,37 +15115,12 @@
     </row>
     <row r="64" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="32" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="C64" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
     <mergeCell ref="B61:C61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="B63:C63"/>
@@ -14971,6 +15130,31 @@
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -14992,245 +15176,245 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>581</v>
+        <v>686</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>130</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
-        <v>584</v>
+        <v>687</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>585</v>
+        <v>688</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>586</v>
+        <v>568</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>590</v>
+        <v>574</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>217</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="E8" s="21" t="s">
         <v>223</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>595</v>
+        <v>579</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>597</v>
+        <v>581</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>222</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="21" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="21" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="21" t="s">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="E12" s="21" t="s">
         <v>395</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="21" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="21" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="21" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>627</v>
+        <v>611</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="21" t="s">
-        <v>628</v>
+        <v>612</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>627</v>
+        <v>611</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="21" t="s">
-        <v>630</v>
+        <v>614</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="C19" s="21" t="s">
         <v>219</v>
@@ -15238,10 +15422,10 @@
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="21" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="C20" s="21" t="s">
         <v>219</v>
@@ -15249,32 +15433,32 @@
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="21" t="s">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="21" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="21" t="s">
-        <v>639</v>
+        <v>623</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
       <c r="C23" s="21" t="s">
         <v>219</v>
@@ -15282,10 +15466,10 @@
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="21" t="s">
-        <v>641</v>
+        <v>625</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>642</v>
+        <v>626</v>
       </c>
       <c r="C24" s="21" t="s">
         <v>219</v>
@@ -15293,76 +15477,76 @@
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
-        <v>643</v>
+        <v>627</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>644</v>
+        <v>628</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="21" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="21" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="21" t="s">
-        <v>652</v>
+        <v>636</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="21" t="s">
-        <v>654</v>
+        <v>638</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>655</v>
+        <v>639</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="21" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>658</v>
+        <v>642</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="21" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>61</v>
@@ -15370,21 +15554,21 @@
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="21" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="21" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
       <c r="C33" s="21" t="s">
         <v>219</v>
@@ -15392,35 +15576,35 @@
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="21" t="s">
-        <v>665</v>
+        <v>649</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>666</v>
+        <v>650</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="21" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="21" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>

--- a/registers/NEK_Master_Registers.xlsx
+++ b/registers/NEK_Master_Registers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude Cowork\NEK\registers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F338D5D4-5712-47B7-8FF2-48EE030FAD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDE81F4-6544-4301-8EA2-37F46EE754FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -551,9 +551,6 @@
     <t>Next renewal capped to max RM 9000 per month</t>
   </si>
   <si>
-    <t xml:space="preserve">Sha Tin </t>
-  </si>
-  <si>
     <t>Sha Tin Riverpark</t>
   </si>
   <si>
@@ -2166,6 +2163,9 @@
   </si>
   <si>
     <t>TNB</t>
+  </si>
+  <si>
+    <t>Sha Tin</t>
   </si>
 </sst>
 </file>
@@ -2397,8 +2397,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2911,6 +2911,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
@@ -2919,16 +2929,6 @@
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2955,71 +2955,71 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>50</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>659</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>660</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>661</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>662</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>62</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="25" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B5" s="25" t="s">
         <v>66</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D5" s="25"/>
       <c r="E5" s="26" t="s">
+        <v>666</v>
+      </c>
+      <c r="F5" s="26" t="s">
         <v>667</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>668</v>
       </c>
       <c r="G5" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>77</v>
@@ -3029,26 +3029,26 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D6" s="25"/>
       <c r="E6" s="26" t="s">
+        <v>666</v>
+      </c>
+      <c r="F6" s="26" t="s">
         <v>667</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>668</v>
       </c>
       <c r="G6" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="I6" s="25" t="s">
         <v>77</v>
@@ -3058,20 +3058,20 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>80</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="26" t="s">
+        <v>666</v>
+      </c>
+      <c r="F7" s="26" t="s">
         <v>667</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>668</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>71</v>
@@ -3085,20 +3085,20 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>84</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="26" t="s">
+        <v>666</v>
+      </c>
+      <c r="F8" s="26" t="s">
         <v>667</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>668</v>
       </c>
       <c r="G8" s="25" t="s">
         <v>71</v>
@@ -3112,26 +3112,26 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>88</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="26" t="s">
+        <v>666</v>
+      </c>
+      <c r="F9" s="26" t="s">
         <v>667</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>668</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="I9" s="25" t="s">
         <v>77</v>
@@ -3141,20 +3141,20 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="26" t="s">
+        <v>666</v>
+      </c>
+      <c r="F10" s="26" t="s">
         <v>667</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>668</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>71</v>
@@ -3168,20 +3168,20 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="25" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>99</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="26" t="s">
+        <v>666</v>
+      </c>
+      <c r="F11" s="26" t="s">
         <v>667</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>668</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>71</v>
@@ -3195,20 +3195,20 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D12" s="25"/>
       <c r="E12" s="26" t="s">
+        <v>666</v>
+      </c>
+      <c r="F12" s="26" t="s">
         <v>667</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>668</v>
       </c>
       <c r="G12" s="25" t="s">
         <v>71</v>
@@ -3222,20 +3222,20 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="25" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B13" s="25" t="s">
         <v>108</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="26" t="s">
+        <v>666</v>
+      </c>
+      <c r="F13" s="26" t="s">
         <v>667</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>668</v>
       </c>
       <c r="G13" s="25" t="s">
         <v>71</v>
@@ -3249,26 +3249,26 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>112</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="26" t="s">
+        <v>666</v>
+      </c>
+      <c r="F14" s="26" t="s">
         <v>667</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>668</v>
       </c>
       <c r="G14" s="25" t="s">
         <v>92</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="I14" s="25" t="s">
         <v>77</v>
@@ -3278,26 +3278,26 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B15" s="25" t="s">
         <v>118</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="26" t="s">
+        <v>666</v>
+      </c>
+      <c r="F15" s="26" t="s">
         <v>667</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>668</v>
       </c>
       <c r="G15" s="25" t="s">
         <v>121</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="I15" s="25" t="s">
         <v>77</v>
@@ -3307,26 +3307,26 @@
     </row>
     <row r="16" spans="1:11" ht="57.5" x14ac:dyDescent="0.35">
       <c r="A16" s="25" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B16" s="25" t="s">
         <v>116</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D16" s="25"/>
       <c r="E16" s="26" t="s">
+        <v>666</v>
+      </c>
+      <c r="F16" s="26" t="s">
         <v>667</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>668</v>
       </c>
       <c r="G16" s="25" t="s">
         <v>92</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I16" s="25" t="s">
         <v>77</v>
@@ -3335,7 +3335,7 @@
         <v>46234</v>
       </c>
       <c r="K16" s="26" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -3431,7 +3431,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="35" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B25" s="35"/>
       <c r="C25" s="35"/>
@@ -4653,13 +4653,13 @@
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>169</v>
       </c>
       <c r="D9" s="9">
         <v>27</v>
@@ -4668,7 +4668,7 @@
         <v>150</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>152</v>
@@ -4700,22 +4700,22 @@
         <v/>
       </c>
       <c r="P9" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q9" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="Q9" s="9" t="s">
+      <c r="R9" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="R9" s="14" t="s">
+      <c r="S9" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="T9" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="U9" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="S9" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="T9" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="U9" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="V9" s="13"/>
       <c r="W9" s="9" t="s">
@@ -4725,13 +4725,13 @@
     </row>
     <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D10" s="9">
         <v>28</v>
@@ -4740,7 +4740,7 @@
         <v>150</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>152</v>
@@ -4772,7 +4772,7 @@
         <v>Prepare</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q10" s="9"/>
       <c r="R10" s="14"/>
@@ -5904,62 +5904,62 @@
   <sheetData>
     <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>188</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>189</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="L4" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="M4" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>193</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>194</v>
       </c>
       <c r="Q4" s="8" t="s">
         <v>62</v>
@@ -5970,7 +5970,7 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>66</v>
@@ -5979,13 +5979,13 @@
         <v>113</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>197</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>198</v>
       </c>
       <c r="G5" s="13">
         <v>42856</v>
@@ -6010,13 +6010,13 @@
         <v>300</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O5" s="13">
         <v>46419</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q5" s="9" t="s">
         <v>77</v>
@@ -6025,7 +6025,7 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>66</v>
@@ -6034,13 +6034,13 @@
         <v>98</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>203</v>
-      </c>
       <c r="F6" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G6" s="13">
         <v>42856</v>
@@ -6065,13 +6065,13 @@
         <v>300</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O6" s="13">
         <v>46419</v>
       </c>
       <c r="P6" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q6" s="9" t="s">
         <v>77</v>
@@ -6080,22 +6080,22 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C7" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>208</v>
-      </c>
       <c r="F7" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G7" s="13">
         <v>42856</v>
@@ -6120,13 +6120,13 @@
         <v>300</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O7" s="13">
         <v>46419</v>
       </c>
       <c r="P7" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q7" s="9" t="s">
         <v>77</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>212</v>
-      </c>
       <c r="F8" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G8" s="13">
         <v>44197</v>
@@ -6175,13 +6175,13 @@
         <v>100</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O8" s="13">
         <v>46419</v>
       </c>
       <c r="P8" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q8" s="9" t="s">
         <v>77</v>
@@ -6818,68 +6818,68 @@
   <sheetData>
     <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>219</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>220</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="H4" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>230</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>231</v>
       </c>
       <c r="S4" s="8" t="s">
         <v>62</v>
@@ -6890,22 +6890,22 @@
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>71</v>
@@ -6915,25 +6915,25 @@
         <v>15287.150000000001</v>
       </c>
       <c r="I5" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K5" s="9">
         <v>27</v>
       </c>
       <c r="L5" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M5" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="N5" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="O5" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P5" s="9"/>
       <c r="Q5" s="13"/>
@@ -6945,22 +6945,22 @@
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>245</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>246</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>71</v>
@@ -6970,25 +6970,25 @@
         <v>2949</v>
       </c>
       <c r="I6" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K6" s="9">
         <v>15</v>
       </c>
       <c r="L6" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M6" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="N6" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="O6" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P6" s="9"/>
       <c r="Q6" s="13"/>
@@ -7000,22 +7000,22 @@
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>71</v>
@@ -7025,25 +7025,25 @@
         <v>368.75</v>
       </c>
       <c r="I7" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K7" s="9">
         <v>15</v>
       </c>
       <c r="L7" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M7" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="N7" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="O7" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="13"/>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E8" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>251</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>252</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>71</v>
@@ -7080,25 +7080,25 @@
         <v>411.5</v>
       </c>
       <c r="I8" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K8" s="30">
         <v>15</v>
       </c>
       <c r="L8" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M8" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="N8" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="O8" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P8" s="9"/>
       <c r="Q8" s="13"/>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>255</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>256</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>71</v>
@@ -7134,25 +7134,25 @@
         <v>2700</v>
       </c>
       <c r="I9" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K9" s="30">
         <v>10</v>
       </c>
       <c r="L9" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M9" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="N9" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="O9" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P9" s="9"/>
       <c r="Q9" s="13"/>
@@ -7164,13 +7164,13 @@
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>61</v>
@@ -7179,7 +7179,7 @@
         <v>76</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>71</v>
@@ -7188,25 +7188,25 @@
         <v>2000</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K10" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L10" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M10" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="N10" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="O10" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P10" s="9"/>
       <c r="Q10" s="13"/>
@@ -7218,22 +7218,22 @@
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>71</v>
@@ -7242,25 +7242,25 @@
         <v>2000</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K11" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L11" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M11" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="N11" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N11" s="9" t="s">
+      <c r="O11" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P11" s="9"/>
       <c r="Q11" s="13"/>
@@ -7272,22 +7272,22 @@
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>71</v>
@@ -7296,25 +7296,25 @@
         <v>1200</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K12" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L12" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M12" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="N12" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="O12" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P12" s="9"/>
       <c r="Q12" s="13"/>
@@ -7326,22 +7326,22 @@
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>71</v>
@@ -7350,25 +7350,25 @@
         <v>1200</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K13" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L13" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M13" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="N13" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="O13" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P13" s="9"/>
       <c r="Q13" s="13"/>
@@ -7380,22 +7380,22 @@
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C14" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>272</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>273</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>71</v>
@@ -7404,25 +7404,25 @@
         <v>9000</v>
       </c>
       <c r="I14" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K14" s="30">
         <v>1</v>
       </c>
       <c r="L14" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M14" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M14" s="9" t="s">
+      <c r="N14" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N14" s="9" t="s">
+      <c r="O14" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P14" s="9"/>
       <c r="Q14" s="13"/>
@@ -7434,22 +7434,22 @@
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>271</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>71</v>
@@ -7458,25 +7458,25 @@
         <v>10000</v>
       </c>
       <c r="I15" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K15" s="30">
         <v>1</v>
       </c>
       <c r="L15" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M15" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="N15" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="O15" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P15" s="9"/>
       <c r="Q15" s="13"/>
@@ -7488,22 +7488,22 @@
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>271</v>
-      </c>
       <c r="E16" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>71</v>
@@ -7512,25 +7512,25 @@
         <v>8750</v>
       </c>
       <c r="I16" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K16" s="30">
         <v>1</v>
       </c>
       <c r="L16" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M16" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="N16" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N16" s="9" t="s">
+      <c r="O16" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P16" s="9"/>
       <c r="Q16" s="13"/>
@@ -7542,22 +7542,22 @@
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>271</v>
-      </c>
       <c r="E17" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>71</v>
@@ -7566,25 +7566,25 @@
         <v>8500</v>
       </c>
       <c r="I17" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K17" s="9">
         <v>1</v>
       </c>
       <c r="L17" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M17" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="N17" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N17" s="9" t="s">
+      <c r="O17" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P17" s="9"/>
       <c r="Q17" s="13"/>
@@ -7596,22 +7596,22 @@
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>234</v>
-      </c>
       <c r="E18" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>71</v>
@@ -7620,25 +7620,25 @@
         <v>5321.85</v>
       </c>
       <c r="I18" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K18" s="9">
         <v>27</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M18" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="N18" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N18" s="9" t="s">
+      <c r="O18" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P18" s="9"/>
       <c r="Q18" s="13"/>
@@ -7650,22 +7650,22 @@
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D19" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="F19" s="9" t="s">
         <v>245</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>246</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>71</v>
@@ -7675,25 +7675,25 @@
         <v>945</v>
       </c>
       <c r="I19" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K19" s="9">
         <v>15</v>
       </c>
       <c r="L19" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M19" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M19" s="9" t="s">
+      <c r="N19" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N19" s="9" t="s">
+      <c r="O19" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P19" s="9"/>
       <c r="Q19" s="13"/>
@@ -7705,22 +7705,22 @@
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E20" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>71</v>
@@ -7729,25 +7729,25 @@
         <v>74.400000000000006</v>
       </c>
       <c r="I20" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K20" s="9">
         <v>15</v>
       </c>
       <c r="L20" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M20" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M20" s="9" t="s">
+      <c r="N20" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N20" s="9" t="s">
+      <c r="O20" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P20" s="9"/>
       <c r="Q20" s="13"/>
@@ -7759,22 +7759,22 @@
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E21" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>251</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>252</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>71</v>
@@ -7783,25 +7783,25 @@
         <v>240.5</v>
       </c>
       <c r="I21" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K21" s="9">
         <v>15</v>
       </c>
       <c r="L21" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M21" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M21" s="9" t="s">
+      <c r="N21" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="O21" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P21" s="9"/>
       <c r="Q21" s="13"/>
@@ -7813,22 +7813,22 @@
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>71</v>
@@ -7837,25 +7837,25 @@
         <v>6500</v>
       </c>
       <c r="I22" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K22" s="9">
         <v>15</v>
       </c>
       <c r="L22" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M22" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M22" s="9" t="s">
+      <c r="N22" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N22" s="9" t="s">
+      <c r="O22" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O22" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P22" s="9"/>
       <c r="Q22" s="13"/>
@@ -7867,22 +7867,22 @@
     </row>
     <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E23" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>289</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>290</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>71</v>
@@ -7891,25 +7891,25 @@
         <v>1017.6</v>
       </c>
       <c r="I23" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K23" s="9">
         <v>7</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M23" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="N23" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N23" s="9" t="s">
+      <c r="O23" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P23" s="9"/>
       <c r="Q23" s="13"/>
@@ -7921,49 +7921,49 @@
     </row>
     <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="F24" s="9" t="s">
         <v>293</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>294</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I24" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K24" s="9">
         <v>15</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M24" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="N24" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N24" s="9" t="s">
+      <c r="O24" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P24" s="9"/>
       <c r="Q24" s="13"/>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D25" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="F25" s="9" t="s">
         <v>298</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>299</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>71</v>
@@ -7999,25 +7999,25 @@
         <v>1296.58</v>
       </c>
       <c r="I25" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K25" s="9">
         <v>15</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M25" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="N25" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N25" s="9" t="s">
+      <c r="O25" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P25" s="9"/>
       <c r="Q25" s="13"/>
@@ -8029,22 +8029,22 @@
     </row>
     <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D26" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>298</v>
-      </c>
       <c r="F26" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>71</v>
@@ -8053,25 +8053,25 @@
         <v>1296.58</v>
       </c>
       <c r="I26" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K26" s="9">
         <v>15</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M26" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="N26" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N26" s="9" t="s">
+      <c r="O26" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O26" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P26" s="9"/>
       <c r="Q26" s="13"/>
@@ -8083,22 +8083,22 @@
     </row>
     <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D27" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>298</v>
-      </c>
       <c r="F27" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>71</v>
@@ -8107,25 +8107,25 @@
         <v>1296.58</v>
       </c>
       <c r="I27" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K27" s="9">
         <v>15</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M27" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="N27" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N27" s="9" t="s">
+      <c r="O27" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P27" s="9"/>
       <c r="Q27" s="13"/>
@@ -8137,22 +8137,22 @@
     </row>
     <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D28" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="E28" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>298</v>
-      </c>
       <c r="F28" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>71</v>
@@ -8161,25 +8161,25 @@
         <v>1296.58</v>
       </c>
       <c r="I28" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J28" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K28" s="30">
         <v>15</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M28" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="N28" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N28" s="9" t="s">
+      <c r="O28" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O28" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P28" s="9"/>
       <c r="Q28" s="13"/>
@@ -8191,22 +8191,22 @@
     </row>
     <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D29" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>298</v>
-      </c>
       <c r="F29" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>71</v>
@@ -8215,25 +8215,25 @@
         <v>968.82</v>
       </c>
       <c r="I29" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K29" s="30">
         <v>15</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M29" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="N29" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N29" s="9" t="s">
+      <c r="O29" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P29" s="9"/>
       <c r="Q29" s="13"/>
@@ -8245,22 +8245,22 @@
     </row>
     <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D30" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="F30" s="9" t="s">
         <v>310</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>311</v>
       </c>
       <c r="G30" s="9" t="s">
         <v>71</v>
@@ -8270,25 +8270,25 @@
         <v>695</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K30" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M30" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="N30" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N30" s="9" t="s">
+      <c r="O30" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O30" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P30" s="9"/>
       <c r="Q30" s="13"/>
@@ -8300,22 +8300,22 @@
     </row>
     <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E31" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="F31" s="9" t="s">
         <v>313</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>314</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>71</v>
@@ -8325,25 +8325,25 @@
         <v>5041.2</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J31" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="K31" s="30" t="s">
         <v>315</v>
       </c>
-      <c r="K31" s="30" t="s">
-        <v>316</v>
-      </c>
       <c r="L31" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M31" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="N31" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N31" s="9" t="s">
+      <c r="O31" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O31" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P31" s="9"/>
       <c r="Q31" s="13"/>
@@ -8355,13 +8355,13 @@
     </row>
     <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>61</v>
@@ -8370,7 +8370,7 @@
         <v>76</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G32" s="9" t="s">
         <v>71</v>
@@ -8379,25 +8379,25 @@
         <v>2000</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K32" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L32" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M32" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M32" s="9" t="s">
+      <c r="N32" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N32" s="9" t="s">
+      <c r="O32" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O32" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P32" s="9"/>
       <c r="Q32" s="13"/>
@@ -8409,22 +8409,22 @@
     </row>
     <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>71</v>
@@ -8433,25 +8433,25 @@
         <v>2000</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K33" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L33" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M33" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M33" s="9" t="s">
+      <c r="N33" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N33" s="9" t="s">
+      <c r="O33" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O33" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P33" s="9"/>
       <c r="Q33" s="13"/>
@@ -8463,22 +8463,22 @@
     </row>
     <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G34" s="9" t="s">
         <v>71</v>
@@ -8487,25 +8487,25 @@
         <v>1200</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K34" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L34" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M34" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M34" s="9" t="s">
+      <c r="N34" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N34" s="9" t="s">
+      <c r="O34" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O34" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P34" s="9"/>
       <c r="Q34" s="13"/>
@@ -8517,22 +8517,22 @@
     </row>
     <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G35" s="9" t="s">
         <v>71</v>
@@ -8541,25 +8541,25 @@
         <v>1200</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K35" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L35" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M35" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M35" s="9" t="s">
+      <c r="N35" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N35" s="9" t="s">
+      <c r="O35" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P35" s="9"/>
       <c r="Q35" s="13"/>
@@ -8571,22 +8571,22 @@
     </row>
     <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E36" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="F36" s="9" t="s">
         <v>322</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>323</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>71</v>
@@ -8595,25 +8595,25 @@
         <v>104.95</v>
       </c>
       <c r="I36" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J36" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K36" s="30">
         <v>27</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N36" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O36" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O36" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P36" s="9"/>
       <c r="Q36" s="13"/>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D37" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="F37" s="9" t="s">
         <v>326</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>327</v>
       </c>
       <c r="G37" s="9" t="s">
         <v>71</v>
@@ -8649,25 +8649,25 @@
         <v>240</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K37" s="31" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N37" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O37" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P37" s="9"/>
       <c r="Q37" s="13"/>
@@ -8679,13 +8679,13 @@
     </row>
     <row r="38" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>61</v>
@@ -8694,7 +8694,7 @@
         <v>76</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>71</v>
@@ -8703,25 +8703,25 @@
         <v>2000</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K38" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N38" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O38" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O38" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P38" s="9"/>
       <c r="Q38" s="13"/>
@@ -8733,22 +8733,22 @@
     </row>
     <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>71</v>
@@ -8757,25 +8757,25 @@
         <v>2000</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K39" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N39" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O39" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O39" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P39" s="9"/>
       <c r="Q39" s="13"/>
@@ -8787,22 +8787,22 @@
     </row>
     <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>71</v>
@@ -8811,25 +8811,25 @@
         <v>1200</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K40" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N40" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O40" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O40" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P40" s="9"/>
       <c r="Q40" s="13"/>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>71</v>
@@ -8865,25 +8865,25 @@
         <v>1200</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K41" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L41" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N41" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O41" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O41" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P41" s="9"/>
       <c r="Q41" s="13"/>
@@ -8895,13 +8895,13 @@
     </row>
     <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>61</v>
@@ -8910,7 +8910,7 @@
         <v>76</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>71</v>
@@ -8919,25 +8919,25 @@
         <v>2000</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K42" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N42" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O42" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O42" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P42" s="9"/>
       <c r="Q42" s="13"/>
@@ -8949,22 +8949,22 @@
     </row>
     <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>71</v>
@@ -8973,25 +8973,25 @@
         <v>2000</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K43" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L43" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N43" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O43" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P43" s="9"/>
       <c r="Q43" s="13"/>
@@ -9003,22 +9003,22 @@
     </row>
     <row r="44" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G44" s="9" t="s">
         <v>71</v>
@@ -9027,25 +9027,25 @@
         <v>1200</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K44" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N44" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O44" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O44" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P44" s="9"/>
       <c r="Q44" s="13"/>
@@ -9057,22 +9057,22 @@
     </row>
     <row r="45" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>71</v>
@@ -9081,25 +9081,25 @@
         <v>1200</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K45" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N45" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O45" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O45" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P45" s="9"/>
       <c r="Q45" s="13"/>
@@ -9111,13 +9111,13 @@
     </row>
     <row r="46" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>61</v>
@@ -9126,7 +9126,7 @@
         <v>76</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>71</v>
@@ -9135,25 +9135,25 @@
         <v>2000</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K46" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L46" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N46" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O46" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O46" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P46" s="9"/>
       <c r="Q46" s="13"/>
@@ -9165,22 +9165,22 @@
     </row>
     <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G47" s="9" t="s">
         <v>71</v>
@@ -9189,25 +9189,25 @@
         <v>2000</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K47" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N47" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O47" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O47" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P47" s="9"/>
       <c r="Q47" s="13"/>
@@ -9219,22 +9219,22 @@
     </row>
     <row r="48" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G48" s="9" t="s">
         <v>71</v>
@@ -9243,25 +9243,25 @@
         <v>1200</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K48" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N48" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O48" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O48" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P48" s="9"/>
       <c r="Q48" s="13"/>
@@ -9273,22 +9273,22 @@
     </row>
     <row r="49" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G49" s="9" t="s">
         <v>71</v>
@@ -9297,25 +9297,25 @@
         <v>1200</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K49" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N49" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O49" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O49" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P49" s="9"/>
       <c r="Q49" s="13"/>
@@ -9327,13 +9327,13 @@
     </row>
     <row r="50" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>61</v>
@@ -9342,7 +9342,7 @@
         <v>76</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G50" s="9" t="s">
         <v>71</v>
@@ -9351,25 +9351,25 @@
         <v>2000</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K50" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L50" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M50" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M50" s="9" t="s">
+      <c r="N50" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N50" s="9" t="s">
+      <c r="O50" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O50" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P50" s="9"/>
       <c r="Q50" s="13"/>
@@ -9381,22 +9381,22 @@
     </row>
     <row r="51" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G51" s="9" t="s">
         <v>71</v>
@@ -9405,25 +9405,25 @@
         <v>2000</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K51" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L51" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M51" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M51" s="9" t="s">
+      <c r="N51" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N51" s="9" t="s">
+      <c r="O51" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O51" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P51" s="9"/>
       <c r="Q51" s="13"/>
@@ -9435,22 +9435,22 @@
     </row>
     <row r="52" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>71</v>
@@ -9459,25 +9459,25 @@
         <v>1200</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K52" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L52" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M52" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M52" s="9" t="s">
+      <c r="N52" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N52" s="9" t="s">
+      <c r="O52" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O52" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P52" s="9"/>
       <c r="Q52" s="13"/>
@@ -9489,22 +9489,22 @@
     </row>
     <row r="53" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>71</v>
@@ -9513,25 +9513,25 @@
         <v>1200</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K53" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L53" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="M53" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="M53" s="9" t="s">
+      <c r="N53" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="N53" s="9" t="s">
+      <c r="O53" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O53" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P53" s="9"/>
       <c r="Q53" s="13"/>
@@ -9543,13 +9543,13 @@
     </row>
     <row r="54" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>61</v>
@@ -9558,7 +9558,7 @@
         <v>76</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>71</v>
@@ -9567,25 +9567,25 @@
         <v>2000</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K54" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N54" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O54" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O54" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P54" s="9"/>
       <c r="Q54" s="13"/>
@@ -9597,22 +9597,22 @@
     </row>
     <row r="55" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>71</v>
@@ -9621,25 +9621,25 @@
         <v>2000</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K55" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N55" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O55" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O55" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P55" s="9"/>
       <c r="Q55" s="13"/>
@@ -9651,22 +9651,22 @@
     </row>
     <row r="56" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>71</v>
@@ -9675,25 +9675,25 @@
         <v>1200</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K56" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N56" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O56" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O56" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P56" s="9"/>
       <c r="Q56" s="13"/>
@@ -9705,22 +9705,22 @@
     </row>
     <row r="57" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>71</v>
@@ -9729,25 +9729,25 @@
         <v>1200</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K57" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L57" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N57" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O57" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O57" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P57" s="9"/>
       <c r="Q57" s="13"/>
@@ -9759,13 +9759,13 @@
     </row>
     <row r="58" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>61</v>
@@ -9774,7 +9774,7 @@
         <v>76</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>71</v>
@@ -9783,25 +9783,25 @@
         <v>2000</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K58" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L58" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N58" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O58" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O58" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P58" s="9"/>
       <c r="Q58" s="13"/>
@@ -9813,22 +9813,22 @@
     </row>
     <row r="59" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>71</v>
@@ -9837,25 +9837,25 @@
         <v>2000</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K59" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L59" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N59" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O59" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O59" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P59" s="9"/>
       <c r="Q59" s="13"/>
@@ -9867,22 +9867,22 @@
     </row>
     <row r="60" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>71</v>
@@ -9891,25 +9891,25 @@
         <v>1200</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K60" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L60" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N60" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O60" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O60" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P60" s="9"/>
       <c r="Q60" s="13"/>
@@ -9921,22 +9921,22 @@
     </row>
     <row r="61" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>71</v>
@@ -9945,25 +9945,25 @@
         <v>1200</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K61" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L61" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N61" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O61" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="O61" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="P61" s="9"/>
       <c r="Q61" s="13"/>
@@ -9975,22 +9975,22 @@
     </row>
     <row r="62" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D62" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="E62" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="E62" s="9" t="s">
+      <c r="F62" s="9" t="s">
         <v>356</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>357</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>92</v>
@@ -10000,25 +10000,25 @@
         <v>3280</v>
       </c>
       <c r="I62" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J62" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J62" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K62" s="9">
         <v>15</v>
       </c>
       <c r="L62" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M62" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N62" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O62" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P62" s="9"/>
       <c r="Q62" s="13"/>
@@ -10030,22 +10030,22 @@
     </row>
     <row r="63" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D63" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E63" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="E63" s="9" t="s">
+      <c r="F63" s="9" t="s">
         <v>361</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>362</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>92</v>
@@ -10054,25 +10054,25 @@
         <v>1862</v>
       </c>
       <c r="I63" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J63" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J63" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K63" s="9">
         <v>15</v>
       </c>
       <c r="L63" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P63" s="9"/>
       <c r="Q63" s="13"/>
@@ -10084,22 +10084,22 @@
     </row>
     <row r="64" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E64" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="F64" s="9" t="s">
         <v>364</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>365</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>92</v>
@@ -10108,25 +10108,25 @@
         <v>2136</v>
       </c>
       <c r="I64" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J64" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J64" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K64" s="9">
         <v>15</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M64" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N64" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O64" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P64" s="9"/>
       <c r="Q64" s="13"/>
@@ -10138,22 +10138,22 @@
     </row>
     <row r="65" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D65" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="E65" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="F65" s="9" t="s">
         <v>368</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>369</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>92</v>
@@ -10163,25 +10163,25 @@
         <v>8946</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K65" s="9">
         <v>15</v>
       </c>
       <c r="L65" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P65" s="9"/>
       <c r="Q65" s="13"/>
@@ -10193,22 +10193,22 @@
     </row>
     <row r="66" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F66" s="9" t="s">
         <v>370</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>371</v>
       </c>
       <c r="G66" s="9" t="s">
         <v>92</v>
@@ -10217,25 +10217,25 @@
         <v>25000</v>
       </c>
       <c r="I66" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J66" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J66" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K66" s="30">
         <v>15</v>
       </c>
       <c r="L66" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M66" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N66" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O66" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P66" s="9"/>
       <c r="Q66" s="13"/>
@@ -10247,22 +10247,22 @@
     </row>
     <row r="67" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C67" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D67" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="D67" s="9" t="s">
-        <v>271</v>
-      </c>
       <c r="E67" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G67" s="9" t="s">
         <v>92</v>
@@ -10271,25 +10271,25 @@
         <v>41000</v>
       </c>
       <c r="I67" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J67" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="J67" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="K67" s="30">
         <v>15</v>
       </c>
       <c r="L67" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M67" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P67" s="9"/>
       <c r="Q67" s="13"/>
@@ -10301,22 +10301,22 @@
     </row>
     <row r="68" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>118</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D68" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="E68" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="E68" s="9" t="s">
+      <c r="F68" s="9" t="s">
         <v>376</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>377</v>
       </c>
       <c r="G68" s="9" t="s">
         <v>121</v>
@@ -10325,25 +10325,25 @@
         <v>2377</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K68" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L68" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M68" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N68" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O68" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P68" s="9"/>
       <c r="Q68" s="13"/>
@@ -10355,22 +10355,22 @@
     </row>
     <row r="69" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>118</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D69" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="F69" s="9" t="s">
         <v>380</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>381</v>
       </c>
       <c r="G69" s="9" t="s">
         <v>121</v>
@@ -10379,25 +10379,25 @@
         <v>220</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K69" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L69" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M69" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P69" s="9"/>
       <c r="Q69" s="13"/>
@@ -10932,68 +10932,68 @@
   <sheetData>
     <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>386</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>387</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>389</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>390</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="K4" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>397</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>398</v>
       </c>
       <c r="S4" s="8" t="s">
         <v>62</v>
@@ -11004,13 +11004,13 @@
     </row>
     <row r="5" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>112</v>
@@ -11031,7 +11031,7 @@
       <c r="N5" s="19"/>
       <c r="O5" s="19"/>
       <c r="P5" s="20" t="str">
-        <f ca="1">IFERROR(IF(M5="","",TODAY()-M5),"")</f>
+        <f t="shared" ref="P5:P21" ca="1" si="0">IFERROR(IF(M5="","",TODAY()-M5),"")</f>
         <v/>
       </c>
       <c r="Q5" s="19"/>
@@ -11040,21 +11040,21 @@
         <v>77</v>
       </c>
       <c r="T5" s="19" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>73</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>68</v>
@@ -11072,7 +11072,7 @@
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
       <c r="P6" s="15" t="str">
-        <f ca="1">IFERROR(IF(M6="","",TODAY()-M6),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q6" s="9"/>
@@ -11081,18 +11081,18 @@
         <v>77</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>112</v>
@@ -11113,7 +11113,7 @@
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
       <c r="P7" s="15" t="str">
-        <f ca="1">IFERROR(IF(M7="","",TODAY()-M7),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q7" s="9"/>
@@ -11122,18 +11122,18 @@
         <v>77</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>88</v>
@@ -11154,7 +11154,7 @@
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
       <c r="P8" s="15" t="str">
-        <f ca="1">IFERROR(IF(M8="","",TODAY()-M8),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q8" s="9"/>
@@ -11163,12 +11163,12 @@
         <v>77</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>76</v>
@@ -11177,7 +11177,7 @@
         <v>61</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>68</v>
@@ -11195,7 +11195,7 @@
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
       <c r="P9" s="15" t="str">
-        <f ca="1">IFERROR(IF(M9="","",TODAY()-M9),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q9" s="9"/>
@@ -11204,21 +11204,21 @@
         <v>77</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>68</v>
@@ -11236,7 +11236,7 @@
       <c r="N10" s="9"/>
       <c r="O10" s="9"/>
       <c r="P10" s="15" t="str">
-        <f ca="1">IFERROR(IF(M10="","",TODAY()-M10),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q10" s="9"/>
@@ -11245,18 +11245,18 @@
         <v>77</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>66</v>
@@ -11277,7 +11277,7 @@
       <c r="N11" s="9"/>
       <c r="O11" s="9"/>
       <c r="P11" s="15" t="str">
-        <f ca="1">IFERROR(IF(M11="","",TODAY()-M11),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q11" s="9"/>
@@ -11286,21 +11286,21 @@
         <v>77</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>68</v>
@@ -11318,7 +11318,7 @@
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
       <c r="P12" s="15" t="str">
-        <f ca="1">IFERROR(IF(M12="","",TODAY()-M12),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q12" s="9"/>
@@ -11327,21 +11327,21 @@
         <v>77</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>68</v>
@@ -11359,7 +11359,7 @@
       <c r="N13" s="9"/>
       <c r="O13" s="9"/>
       <c r="P13" s="15" t="str">
-        <f ca="1">IFERROR(IF(M13="","",TODAY()-M13),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q13" s="9"/>
@@ -11368,21 +11368,21 @@
         <v>77</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C14" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>699</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>700</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>68</v>
@@ -11400,7 +11400,7 @@
       <c r="N14" s="9"/>
       <c r="O14" s="9"/>
       <c r="P14" s="15" t="str">
-        <f ca="1">IFERROR(IF(M14="","",TODAY()-M14),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q14" s="9"/>
@@ -11409,18 +11409,18 @@
         <v>77</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>112</v>
@@ -11441,7 +11441,7 @@
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
       <c r="P15" s="15" t="str">
-        <f ca="1">IFERROR(IF(M15="","",TODAY()-M15),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q15" s="9"/>
@@ -11450,21 +11450,21 @@
         <v>77</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>68</v>
@@ -11482,7 +11482,7 @@
       <c r="N16" s="9"/>
       <c r="O16" s="9"/>
       <c r="P16" s="15" t="str">
-        <f ca="1">IFERROR(IF(M16="","",TODAY()-M16),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q16" s="9"/>
@@ -11491,18 +11491,18 @@
         <v>77</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>88</v>
@@ -11523,7 +11523,7 @@
       <c r="N17" s="9"/>
       <c r="O17" s="9"/>
       <c r="P17" s="15" t="str">
-        <f ca="1">IFERROR(IF(M17="","",TODAY()-M17),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q17" s="9"/>
@@ -11532,18 +11532,18 @@
         <v>77</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>88</v>
@@ -11564,7 +11564,7 @@
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>
       <c r="P18" s="15" t="str">
-        <f ca="1">IFERROR(IF(M18="","",TODAY()-M18),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q18" s="9"/>
@@ -11573,18 +11573,18 @@
         <v>77</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>112</v>
@@ -11605,7 +11605,7 @@
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
       <c r="P19" s="15" t="str">
-        <f ca="1">IFERROR(IF(M19="","",TODAY()-M19),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q19" s="9"/>
@@ -11614,18 +11614,18 @@
         <v>77</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>84</v>
@@ -11646,7 +11646,7 @@
       <c r="N20" s="9"/>
       <c r="O20" s="9"/>
       <c r="P20" s="15" t="str">
-        <f ca="1">IFERROR(IF(M20="","",TODAY()-M20),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q20" s="9"/>
@@ -11655,18 +11655,18 @@
         <v>77</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>88</v>
@@ -11687,7 +11687,7 @@
       <c r="N21" s="9"/>
       <c r="O21" s="9"/>
       <c r="P21" s="15" t="str">
-        <f ca="1">IFERROR(IF(M21="","",TODAY()-M21),"")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Q21" s="9"/>
@@ -11696,7 +11696,7 @@
         <v>77</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -12260,65 +12260,65 @@
   <sheetData>
     <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>215</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>216</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>52</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>412</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>413</v>
       </c>
       <c r="R4" s="8" t="s">
         <v>63</v>
@@ -12326,7 +12326,7 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>66</v>
@@ -12335,19 +12335,19 @@
         <v>68</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>417</v>
       </c>
       <c r="I5" s="13">
         <v>46249</v>
@@ -12361,7 +12361,7 @@
         <v>Prepare</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M5" s="13"/>
       <c r="N5" s="9"/>
@@ -12372,7 +12372,7 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>66</v>
@@ -12381,19 +12381,19 @@
         <v>68</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>420</v>
-      </c>
       <c r="F6" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I6" s="13">
         <v>46249</v>
@@ -12407,7 +12407,7 @@
         <v>Prepare</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M6" s="13"/>
       <c r="N6" s="9"/>
@@ -12418,7 +12418,7 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>66</v>
@@ -12427,19 +12427,19 @@
         <v>68</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I7" s="13">
         <v>46249</v>
@@ -12453,7 +12453,7 @@
         <v>Prepare</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="9"/>
@@ -12464,7 +12464,7 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>66</v>
@@ -12473,16 +12473,16 @@
         <v>68</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>106</v>
@@ -12499,7 +12499,7 @@
         <v>DUE NOW</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M8" s="13"/>
       <c r="N8" s="9"/>
@@ -12510,7 +12510,7 @@
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>66</v>
@@ -12519,16 +12519,16 @@
         <v>68</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E9" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>106</v>
@@ -12556,7 +12556,7 @@
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>66</v>
@@ -12565,19 +12565,19 @@
         <v>68</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>429</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>430</v>
       </c>
       <c r="I10" s="13">
         <v>46366</v>
@@ -12591,7 +12591,7 @@
         <v/>
       </c>
       <c r="L10" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="9"/>
@@ -12602,7 +12602,7 @@
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>66</v>
@@ -12611,16 +12611,16 @@
         <v>68</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>106</v>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="K11" s="15"/>
       <c r="L11" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="9"/>
@@ -12645,7 +12645,7 @@
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>66</v>
@@ -12654,19 +12654,19 @@
         <v>68</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H12" s="17" t="s">
         <v>435</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>436</v>
       </c>
       <c r="I12" s="13">
         <v>46477</v>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="K12" s="15"/>
       <c r="L12" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M12" s="13"/>
       <c r="N12" s="9"/>
@@ -12688,7 +12688,7 @@
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>66</v>
@@ -12697,19 +12697,19 @@
         <v>68</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H13" s="17" t="s">
         <v>438</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>439</v>
       </c>
       <c r="I13" s="13">
         <v>46477</v>
@@ -12720,7 +12720,7 @@
       </c>
       <c r="K13" s="15"/>
       <c r="L13" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M13" s="13"/>
       <c r="N13" s="9"/>
@@ -12731,7 +12731,7 @@
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>84</v>
@@ -12740,16 +12740,16 @@
         <v>68</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>70</v>
@@ -12763,7 +12763,7 @@
       </c>
       <c r="K14" s="15"/>
       <c r="L14" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M14" s="13"/>
       <c r="N14" s="9"/>
@@ -12774,7 +12774,7 @@
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>84</v>
@@ -12783,16 +12783,16 @@
         <v>68</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>106</v>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="K15" s="15"/>
       <c r="L15" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="9"/>
@@ -12817,7 +12817,7 @@
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>84</v>
@@ -12826,19 +12826,19 @@
         <v>68</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H16" s="17" t="s">
         <v>435</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>436</v>
       </c>
       <c r="I16" s="13">
         <v>46477</v>
@@ -12849,7 +12849,7 @@
       </c>
       <c r="K16" s="15"/>
       <c r="L16" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="9"/>
@@ -12860,7 +12860,7 @@
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>84</v>
@@ -12869,16 +12869,16 @@
         <v>68</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G17" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>106</v>
@@ -12895,7 +12895,7 @@
         <v>DUE NOW</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="9"/>
@@ -12906,7 +12906,7 @@
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>84</v>
@@ -12915,16 +12915,16 @@
         <v>68</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E18" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G18" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>106</v>
@@ -12952,7 +12952,7 @@
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>95</v>
@@ -12961,16 +12961,16 @@
         <v>68</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>106</v>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="K19" s="15"/>
       <c r="L19" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M19" s="13"/>
       <c r="N19" s="9"/>
@@ -12995,7 +12995,7 @@
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>95</v>
@@ -13004,19 +13004,19 @@
         <v>68</v>
       </c>
       <c r="D20" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H20" s="17" t="s">
         <v>435</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>436</v>
       </c>
       <c r="I20" s="13">
         <v>46477</v>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="K20" s="15"/>
       <c r="L20" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M20" s="13"/>
       <c r="N20" s="9"/>
@@ -13038,7 +13038,7 @@
     </row>
     <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>95</v>
@@ -13047,16 +13047,16 @@
         <v>68</v>
       </c>
       <c r="D21" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>106</v>
@@ -13073,7 +13073,7 @@
         <v>DUE NOW</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="9"/>
@@ -13084,7 +13084,7 @@
     </row>
     <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>95</v>
@@ -13093,16 +13093,16 @@
         <v>68</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E22" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G22" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>106</v>
@@ -13130,7 +13130,7 @@
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>99</v>
@@ -13139,16 +13139,16 @@
         <v>68</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>106</v>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="K23" s="15"/>
       <c r="L23" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M23" s="13"/>
       <c r="N23" s="9"/>
@@ -13173,7 +13173,7 @@
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>99</v>
@@ -13182,19 +13182,19 @@
         <v>68</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H24" s="17" t="s">
         <v>435</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H24" s="17" t="s">
-        <v>436</v>
       </c>
       <c r="I24" s="13">
         <v>46477</v>
@@ -13205,7 +13205,7 @@
       </c>
       <c r="K24" s="15"/>
       <c r="L24" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M24" s="13"/>
       <c r="N24" s="9"/>
@@ -13216,7 +13216,7 @@
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>99</v>
@@ -13225,16 +13225,16 @@
         <v>68</v>
       </c>
       <c r="D25" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="F25" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G25" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>106</v>
@@ -13251,7 +13251,7 @@
         <v>DUE NOW</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M25" s="13"/>
       <c r="N25" s="9"/>
@@ -13262,7 +13262,7 @@
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>99</v>
@@ -13271,16 +13271,16 @@
         <v>68</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E26" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G26" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>106</v>
@@ -13308,7 +13308,7 @@
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>80</v>
@@ -13317,16 +13317,16 @@
         <v>68</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>106</v>
@@ -13340,7 +13340,7 @@
       </c>
       <c r="K27" s="15"/>
       <c r="L27" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="9"/>
@@ -13351,7 +13351,7 @@
     </row>
     <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>80</v>
@@ -13360,19 +13360,19 @@
         <v>68</v>
       </c>
       <c r="D28" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H28" s="17" t="s">
         <v>435</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>436</v>
       </c>
       <c r="I28" s="13">
         <v>46477</v>
@@ -13383,7 +13383,7 @@
       </c>
       <c r="K28" s="15"/>
       <c r="L28" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="9"/>
@@ -13394,7 +13394,7 @@
     </row>
     <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>80</v>
@@ -13403,16 +13403,16 @@
         <v>68</v>
       </c>
       <c r="D29" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="F29" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G29" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>106</v>
@@ -13429,7 +13429,7 @@
         <v>DUE NOW</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="9"/>
@@ -13440,7 +13440,7 @@
     </row>
     <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>80</v>
@@ -13449,16 +13449,16 @@
         <v>68</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E30" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G30" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>106</v>
@@ -13486,7 +13486,7 @@
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>103</v>
@@ -13495,19 +13495,19 @@
         <v>68</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I31" s="13">
         <v>46446</v>
@@ -13518,7 +13518,7 @@
       </c>
       <c r="K31" s="15"/>
       <c r="L31" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="9"/>
@@ -13526,12 +13526,12 @@
       <c r="P31" s="13"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>103</v>
@@ -13540,19 +13540,19 @@
         <v>68</v>
       </c>
       <c r="D32" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H32" s="17" t="s">
         <v>435</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>436</v>
       </c>
       <c r="I32" s="13">
         <v>46477</v>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="K32" s="15"/>
       <c r="L32" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="9"/>
@@ -13574,7 +13574,7 @@
     </row>
     <row r="33" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>103</v>
@@ -13583,16 +13583,16 @@
         <v>68</v>
       </c>
       <c r="D33" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="F33" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>106</v>
@@ -13609,7 +13609,7 @@
         <v>DUE NOW</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="9"/>
@@ -13620,7 +13620,7 @@
     </row>
     <row r="34" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>103</v>
@@ -13629,16 +13629,16 @@
         <v>68</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E34" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G34" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>106</v>
@@ -13666,7 +13666,7 @@
     </row>
     <row r="35" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>108</v>
@@ -13675,19 +13675,19 @@
         <v>68</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I35" s="13">
         <v>46446</v>
@@ -13698,7 +13698,7 @@
       </c>
       <c r="K35" s="15"/>
       <c r="L35" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="9"/>
@@ -13706,12 +13706,12 @@
       <c r="P35" s="13"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>108</v>
@@ -13720,19 +13720,19 @@
         <v>68</v>
       </c>
       <c r="D36" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H36" s="17" t="s">
         <v>435</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>436</v>
       </c>
       <c r="I36" s="13">
         <v>46477</v>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="K36" s="15"/>
       <c r="L36" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="9"/>
@@ -13754,7 +13754,7 @@
     </row>
     <row r="37" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>108</v>
@@ -13763,16 +13763,16 @@
         <v>68</v>
       </c>
       <c r="D37" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="F37" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G37" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>106</v>
@@ -13789,7 +13789,7 @@
         <v>DUE NOW</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="9"/>
@@ -13800,7 +13800,7 @@
     </row>
     <row r="38" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>108</v>
@@ -13809,16 +13809,16 @@
         <v>68</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E38" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G38" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>106</v>
@@ -13846,7 +13846,7 @@
     </row>
     <row r="39" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>88</v>
@@ -13855,19 +13855,19 @@
         <v>90</v>
       </c>
       <c r="D39" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="F39" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H39" s="17" t="s">
         <v>470</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>471</v>
       </c>
       <c r="I39" s="13">
         <v>46265</v>
@@ -13881,7 +13881,7 @@
         <v/>
       </c>
       <c r="L39" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="9"/>
@@ -13892,7 +13892,7 @@
     </row>
     <row r="40" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>88</v>
@@ -13901,19 +13901,19 @@
         <v>90</v>
       </c>
       <c r="D40" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="E40" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="F40" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H40" s="17" t="s">
         <v>474</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H40" s="17" t="s">
-        <v>475</v>
       </c>
       <c r="I40" s="13">
         <v>46536</v>
@@ -13927,7 +13927,7 @@
         <v/>
       </c>
       <c r="L40" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="9"/>
@@ -13938,7 +13938,7 @@
     </row>
     <row r="41" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>88</v>
@@ -13947,19 +13947,19 @@
         <v>90</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I41" s="13">
         <v>46356</v>
@@ -13973,7 +13973,7 @@
         <v/>
       </c>
       <c r="L41" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="9"/>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="42" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>88</v>
@@ -13993,16 +13993,16 @@
         <v>90</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>106</v>
@@ -14019,7 +14019,7 @@
         <v>DUE NOW</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="9"/>
@@ -14030,7 +14030,7 @@
     </row>
     <row r="43" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>88</v>
@@ -14039,19 +14039,19 @@
         <v>68</v>
       </c>
       <c r="D43" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H43" s="17" t="s">
         <v>429</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H43" s="17" t="s">
-        <v>430</v>
       </c>
       <c r="I43" s="13">
         <v>46366</v>
@@ -14065,7 +14065,7 @@
         <v/>
       </c>
       <c r="L43" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="9"/>
@@ -14076,7 +14076,7 @@
     </row>
     <row r="44" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>88</v>
@@ -14085,16 +14085,16 @@
         <v>68</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>106</v>
@@ -14108,7 +14108,7 @@
       </c>
       <c r="K44" s="15"/>
       <c r="L44" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="9"/>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>88</v>
@@ -14128,19 +14128,19 @@
         <v>68</v>
       </c>
       <c r="D45" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H45" s="17" t="s">
         <v>435</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H45" s="17" t="s">
-        <v>436</v>
       </c>
       <c r="I45" s="13">
         <v>46477</v>
@@ -14151,7 +14151,7 @@
       </c>
       <c r="K45" s="15"/>
       <c r="L45" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M45" s="13"/>
       <c r="N45" s="9"/>
@@ -14162,7 +14162,7 @@
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>88</v>
@@ -14171,19 +14171,19 @@
         <v>68</v>
       </c>
       <c r="D46" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H46" s="17" t="s">
         <v>438</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H46" s="17" t="s">
-        <v>439</v>
       </c>
       <c r="I46" s="13">
         <v>46477</v>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="K46" s="15"/>
       <c r="L46" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M46" s="13"/>
       <c r="N46" s="9"/>
@@ -14205,7 +14205,7 @@
     </row>
     <row r="47" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>118</v>
@@ -14214,19 +14214,19 @@
         <v>120</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>120</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I47" s="13">
         <v>46295</v>
@@ -14240,7 +14240,7 @@
         <v/>
       </c>
       <c r="L47" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M47" s="13"/>
       <c r="N47" s="9"/>
@@ -14251,7 +14251,7 @@
     </row>
     <row r="48" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>118</v>
@@ -14260,19 +14260,19 @@
         <v>120</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>120</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I48" s="13">
         <v>46265</v>
@@ -14286,7 +14286,7 @@
         <v/>
       </c>
       <c r="L48" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M48" s="13"/>
       <c r="N48" s="9"/>
@@ -14755,357 +14755,357 @@
   <sheetData>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="34" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="33" t="s">
-        <v>490</v>
-      </c>
-      <c r="C5" s="33"/>
+      <c r="C5" s="34"/>
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
+        <v>491</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>492</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>494</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>496</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="C11" s="21" t="s">
         <v>498</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="22" t="s">
+        <v>499</v>
+      </c>
+      <c r="C12" s="21" t="s">
         <v>500</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>502</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="C14" s="21" t="s">
         <v>504</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>507</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="23" t="s">
+        <v>508</v>
+      </c>
+      <c r="C18" s="21" t="s">
         <v>509</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="23" t="s">
+        <v>510</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>511</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="23" t="s">
+        <v>512</v>
+      </c>
+      <c r="C20" s="21" t="s">
         <v>513</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="23" t="s">
+        <v>514</v>
+      </c>
+      <c r="C21" s="21" t="s">
         <v>515</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="23" t="s">
+        <v>516</v>
+      </c>
+      <c r="C22" s="21" t="s">
         <v>517</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="23" t="s">
+        <v>518</v>
+      </c>
+      <c r="C23" s="21" t="s">
         <v>519</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="23" t="s">
+        <v>520</v>
+      </c>
+      <c r="C24" s="21" t="s">
         <v>521</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="23" t="s">
+        <v>522</v>
+      </c>
+      <c r="C25" s="21" t="s">
         <v>523</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="32" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C28" s="32"/>
     </row>
     <row r="29" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="32" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C29" s="32"/>
     </row>
     <row r="30" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="32" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C30" s="32"/>
     </row>
     <row r="31" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="32" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C31" s="32"/>
     </row>
     <row r="32" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="32" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C32" s="32"/>
     </row>
     <row r="33" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="32" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C33" s="32"/>
     </row>
     <row r="34" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="32" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C34" s="32"/>
     </row>
     <row r="36" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="4" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="33" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="37" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="34" t="s">
+      <c r="C37" s="33"/>
+    </row>
+    <row r="38" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="33" t="s">
         <v>534</v>
       </c>
-      <c r="C37" s="34"/>
-    </row>
-    <row r="38" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="34" t="s">
+      <c r="C38" s="33"/>
+    </row>
+    <row r="39" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="33" t="s">
         <v>535</v>
       </c>
-      <c r="C38" s="34"/>
-    </row>
-    <row r="39" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="34" t="s">
+      <c r="C39" s="33"/>
+    </row>
+    <row r="40" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="33" t="s">
         <v>536</v>
       </c>
-      <c r="C39" s="34"/>
-    </row>
-    <row r="40" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="34" t="s">
+      <c r="C40" s="33"/>
+    </row>
+    <row r="41" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="33" t="s">
         <v>537</v>
       </c>
-      <c r="C40" s="34"/>
-    </row>
-    <row r="41" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="34" t="s">
+      <c r="C41" s="33"/>
+    </row>
+    <row r="42" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="33" t="s">
         <v>538</v>
       </c>
-      <c r="C41" s="34"/>
-    </row>
-    <row r="42" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="34" t="s">
+      <c r="C42" s="33"/>
+    </row>
+    <row r="43" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="33" t="s">
         <v>539</v>
       </c>
-      <c r="C42" s="34"/>
-    </row>
-    <row r="43" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="34" t="s">
+      <c r="C43" s="33"/>
+    </row>
+    <row r="44" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="33" t="s">
         <v>540</v>
       </c>
-      <c r="C43" s="34"/>
-    </row>
-    <row r="44" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="34" t="s">
+      <c r="C44" s="33"/>
+    </row>
+    <row r="45" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="33" t="s">
         <v>541</v>
       </c>
-      <c r="C44" s="34"/>
-    </row>
-    <row r="45" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="34" t="s">
+      <c r="C45" s="33"/>
+    </row>
+    <row r="46" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="33" t="s">
         <v>542</v>
       </c>
-      <c r="C45" s="34"/>
-    </row>
-    <row r="46" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="34" t="s">
+      <c r="C46" s="33"/>
+    </row>
+    <row r="47" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="33" t="s">
         <v>543</v>
       </c>
-      <c r="C46" s="34"/>
-    </row>
-    <row r="47" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="34" t="s">
+      <c r="C47" s="33"/>
+    </row>
+    <row r="48" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="33" t="s">
         <v>544</v>
       </c>
-      <c r="C47" s="34"/>
-    </row>
-    <row r="48" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="34" t="s">
+      <c r="C48" s="33"/>
+    </row>
+    <row r="49" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="33" t="s">
         <v>545</v>
       </c>
-      <c r="C48" s="34"/>
-    </row>
-    <row r="49" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="34" t="s">
+      <c r="C49" s="33"/>
+    </row>
+    <row r="50" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="33" t="s">
         <v>546</v>
       </c>
-      <c r="C49" s="34"/>
-    </row>
-    <row r="50" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="34" t="s">
+      <c r="C50" s="33"/>
+    </row>
+    <row r="51" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="33" t="s">
         <v>547</v>
       </c>
-      <c r="C50" s="34"/>
-    </row>
-    <row r="51" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="34" t="s">
+      <c r="C51" s="33"/>
+    </row>
+    <row r="52" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="33" t="s">
         <v>548</v>
       </c>
-      <c r="C51" s="34"/>
-    </row>
-    <row r="52" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="34" t="s">
+      <c r="C52" s="33"/>
+    </row>
+    <row r="53" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="33" t="s">
         <v>549</v>
       </c>
-      <c r="C52" s="34"/>
-    </row>
-    <row r="53" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="34" t="s">
+      <c r="C53" s="33"/>
+    </row>
+    <row r="54" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="33" t="s">
         <v>550</v>
       </c>
-      <c r="C53" s="34"/>
-    </row>
-    <row r="54" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="34" t="s">
+      <c r="C54" s="33"/>
+    </row>
+    <row r="55" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="33" t="s">
         <v>551</v>
       </c>
-      <c r="C54" s="34"/>
-    </row>
-    <row r="55" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="34" t="s">
+      <c r="C55" s="33"/>
+    </row>
+    <row r="56" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="33" t="s">
         <v>552</v>
       </c>
-      <c r="C55" s="34"/>
-    </row>
-    <row r="56" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="34" t="s">
-        <v>553</v>
-      </c>
-      <c r="C56" s="34"/>
+      <c r="C56" s="33"/>
     </row>
     <row r="58" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="59" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="32" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C59" s="32"/>
     </row>
     <row r="60" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="32" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C60" s="32"/>
     </row>
     <row r="61" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="32" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C61" s="32"/>
     </row>
     <row r="62" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="32" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C62" s="32"/>
     </row>
@@ -15115,12 +15115,37 @@
     </row>
     <row r="64" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="32" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C64" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
     <mergeCell ref="B61:C61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="B63:C63"/>
@@ -15130,31 +15155,6 @@
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -15176,377 +15176,377 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>563</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>564</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>565</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>130</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
+        <v>686</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>687</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>688</v>
-      </c>
       <c r="C6" s="21" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E6" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>571</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>573</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="C7" s="21" t="s">
         <v>574</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="E7" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="F7" s="21" t="s">
         <v>575</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>577</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="C8" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="F8" s="21" t="s">
         <v>578</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>568</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>223</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
+        <v>579</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>580</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="C9" s="21" t="s">
         <v>581</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="E9" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="F9" s="21" t="s">
         <v>582</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="21" t="s">
+        <v>583</v>
+      </c>
+      <c r="B10" s="21" t="s">
         <v>584</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="C10" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="E10" s="21" t="s">
         <v>585</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>575</v>
-      </c>
-      <c r="E10" s="21" t="s">
+      <c r="F10" s="21" t="s">
         <v>586</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="21" t="s">
+        <v>587</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>588</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="C11" s="21" t="s">
         <v>589</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="E11" s="21" t="s">
         <v>590</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="F11" s="21" t="s">
         <v>591</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="21" t="s">
+        <v>592</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>593</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="C12" s="21" t="s">
         <v>594</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="E12" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="F12" s="21" t="s">
         <v>595</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="21" t="s">
+        <v>596</v>
+      </c>
+      <c r="B13" s="21" t="s">
         <v>597</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="C13" s="21" t="s">
+        <v>589</v>
+      </c>
+      <c r="E13" s="21" t="s">
         <v>598</v>
       </c>
-      <c r="C13" s="21" t="s">
-        <v>590</v>
-      </c>
-      <c r="E13" s="21" t="s">
+      <c r="F13" s="21" t="s">
         <v>599</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
+        <v>600</v>
+      </c>
+      <c r="B14" s="21" t="s">
         <v>601</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="C14" s="21" t="s">
         <v>602</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
+        <v>603</v>
+      </c>
+      <c r="B15" s="21" t="s">
         <v>604</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>605</v>
-      </c>
       <c r="C15" s="21" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="21" t="s">
+        <v>605</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>606</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="C16" s="21" t="s">
         <v>607</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="21" t="s">
+        <v>608</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>609</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="C17" s="21" t="s">
         <v>610</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="21" t="s">
+        <v>611</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>612</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>613</v>
-      </c>
       <c r="C18" s="21" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="21" t="s">
+        <v>613</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>614</v>
       </c>
-      <c r="B19" s="21" t="s">
-        <v>615</v>
-      </c>
       <c r="C19" s="21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>616</v>
       </c>
-      <c r="B20" s="21" t="s">
-        <v>617</v>
-      </c>
       <c r="C20" s="21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="21" t="s">
+        <v>617</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>618</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="C21" s="21" t="s">
         <v>619</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="21" t="s">
+        <v>620</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>621</v>
       </c>
-      <c r="B22" s="21" t="s">
-        <v>622</v>
-      </c>
       <c r="C22" s="21" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="21" t="s">
+        <v>622</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>623</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>624</v>
-      </c>
       <c r="C23" s="21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="21" t="s">
+        <v>624</v>
+      </c>
+      <c r="B24" s="21" t="s">
         <v>625</v>
       </c>
-      <c r="B24" s="21" t="s">
-        <v>626</v>
-      </c>
       <c r="C24" s="21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
+        <v>626</v>
+      </c>
+      <c r="B25" s="21" t="s">
         <v>627</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="C25" s="21" t="s">
         <v>628</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="21" t="s">
+        <v>629</v>
+      </c>
+      <c r="B26" s="21" t="s">
         <v>630</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="C26" s="21" t="s">
         <v>631</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="21" t="s">
+        <v>632</v>
+      </c>
+      <c r="B27" s="21" t="s">
         <v>633</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="C27" s="21" t="s">
         <v>634</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="21" t="s">
+        <v>635</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>636</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>484</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="21" t="s">
+        <v>637</v>
+      </c>
+      <c r="B29" s="21" t="s">
         <v>638</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="C29" s="21" t="s">
         <v>639</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="21" t="s">
+        <v>640</v>
+      </c>
+      <c r="B30" s="21" t="s">
         <v>641</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="C30" s="21" t="s">
         <v>642</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="21" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>61</v>
@@ -15554,57 +15554,57 @@
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="21" t="s">
+        <v>644</v>
+      </c>
+      <c r="B32" s="21" t="s">
         <v>645</v>
       </c>
-      <c r="B32" s="21" t="s">
-        <v>646</v>
-      </c>
       <c r="C32" s="21" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="21" t="s">
+        <v>646</v>
+      </c>
+      <c r="B33" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="B33" s="21" t="s">
-        <v>648</v>
-      </c>
       <c r="C33" s="21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="21" t="s">
+        <v>648</v>
+      </c>
+      <c r="B34" s="21" t="s">
         <v>649</v>
       </c>
-      <c r="B34" s="21" t="s">
-        <v>650</v>
-      </c>
       <c r="C34" s="21" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="21" t="s">
+        <v>650</v>
+      </c>
+      <c r="B35" s="21" t="s">
         <v>651</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="C35" s="21" t="s">
         <v>652</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="21" t="s">
+        <v>653</v>
+      </c>
+      <c r="B36" s="21" t="s">
         <v>654</v>
       </c>
-      <c r="B36" s="21" t="s">
-        <v>655</v>
-      </c>
       <c r="C36" s="21" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>

--- a/registers/NEK_Master_Registers.xlsx
+++ b/registers/NEK_Master_Registers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude Cowork\NEK\registers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDE81F4-6544-4301-8EA2-37F46EE754FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAAC316-DB91-4AE6-9247-E0BEAEDE4951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2227" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2219" uniqueCount="707">
   <si>
     <t>NEK GROUP — MASTER REGISTER WORKBOOK</t>
   </si>
@@ -2096,12 +2096,6 @@
     <t>Note: a bank code identifies the BANK, not a single account — Bank of China is 'BOC' for every entity that banks there. The account is identified by the pair (Entity Code + Bank Code). If one entity ever holds two accounts at the same bank, extend the code (e.g. BOC1, BOC2).</t>
   </si>
   <si>
-    <t>Shared account with NCL (spouses) - Sha Tin rental. Same physical account as NCL|BOCOM; two entity keys, one account.</t>
-  </si>
-  <si>
-    <t>Timothy Ng</t>
-  </si>
-  <si>
     <t>Invoice issued by us (receivable)</t>
   </si>
   <si>
@@ -2166,6 +2160,12 @@
   </si>
   <si>
     <t>Sha Tin</t>
+  </si>
+  <si>
+    <t>Dormant</t>
+  </si>
+  <si>
+    <t>Non-transacting. Director of NCLCAP. Sha Tin property is booked to NCL and transacted through NCL|BOCOM (shared account, spouses), so CSK holds no bank account row of its own. Standardised 2026-07-31.</t>
   </si>
 </sst>
 </file>
@@ -2397,8 +2397,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2911,16 +2911,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
@@ -2929,6 +2919,16 @@
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2937,7 +2937,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -3305,38 +3305,18 @@
       <c r="J15" s="27"/>
       <c r="K15" s="26"/>
     </row>
-    <row r="16" spans="1:11" ht="57.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="25" t="s">
-        <v>677</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>678</v>
-      </c>
-      <c r="D16" s="25"/>
-      <c r="E16" s="26" t="s">
-        <v>666</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>667</v>
-      </c>
-      <c r="G16" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="H16" s="26" t="s">
-        <v>683</v>
-      </c>
-      <c r="I16" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="J16" s="27">
-        <v>46234</v>
-      </c>
-      <c r="K16" s="26" t="s">
-        <v>684</v>
-      </c>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="28"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="28"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="28"/>
@@ -3416,34 +3396,21 @@
       <c r="J22" s="29"/>
       <c r="K22" s="28"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="28"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A25" s="35" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" s="35" t="s">
         <v>682</v>
       </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A24:H24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4003,9 +3970,11 @@
         <v>114</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="N14" s="9"/>
+        <v>705</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>706</v>
+      </c>
       <c r="O14" s="9" t="s">
         <v>78</v>
       </c>
@@ -4653,7 +4622,7 @@
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>112</v>
@@ -11004,7 +10973,7 @@
     </row>
     <row r="5" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>355</v>
@@ -11040,12 +11009,12 @@
         <v>77</v>
       </c>
       <c r="T5" s="19" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>73</v>
@@ -11054,7 +11023,7 @@
         <v>263</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>68</v>
@@ -11081,12 +11050,12 @@
         <v>77</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>363</v>
@@ -11122,12 +11091,12 @@
         <v>77</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>288</v>
@@ -11163,12 +11132,12 @@
         <v>77</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>76</v>
@@ -11177,7 +11146,7 @@
         <v>61</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>68</v>
@@ -11204,12 +11173,12 @@
         <v>77</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>75</v>
@@ -11218,7 +11187,7 @@
         <v>260</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>68</v>
@@ -11245,12 +11214,12 @@
         <v>77</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>254</v>
@@ -11286,7 +11255,7 @@
         <v>77</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -11300,7 +11269,7 @@
         <v>243</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>68</v>
@@ -11327,7 +11296,7 @@
         <v>77</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -11341,7 +11310,7 @@
         <v>243</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>68</v>
@@ -11368,7 +11337,7 @@
         <v>77</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -11379,10 +11348,10 @@
         <v>312</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>68</v>
@@ -11409,12 +11378,12 @@
         <v>77</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>360</v>
@@ -11450,7 +11419,7 @@
         <v>77</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -11464,7 +11433,7 @@
         <v>243</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>68</v>
@@ -11491,12 +11460,12 @@
         <v>77</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>309</v>
@@ -11532,12 +11501,12 @@
         <v>77</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>297</v>
@@ -11573,12 +11542,12 @@
         <v>77</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>367</v>
@@ -11614,12 +11583,12 @@
         <v>77</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>321</v>
@@ -11655,12 +11624,12 @@
         <v>77</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>292</v>
@@ -11696,7 +11665,7 @@
         <v>77</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -14764,10 +14733,10 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="33" t="s">
         <v>489</v>
       </c>
-      <c r="C5" s="34"/>
+      <c r="C5" s="33"/>
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
@@ -14961,124 +14930,124 @@
       </c>
     </row>
     <row r="37" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="33" t="s">
+      <c r="B37" s="34" t="s">
         <v>533</v>
       </c>
-      <c r="C37" s="33"/>
+      <c r="C37" s="34"/>
     </row>
     <row r="38" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="33" t="s">
+      <c r="B38" s="34" t="s">
         <v>534</v>
       </c>
-      <c r="C38" s="33"/>
+      <c r="C38" s="34"/>
     </row>
     <row r="39" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="33" t="s">
+      <c r="B39" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="C39" s="33"/>
+      <c r="C39" s="34"/>
     </row>
     <row r="40" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="33" t="s">
+      <c r="B40" s="34" t="s">
         <v>536</v>
       </c>
-      <c r="C40" s="33"/>
+      <c r="C40" s="34"/>
     </row>
     <row r="41" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="33" t="s">
+      <c r="B41" s="34" t="s">
         <v>537</v>
       </c>
-      <c r="C41" s="33"/>
+      <c r="C41" s="34"/>
     </row>
     <row r="42" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="33" t="s">
+      <c r="B42" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="C42" s="33"/>
+      <c r="C42" s="34"/>
     </row>
     <row r="43" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="33" t="s">
+      <c r="B43" s="34" t="s">
         <v>539</v>
       </c>
-      <c r="C43" s="33"/>
+      <c r="C43" s="34"/>
     </row>
     <row r="44" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="33" t="s">
+      <c r="B44" s="34" t="s">
         <v>540</v>
       </c>
-      <c r="C44" s="33"/>
+      <c r="C44" s="34"/>
     </row>
     <row r="45" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="33" t="s">
+      <c r="B45" s="34" t="s">
         <v>541</v>
       </c>
-      <c r="C45" s="33"/>
+      <c r="C45" s="34"/>
     </row>
     <row r="46" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="33" t="s">
+      <c r="B46" s="34" t="s">
         <v>542</v>
       </c>
-      <c r="C46" s="33"/>
+      <c r="C46" s="34"/>
     </row>
     <row r="47" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="33" t="s">
+      <c r="B47" s="34" t="s">
         <v>543</v>
       </c>
-      <c r="C47" s="33"/>
+      <c r="C47" s="34"/>
     </row>
     <row r="48" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="33" t="s">
+      <c r="B48" s="34" t="s">
         <v>544</v>
       </c>
-      <c r="C48" s="33"/>
+      <c r="C48" s="34"/>
     </row>
     <row r="49" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="33" t="s">
+      <c r="B49" s="34" t="s">
         <v>545</v>
       </c>
-      <c r="C49" s="33"/>
+      <c r="C49" s="34"/>
     </row>
     <row r="50" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="33" t="s">
+      <c r="B50" s="34" t="s">
         <v>546</v>
       </c>
-      <c r="C50" s="33"/>
+      <c r="C50" s="34"/>
     </row>
     <row r="51" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="33" t="s">
+      <c r="B51" s="34" t="s">
         <v>547</v>
       </c>
-      <c r="C51" s="33"/>
+      <c r="C51" s="34"/>
     </row>
     <row r="52" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="33" t="s">
+      <c r="B52" s="34" t="s">
         <v>548</v>
       </c>
-      <c r="C52" s="33"/>
+      <c r="C52" s="34"/>
     </row>
     <row r="53" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="33" t="s">
+      <c r="B53" s="34" t="s">
         <v>549</v>
       </c>
-      <c r="C53" s="33"/>
+      <c r="C53" s="34"/>
     </row>
     <row r="54" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="33" t="s">
+      <c r="B54" s="34" t="s">
         <v>550</v>
       </c>
-      <c r="C54" s="33"/>
+      <c r="C54" s="34"/>
     </row>
     <row r="55" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="33" t="s">
+      <c r="B55" s="34" t="s">
         <v>551</v>
       </c>
-      <c r="C55" s="33"/>
+      <c r="C55" s="34"/>
     </row>
     <row r="56" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="33" t="s">
+      <c r="B56" s="34" t="s">
         <v>552</v>
       </c>
-      <c r="C56" s="33"/>
+      <c r="C56" s="34"/>
     </row>
     <row r="58" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="4" t="s">
@@ -15121,31 +15090,6 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
     <mergeCell ref="B61:C61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="B63:C63"/>
@@ -15155,6 +15099,31 @@
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -15206,7 +15175,7 @@
         <v>566</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>569</v>
@@ -15220,10 +15189,10 @@
     </row>
     <row r="6" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>567</v>

--- a/registers/NEK_Master_Registers.xlsx
+++ b/registers/NEK_Master_Registers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude Cowork\NEK\registers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAAC316-DB91-4AE6-9247-E0BEAEDE4951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34E587E-FDAE-48B6-BE8D-C3BA3A7EA494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -569,9 +569,6 @@
     <t>Bank of Communication</t>
   </si>
   <si>
-    <t>Victoria</t>
-  </si>
-  <si>
     <t>Victoria Center</t>
   </si>
   <si>
@@ -2159,13 +2156,16 @@
     <t>TNB</t>
   </si>
   <si>
-    <t>Sha Tin</t>
-  </si>
-  <si>
     <t>Dormant</t>
   </si>
   <si>
     <t>Non-transacting. Director of NCLCAP. Sha Tin property is booked to NCL and transacted through NCL|BOCOM (shared account, spouses), so CSK holds no bank account row of its own. Standardised 2026-07-31.</t>
+  </si>
+  <si>
+    <t>27-STRP</t>
+  </si>
+  <si>
+    <t>28-VC</t>
   </si>
 </sst>
 </file>
@@ -2397,8 +2397,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2911,6 +2911,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
@@ -2919,16 +2929,6 @@
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2955,71 +2955,71 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>50</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>658</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>659</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>660</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>661</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>62</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="25" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B5" s="25" t="s">
         <v>66</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D5" s="25"/>
       <c r="E5" s="26" t="s">
+        <v>665</v>
+      </c>
+      <c r="F5" s="26" t="s">
         <v>666</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>667</v>
       </c>
       <c r="G5" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>77</v>
@@ -3029,26 +3029,26 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D6" s="25"/>
       <c r="E6" s="26" t="s">
+        <v>665</v>
+      </c>
+      <c r="F6" s="26" t="s">
         <v>666</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>667</v>
       </c>
       <c r="G6" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="I6" s="25" t="s">
         <v>77</v>
@@ -3058,20 +3058,20 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>80</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="26" t="s">
+        <v>665</v>
+      </c>
+      <c r="F7" s="26" t="s">
         <v>666</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>667</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>71</v>
@@ -3085,20 +3085,20 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>84</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="26" t="s">
+        <v>665</v>
+      </c>
+      <c r="F8" s="26" t="s">
         <v>666</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>667</v>
       </c>
       <c r="G8" s="25" t="s">
         <v>71</v>
@@ -3112,26 +3112,26 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>88</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="26" t="s">
+        <v>665</v>
+      </c>
+      <c r="F9" s="26" t="s">
         <v>666</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>667</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="I9" s="25" t="s">
         <v>77</v>
@@ -3141,20 +3141,20 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="26" t="s">
+        <v>665</v>
+      </c>
+      <c r="F10" s="26" t="s">
         <v>666</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>667</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>71</v>
@@ -3168,20 +3168,20 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="25" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>99</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="26" t="s">
+        <v>665</v>
+      </c>
+      <c r="F11" s="26" t="s">
         <v>666</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>667</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>71</v>
@@ -3195,20 +3195,20 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D12" s="25"/>
       <c r="E12" s="26" t="s">
+        <v>665</v>
+      </c>
+      <c r="F12" s="26" t="s">
         <v>666</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>667</v>
       </c>
       <c r="G12" s="25" t="s">
         <v>71</v>
@@ -3222,20 +3222,20 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="25" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B13" s="25" t="s">
         <v>108</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="26" t="s">
+        <v>665</v>
+      </c>
+      <c r="F13" s="26" t="s">
         <v>666</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>667</v>
       </c>
       <c r="G13" s="25" t="s">
         <v>71</v>
@@ -3249,26 +3249,26 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>112</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="26" t="s">
+        <v>665</v>
+      </c>
+      <c r="F14" s="26" t="s">
         <v>666</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>667</v>
       </c>
       <c r="G14" s="25" t="s">
         <v>92</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="I14" s="25" t="s">
         <v>77</v>
@@ -3278,26 +3278,26 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B15" s="25" t="s">
         <v>118</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="26" t="s">
+        <v>665</v>
+      </c>
+      <c r="F15" s="26" t="s">
         <v>666</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>667</v>
       </c>
       <c r="G15" s="25" t="s">
         <v>121</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="I15" s="25" t="s">
         <v>77</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="35" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B24" s="35"/>
       <c r="C24" s="35"/>
@@ -3970,10 +3970,10 @@
         <v>114</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="O14" s="9" t="s">
         <v>78</v>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="N5" s="15">
         <f t="shared" ref="N5:N44" ca="1" si="0">IFERROR(IF(M5="","",M5-TODAY()),"")</f>
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="O5" s="15" t="str">
         <f t="shared" ref="O5:O44" ca="1" si="1">IFERROR(IF(M5="","",IF(M5-TODAY()&lt;0,"EXPIRED",IF(M5-TODAY()&lt;=90,"RENEW NOW",IF(M5-TODAY()&lt;=180,"Prepare","")))),"")</f>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="N6" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="O6" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="N7" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="O7" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="N8" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="O8" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4622,7 +4622,7 @@
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>112</v>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="N9" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="O9" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4694,13 +4694,13 @@
     </row>
     <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>174</v>
+        <v>706</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" s="9">
         <v>28</v>
@@ -4709,7 +4709,7 @@
         <v>150</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>152</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="N10" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O10" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -5873,62 +5873,62 @@
   <sheetData>
     <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>187</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>188</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="L4" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="M4" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>192</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>193</v>
       </c>
       <c r="Q4" s="8" t="s">
         <v>62</v>
@@ -5939,7 +5939,7 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>66</v>
@@ -5948,13 +5948,13 @@
         <v>113</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>197</v>
       </c>
       <c r="G5" s="13">
         <v>42856</v>
@@ -5979,13 +5979,13 @@
         <v>300</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O5" s="13">
         <v>46419</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q5" s="9" t="s">
         <v>77</v>
@@ -5994,7 +5994,7 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>66</v>
@@ -6003,13 +6003,13 @@
         <v>98</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>202</v>
-      </c>
       <c r="F6" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G6" s="13">
         <v>42856</v>
@@ -6034,13 +6034,13 @@
         <v>300</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O6" s="13">
         <v>46419</v>
       </c>
       <c r="P6" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q6" s="9" t="s">
         <v>77</v>
@@ -6049,22 +6049,22 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C7" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>207</v>
-      </c>
       <c r="F7" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G7" s="13">
         <v>42856</v>
@@ -6089,13 +6089,13 @@
         <v>300</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O7" s="13">
         <v>46419</v>
       </c>
       <c r="P7" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q7" s="9" t="s">
         <v>77</v>
@@ -6104,22 +6104,22 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>211</v>
-      </c>
       <c r="F8" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G8" s="13">
         <v>44197</v>
@@ -6144,13 +6144,13 @@
         <v>100</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O8" s="13">
         <v>46419</v>
       </c>
       <c r="P8" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q8" s="9" t="s">
         <v>77</v>
@@ -6787,68 +6787,68 @@
   <sheetData>
     <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>218</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>219</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="H4" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>229</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>230</v>
       </c>
       <c r="S4" s="8" t="s">
         <v>62</v>
@@ -6859,22 +6859,22 @@
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>71</v>
@@ -6884,25 +6884,25 @@
         <v>15287.150000000001</v>
       </c>
       <c r="I5" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K5" s="9">
         <v>27</v>
       </c>
       <c r="L5" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M5" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="N5" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="O5" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P5" s="9"/>
       <c r="Q5" s="13"/>
@@ -6914,22 +6914,22 @@
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>244</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>245</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>71</v>
@@ -6939,25 +6939,25 @@
         <v>2949</v>
       </c>
       <c r="I6" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K6" s="9">
         <v>15</v>
       </c>
       <c r="L6" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M6" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="N6" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="O6" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P6" s="9"/>
       <c r="Q6" s="13"/>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>71</v>
@@ -6994,25 +6994,25 @@
         <v>368.75</v>
       </c>
       <c r="I7" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K7" s="9">
         <v>15</v>
       </c>
       <c r="L7" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M7" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="N7" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="O7" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="13"/>
@@ -7024,22 +7024,22 @@
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E8" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>250</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>251</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>71</v>
@@ -7049,25 +7049,25 @@
         <v>411.5</v>
       </c>
       <c r="I8" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K8" s="30">
         <v>15</v>
       </c>
       <c r="L8" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M8" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="N8" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="O8" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P8" s="9"/>
       <c r="Q8" s="13"/>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>255</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>71</v>
@@ -7103,25 +7103,25 @@
         <v>2700</v>
       </c>
       <c r="I9" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K9" s="30">
         <v>10</v>
       </c>
       <c r="L9" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M9" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="N9" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="O9" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P9" s="9"/>
       <c r="Q9" s="13"/>
@@ -7133,13 +7133,13 @@
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>61</v>
@@ -7148,7 +7148,7 @@
         <v>76</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>71</v>
@@ -7157,25 +7157,25 @@
         <v>2000</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K10" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L10" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M10" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="N10" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="O10" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P10" s="9"/>
       <c r="Q10" s="13"/>
@@ -7187,22 +7187,22 @@
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>71</v>
@@ -7211,25 +7211,25 @@
         <v>2000</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K11" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L11" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M11" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="N11" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N11" s="9" t="s">
+      <c r="O11" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P11" s="9"/>
       <c r="Q11" s="13"/>
@@ -7241,22 +7241,22 @@
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>71</v>
@@ -7265,25 +7265,25 @@
         <v>1200</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K12" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L12" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M12" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="N12" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="O12" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P12" s="9"/>
       <c r="Q12" s="13"/>
@@ -7295,22 +7295,22 @@
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>71</v>
@@ -7319,25 +7319,25 @@
         <v>1200</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K13" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L13" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M13" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="N13" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="O13" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P13" s="9"/>
       <c r="Q13" s="13"/>
@@ -7349,22 +7349,22 @@
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C14" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>271</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>272</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>71</v>
@@ -7373,25 +7373,25 @@
         <v>9000</v>
       </c>
       <c r="I14" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K14" s="30">
         <v>1</v>
       </c>
       <c r="L14" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M14" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M14" s="9" t="s">
+      <c r="N14" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N14" s="9" t="s">
+      <c r="O14" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P14" s="9"/>
       <c r="Q14" s="13"/>
@@ -7403,22 +7403,22 @@
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>270</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>71</v>
@@ -7427,25 +7427,25 @@
         <v>10000</v>
       </c>
       <c r="I15" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K15" s="30">
         <v>1</v>
       </c>
       <c r="L15" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M15" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="N15" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="O15" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P15" s="9"/>
       <c r="Q15" s="13"/>
@@ -7457,22 +7457,22 @@
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>270</v>
-      </c>
       <c r="E16" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>71</v>
@@ -7481,25 +7481,25 @@
         <v>8750</v>
       </c>
       <c r="I16" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K16" s="30">
         <v>1</v>
       </c>
       <c r="L16" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M16" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="N16" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N16" s="9" t="s">
+      <c r="O16" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P16" s="9"/>
       <c r="Q16" s="13"/>
@@ -7511,22 +7511,22 @@
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>270</v>
-      </c>
       <c r="E17" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>71</v>
@@ -7535,25 +7535,25 @@
         <v>8500</v>
       </c>
       <c r="I17" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K17" s="9">
         <v>1</v>
       </c>
       <c r="L17" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M17" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="N17" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N17" s="9" t="s">
+      <c r="O17" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P17" s="9"/>
       <c r="Q17" s="13"/>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>233</v>
-      </c>
       <c r="E18" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>71</v>
@@ -7589,25 +7589,25 @@
         <v>5321.85</v>
       </c>
       <c r="I18" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K18" s="9">
         <v>27</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M18" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="N18" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N18" s="9" t="s">
+      <c r="O18" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P18" s="9"/>
       <c r="Q18" s="13"/>
@@ -7619,22 +7619,22 @@
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D19" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="F19" s="9" t="s">
         <v>244</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>245</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>71</v>
@@ -7644,25 +7644,25 @@
         <v>945</v>
       </c>
       <c r="I19" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K19" s="9">
         <v>15</v>
       </c>
       <c r="L19" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M19" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M19" s="9" t="s">
+      <c r="N19" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N19" s="9" t="s">
+      <c r="O19" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P19" s="9"/>
       <c r="Q19" s="13"/>
@@ -7674,22 +7674,22 @@
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E20" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>71</v>
@@ -7698,25 +7698,25 @@
         <v>74.400000000000006</v>
       </c>
       <c r="I20" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K20" s="9">
         <v>15</v>
       </c>
       <c r="L20" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M20" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M20" s="9" t="s">
+      <c r="N20" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N20" s="9" t="s">
+      <c r="O20" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P20" s="9"/>
       <c r="Q20" s="13"/>
@@ -7728,22 +7728,22 @@
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E21" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>250</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>251</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>71</v>
@@ -7752,25 +7752,25 @@
         <v>240.5</v>
       </c>
       <c r="I21" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K21" s="9">
         <v>15</v>
       </c>
       <c r="L21" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M21" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M21" s="9" t="s">
+      <c r="N21" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="O21" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P21" s="9"/>
       <c r="Q21" s="13"/>
@@ -7782,22 +7782,22 @@
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>71</v>
@@ -7806,25 +7806,25 @@
         <v>6500</v>
       </c>
       <c r="I22" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K22" s="9">
         <v>15</v>
       </c>
       <c r="L22" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M22" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M22" s="9" t="s">
+      <c r="N22" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N22" s="9" t="s">
+      <c r="O22" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O22" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P22" s="9"/>
       <c r="Q22" s="13"/>
@@ -7836,22 +7836,22 @@
     </row>
     <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E23" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>288</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>289</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>71</v>
@@ -7860,25 +7860,25 @@
         <v>1017.6</v>
       </c>
       <c r="I23" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K23" s="9">
         <v>7</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M23" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="N23" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N23" s="9" t="s">
+      <c r="O23" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P23" s="9"/>
       <c r="Q23" s="13"/>
@@ -7890,49 +7890,49 @@
     </row>
     <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="F24" s="9" t="s">
         <v>292</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>293</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I24" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K24" s="9">
         <v>15</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M24" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="N24" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N24" s="9" t="s">
+      <c r="O24" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P24" s="9"/>
       <c r="Q24" s="13"/>
@@ -7944,22 +7944,22 @@
     </row>
     <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D25" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="F25" s="9" t="s">
         <v>297</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>298</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>71</v>
@@ -7968,25 +7968,25 @@
         <v>1296.58</v>
       </c>
       <c r="I25" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K25" s="9">
         <v>15</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M25" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="N25" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N25" s="9" t="s">
+      <c r="O25" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P25" s="9"/>
       <c r="Q25" s="13"/>
@@ -7998,22 +7998,22 @@
     </row>
     <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D26" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>297</v>
-      </c>
       <c r="F26" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>71</v>
@@ -8022,25 +8022,25 @@
         <v>1296.58</v>
       </c>
       <c r="I26" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K26" s="9">
         <v>15</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M26" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="N26" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N26" s="9" t="s">
+      <c r="O26" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O26" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P26" s="9"/>
       <c r="Q26" s="13"/>
@@ -8052,22 +8052,22 @@
     </row>
     <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D27" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>297</v>
-      </c>
       <c r="F27" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>71</v>
@@ -8076,25 +8076,25 @@
         <v>1296.58</v>
       </c>
       <c r="I27" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K27" s="9">
         <v>15</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M27" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="N27" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N27" s="9" t="s">
+      <c r="O27" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P27" s="9"/>
       <c r="Q27" s="13"/>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D28" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E28" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>297</v>
-      </c>
       <c r="F28" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>71</v>
@@ -8130,25 +8130,25 @@
         <v>1296.58</v>
       </c>
       <c r="I28" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J28" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K28" s="30">
         <v>15</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M28" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="N28" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N28" s="9" t="s">
+      <c r="O28" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O28" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P28" s="9"/>
       <c r="Q28" s="13"/>
@@ -8160,22 +8160,22 @@
     </row>
     <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D29" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>297</v>
-      </c>
       <c r="F29" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>71</v>
@@ -8184,25 +8184,25 @@
         <v>968.82</v>
       </c>
       <c r="I29" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K29" s="30">
         <v>15</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M29" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="N29" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N29" s="9" t="s">
+      <c r="O29" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P29" s="9"/>
       <c r="Q29" s="13"/>
@@ -8214,22 +8214,22 @@
     </row>
     <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D30" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="F30" s="9" t="s">
         <v>309</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>310</v>
       </c>
       <c r="G30" s="9" t="s">
         <v>71</v>
@@ -8239,25 +8239,25 @@
         <v>695</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K30" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M30" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="N30" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N30" s="9" t="s">
+      <c r="O30" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O30" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P30" s="9"/>
       <c r="Q30" s="13"/>
@@ -8269,22 +8269,22 @@
     </row>
     <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E31" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="F31" s="9" t="s">
         <v>312</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>313</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>71</v>
@@ -8294,25 +8294,25 @@
         <v>5041.2</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J31" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="K31" s="30" t="s">
         <v>314</v>
       </c>
-      <c r="K31" s="30" t="s">
-        <v>315</v>
-      </c>
       <c r="L31" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M31" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="N31" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N31" s="9" t="s">
+      <c r="O31" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O31" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P31" s="9"/>
       <c r="Q31" s="13"/>
@@ -8324,13 +8324,13 @@
     </row>
     <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>61</v>
@@ -8339,7 +8339,7 @@
         <v>76</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G32" s="9" t="s">
         <v>71</v>
@@ -8348,25 +8348,25 @@
         <v>2000</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K32" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L32" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M32" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M32" s="9" t="s">
+      <c r="N32" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N32" s="9" t="s">
+      <c r="O32" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O32" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P32" s="9"/>
       <c r="Q32" s="13"/>
@@ -8378,22 +8378,22 @@
     </row>
     <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>71</v>
@@ -8402,25 +8402,25 @@
         <v>2000</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K33" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L33" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M33" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M33" s="9" t="s">
+      <c r="N33" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N33" s="9" t="s">
+      <c r="O33" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O33" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P33" s="9"/>
       <c r="Q33" s="13"/>
@@ -8432,22 +8432,22 @@
     </row>
     <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G34" s="9" t="s">
         <v>71</v>
@@ -8456,25 +8456,25 @@
         <v>1200</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K34" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L34" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M34" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M34" s="9" t="s">
+      <c r="N34" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N34" s="9" t="s">
+      <c r="O34" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O34" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P34" s="9"/>
       <c r="Q34" s="13"/>
@@ -8486,22 +8486,22 @@
     </row>
     <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G35" s="9" t="s">
         <v>71</v>
@@ -8510,25 +8510,25 @@
         <v>1200</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K35" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L35" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M35" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M35" s="9" t="s">
+      <c r="N35" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N35" s="9" t="s">
+      <c r="O35" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P35" s="9"/>
       <c r="Q35" s="13"/>
@@ -8540,22 +8540,22 @@
     </row>
     <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E36" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="F36" s="9" t="s">
         <v>321</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>322</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>71</v>
@@ -8564,25 +8564,25 @@
         <v>104.95</v>
       </c>
       <c r="I36" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J36" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K36" s="30">
         <v>27</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N36" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O36" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O36" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P36" s="9"/>
       <c r="Q36" s="13"/>
@@ -8594,22 +8594,22 @@
     </row>
     <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D37" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="F37" s="9" t="s">
         <v>325</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>326</v>
       </c>
       <c r="G37" s="9" t="s">
         <v>71</v>
@@ -8618,25 +8618,25 @@
         <v>240</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K37" s="31" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N37" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O37" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P37" s="9"/>
       <c r="Q37" s="13"/>
@@ -8648,13 +8648,13 @@
     </row>
     <row r="38" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>61</v>
@@ -8663,7 +8663,7 @@
         <v>76</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>71</v>
@@ -8672,25 +8672,25 @@
         <v>2000</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K38" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N38" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O38" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O38" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P38" s="9"/>
       <c r="Q38" s="13"/>
@@ -8702,22 +8702,22 @@
     </row>
     <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>71</v>
@@ -8726,25 +8726,25 @@
         <v>2000</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K39" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N39" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O39" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O39" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P39" s="9"/>
       <c r="Q39" s="13"/>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>71</v>
@@ -8780,25 +8780,25 @@
         <v>1200</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K40" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N40" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O40" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O40" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P40" s="9"/>
       <c r="Q40" s="13"/>
@@ -8810,22 +8810,22 @@
     </row>
     <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>71</v>
@@ -8834,25 +8834,25 @@
         <v>1200</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K41" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L41" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N41" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O41" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O41" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P41" s="9"/>
       <c r="Q41" s="13"/>
@@ -8864,13 +8864,13 @@
     </row>
     <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>61</v>
@@ -8879,7 +8879,7 @@
         <v>76</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>71</v>
@@ -8888,25 +8888,25 @@
         <v>2000</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K42" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N42" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O42" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O42" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P42" s="9"/>
       <c r="Q42" s="13"/>
@@ -8918,22 +8918,22 @@
     </row>
     <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>71</v>
@@ -8942,25 +8942,25 @@
         <v>2000</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K43" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L43" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N43" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O43" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P43" s="9"/>
       <c r="Q43" s="13"/>
@@ -8972,22 +8972,22 @@
     </row>
     <row r="44" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G44" s="9" t="s">
         <v>71</v>
@@ -8996,25 +8996,25 @@
         <v>1200</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K44" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N44" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O44" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O44" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P44" s="9"/>
       <c r="Q44" s="13"/>
@@ -9026,22 +9026,22 @@
     </row>
     <row r="45" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>71</v>
@@ -9050,25 +9050,25 @@
         <v>1200</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K45" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N45" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O45" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O45" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P45" s="9"/>
       <c r="Q45" s="13"/>
@@ -9080,13 +9080,13 @@
     </row>
     <row r="46" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>61</v>
@@ -9095,7 +9095,7 @@
         <v>76</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>71</v>
@@ -9104,25 +9104,25 @@
         <v>2000</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K46" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L46" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="N46" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O46" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O46" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P46" s="9"/>
       <c r="Q46" s="13"/>
@@ -9134,22 +9134,22 @@
     </row>
     <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G47" s="9" t="s">
         <v>71</v>
@@ -9158,25 +9158,25 @@
         <v>2000</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K47" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="N47" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O47" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O47" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P47" s="9"/>
       <c r="Q47" s="13"/>
@@ -9188,22 +9188,22 @@
     </row>
     <row r="48" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G48" s="9" t="s">
         <v>71</v>
@@ -9212,25 +9212,25 @@
         <v>1200</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K48" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="N48" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O48" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O48" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P48" s="9"/>
       <c r="Q48" s="13"/>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="49" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G49" s="9" t="s">
         <v>71</v>
@@ -9266,25 +9266,25 @@
         <v>1200</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K49" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="N49" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O49" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O49" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P49" s="9"/>
       <c r="Q49" s="13"/>
@@ -9296,13 +9296,13 @@
     </row>
     <row r="50" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>61</v>
@@ -9311,7 +9311,7 @@
         <v>76</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G50" s="9" t="s">
         <v>71</v>
@@ -9320,25 +9320,25 @@
         <v>2000</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K50" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L50" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M50" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M50" s="9" t="s">
+      <c r="N50" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N50" s="9" t="s">
+      <c r="O50" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O50" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P50" s="9"/>
       <c r="Q50" s="13"/>
@@ -9350,22 +9350,22 @@
     </row>
     <row r="51" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G51" s="9" t="s">
         <v>71</v>
@@ -9374,25 +9374,25 @@
         <v>2000</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K51" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L51" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M51" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M51" s="9" t="s">
+      <c r="N51" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N51" s="9" t="s">
+      <c r="O51" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O51" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P51" s="9"/>
       <c r="Q51" s="13"/>
@@ -9404,22 +9404,22 @@
     </row>
     <row r="52" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>71</v>
@@ -9428,25 +9428,25 @@
         <v>1200</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K52" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L52" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M52" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M52" s="9" t="s">
+      <c r="N52" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N52" s="9" t="s">
+      <c r="O52" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O52" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P52" s="9"/>
       <c r="Q52" s="13"/>
@@ -9458,22 +9458,22 @@
     </row>
     <row r="53" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>71</v>
@@ -9482,25 +9482,25 @@
         <v>1200</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K53" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L53" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M53" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="M53" s="9" t="s">
+      <c r="N53" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="N53" s="9" t="s">
+      <c r="O53" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O53" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P53" s="9"/>
       <c r="Q53" s="13"/>
@@ -9512,13 +9512,13 @@
     </row>
     <row r="54" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>61</v>
@@ -9527,7 +9527,7 @@
         <v>76</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>71</v>
@@ -9536,25 +9536,25 @@
         <v>2000</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K54" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N54" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O54" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O54" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P54" s="9"/>
       <c r="Q54" s="13"/>
@@ -9566,22 +9566,22 @@
     </row>
     <row r="55" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>71</v>
@@ -9590,25 +9590,25 @@
         <v>2000</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K55" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N55" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O55" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O55" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P55" s="9"/>
       <c r="Q55" s="13"/>
@@ -9620,22 +9620,22 @@
     </row>
     <row r="56" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>71</v>
@@ -9644,25 +9644,25 @@
         <v>1200</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K56" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N56" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O56" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O56" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P56" s="9"/>
       <c r="Q56" s="13"/>
@@ -9674,22 +9674,22 @@
     </row>
     <row r="57" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>71</v>
@@ -9698,25 +9698,25 @@
         <v>1200</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K57" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L57" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N57" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O57" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O57" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P57" s="9"/>
       <c r="Q57" s="13"/>
@@ -9728,13 +9728,13 @@
     </row>
     <row r="58" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>61</v>
@@ -9743,7 +9743,7 @@
         <v>76</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>71</v>
@@ -9752,25 +9752,25 @@
         <v>2000</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K58" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L58" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N58" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O58" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O58" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P58" s="9"/>
       <c r="Q58" s="13"/>
@@ -9782,22 +9782,22 @@
     </row>
     <row r="59" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>71</v>
@@ -9806,25 +9806,25 @@
         <v>2000</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K59" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L59" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N59" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O59" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O59" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P59" s="9"/>
       <c r="Q59" s="13"/>
@@ -9836,22 +9836,22 @@
     </row>
     <row r="60" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>71</v>
@@ -9860,25 +9860,25 @@
         <v>1200</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K60" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L60" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N60" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O60" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O60" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P60" s="9"/>
       <c r="Q60" s="13"/>
@@ -9890,22 +9890,22 @@
     </row>
     <row r="61" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>71</v>
@@ -9914,25 +9914,25 @@
         <v>1200</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K61" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L61" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N61" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O61" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="O61" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="P61" s="9"/>
       <c r="Q61" s="13"/>
@@ -9944,22 +9944,22 @@
     </row>
     <row r="62" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D62" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="E62" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E62" s="9" t="s">
+      <c r="F62" s="9" t="s">
         <v>355</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>356</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>92</v>
@@ -9969,25 +9969,25 @@
         <v>3280</v>
       </c>
       <c r="I62" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J62" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J62" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K62" s="9">
         <v>15</v>
       </c>
       <c r="L62" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M62" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N62" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O62" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P62" s="9"/>
       <c r="Q62" s="13"/>
@@ -9999,22 +9999,22 @@
     </row>
     <row r="63" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D63" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="E63" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="E63" s="9" t="s">
+      <c r="F63" s="9" t="s">
         <v>360</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>361</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>92</v>
@@ -10023,25 +10023,25 @@
         <v>1862</v>
       </c>
       <c r="I63" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J63" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J63" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K63" s="9">
         <v>15</v>
       </c>
       <c r="L63" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P63" s="9"/>
       <c r="Q63" s="13"/>
@@ -10053,22 +10053,22 @@
     </row>
     <row r="64" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E64" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="F64" s="9" t="s">
         <v>363</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>364</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>92</v>
@@ -10077,25 +10077,25 @@
         <v>2136</v>
       </c>
       <c r="I64" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J64" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J64" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K64" s="9">
         <v>15</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M64" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N64" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O64" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P64" s="9"/>
       <c r="Q64" s="13"/>
@@ -10107,22 +10107,22 @@
     </row>
     <row r="65" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D65" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="E65" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="F65" s="9" t="s">
         <v>367</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>368</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>92</v>
@@ -10132,25 +10132,25 @@
         <v>8946</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K65" s="9">
         <v>15</v>
       </c>
       <c r="L65" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P65" s="9"/>
       <c r="Q65" s="13"/>
@@ -10162,22 +10162,22 @@
     </row>
     <row r="66" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C66" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D66" s="9" t="s">
         <v>269</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>270</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>169</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G66" s="9" t="s">
         <v>92</v>
@@ -10186,25 +10186,25 @@
         <v>25000</v>
       </c>
       <c r="I66" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J66" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J66" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K66" s="30">
         <v>15</v>
       </c>
       <c r="L66" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M66" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N66" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O66" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P66" s="9"/>
       <c r="Q66" s="13"/>
@@ -10216,22 +10216,22 @@
     </row>
     <row r="67" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C67" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D67" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="D67" s="9" t="s">
-        <v>270</v>
-      </c>
       <c r="E67" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G67" s="9" t="s">
         <v>92</v>
@@ -10240,25 +10240,25 @@
         <v>41000</v>
       </c>
       <c r="I67" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J67" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J67" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="K67" s="30">
         <v>15</v>
       </c>
       <c r="L67" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M67" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P67" s="9"/>
       <c r="Q67" s="13"/>
@@ -10270,22 +10270,22 @@
     </row>
     <row r="68" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>118</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D68" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="E68" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="E68" s="9" t="s">
+      <c r="F68" s="9" t="s">
         <v>375</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>376</v>
       </c>
       <c r="G68" s="9" t="s">
         <v>121</v>
@@ -10294,25 +10294,25 @@
         <v>2377</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K68" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L68" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M68" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N68" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O68" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P68" s="9"/>
       <c r="Q68" s="13"/>
@@ -10324,22 +10324,22 @@
     </row>
     <row r="69" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>118</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D69" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="F69" s="9" t="s">
         <v>379</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>380</v>
       </c>
       <c r="G69" s="9" t="s">
         <v>121</v>
@@ -10348,25 +10348,25 @@
         <v>220</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K69" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L69" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M69" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P69" s="9"/>
       <c r="Q69" s="13"/>
@@ -10901,68 +10901,68 @@
   <sheetData>
     <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>385</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>386</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>388</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>389</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="K4" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>396</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>397</v>
       </c>
       <c r="S4" s="8" t="s">
         <v>62</v>
@@ -10973,13 +10973,13 @@
     </row>
     <row r="5" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>112</v>
@@ -11009,21 +11009,21 @@
         <v>77</v>
       </c>
       <c r="T5" s="19" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>73</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>68</v>
@@ -11050,18 +11050,18 @@
         <v>77</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>112</v>
@@ -11091,18 +11091,18 @@
         <v>77</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>88</v>
@@ -11132,12 +11132,12 @@
         <v>77</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>76</v>
@@ -11146,7 +11146,7 @@
         <v>61</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>68</v>
@@ -11173,21 +11173,21 @@
         <v>77</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>68</v>
@@ -11214,18 +11214,18 @@
         <v>77</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>66</v>
@@ -11255,21 +11255,21 @@
         <v>77</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>68</v>
@@ -11296,21 +11296,21 @@
         <v>77</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>68</v>
@@ -11337,21 +11337,21 @@
         <v>77</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C14" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>696</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>697</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>68</v>
@@ -11378,18 +11378,18 @@
         <v>77</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>112</v>
@@ -11419,21 +11419,21 @@
         <v>77</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>68</v>
@@ -11460,18 +11460,18 @@
         <v>77</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>88</v>
@@ -11501,18 +11501,18 @@
         <v>77</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>88</v>
@@ -11542,18 +11542,18 @@
         <v>77</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>112</v>
@@ -11583,18 +11583,18 @@
         <v>77</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>84</v>
@@ -11624,18 +11624,18 @@
         <v>77</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>88</v>
@@ -11665,7 +11665,7 @@
         <v>77</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -12229,65 +12229,65 @@
   <sheetData>
     <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>214</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>215</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>52</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>411</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>412</v>
       </c>
       <c r="R4" s="8" t="s">
         <v>63</v>
@@ -12295,7 +12295,7 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>66</v>
@@ -12304,33 +12304,33 @@
         <v>68</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>415</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>416</v>
       </c>
       <c r="I5" s="13">
         <v>46249</v>
       </c>
       <c r="J5" s="15">
         <f t="shared" ref="J5:J36" ca="1" si="0">IFERROR(IF(I5="","",I5-TODAY()),"")</f>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K5" s="15" t="str">
         <f t="shared" ref="K5:K10" ca="1" si="1">IFERROR(IF(I5="","",IF(I5-TODAY()&lt;0,"OVERDUE",IF(I5-TODAY()&lt;=14,"DUE NOW",IF(I5-TODAY()&lt;=30,"Prepare","")))),"")</f>
-        <v>Prepare</v>
+        <v>DUE NOW</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M5" s="13"/>
       <c r="N5" s="9"/>
@@ -12341,7 +12341,7 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>66</v>
@@ -12350,33 +12350,33 @@
         <v>68</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>419</v>
-      </c>
       <c r="F6" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I6" s="13">
         <v>46249</v>
       </c>
       <c r="J6" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K6" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Prepare</v>
+        <v>DUE NOW</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M6" s="13"/>
       <c r="N6" s="9"/>
@@ -12387,7 +12387,7 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>66</v>
@@ -12396,33 +12396,33 @@
         <v>68</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I7" s="13">
         <v>46249</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K7" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Prepare</v>
+        <v>DUE NOW</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="9"/>
@@ -12433,7 +12433,7 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>66</v>
@@ -12442,16 +12442,16 @@
         <v>68</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>106</v>
@@ -12461,14 +12461,14 @@
       </c>
       <c r="J8" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K8" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M8" s="13"/>
       <c r="N8" s="9"/>
@@ -12479,7 +12479,7 @@
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>66</v>
@@ -12488,16 +12488,16 @@
         <v>68</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E9" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>106</v>
@@ -12507,11 +12507,11 @@
       </c>
       <c r="J9" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K9" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>61</v>
@@ -12525,7 +12525,7 @@
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>66</v>
@@ -12534,33 +12534,33 @@
         <v>68</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>428</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>429</v>
       </c>
       <c r="I10" s="13">
         <v>46366</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K10" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
       <c r="L10" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="9"/>
@@ -12571,7 +12571,7 @@
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>66</v>
@@ -12580,16 +12580,16 @@
         <v>68</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>106</v>
@@ -12599,11 +12599,11 @@
       </c>
       <c r="J11" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K11" s="15"/>
       <c r="L11" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="9"/>
@@ -12614,7 +12614,7 @@
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>66</v>
@@ -12623,30 +12623,30 @@
         <v>68</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H12" s="17" t="s">
         <v>434</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>435</v>
       </c>
       <c r="I12" s="13">
         <v>46477</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K12" s="15"/>
       <c r="L12" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M12" s="13"/>
       <c r="N12" s="9"/>
@@ -12657,7 +12657,7 @@
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>66</v>
@@ -12666,30 +12666,30 @@
         <v>68</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H13" s="17" t="s">
         <v>437</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>438</v>
       </c>
       <c r="I13" s="13">
         <v>46477</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K13" s="15"/>
       <c r="L13" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M13" s="13"/>
       <c r="N13" s="9"/>
@@ -12700,7 +12700,7 @@
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>84</v>
@@ -12709,16 +12709,16 @@
         <v>68</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>70</v>
@@ -12728,11 +12728,11 @@
       </c>
       <c r="J14" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K14" s="15"/>
       <c r="L14" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M14" s="13"/>
       <c r="N14" s="9"/>
@@ -12743,7 +12743,7 @@
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>84</v>
@@ -12752,16 +12752,16 @@
         <v>68</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>106</v>
@@ -12771,11 +12771,11 @@
       </c>
       <c r="J15" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K15" s="15"/>
       <c r="L15" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="9"/>
@@ -12786,7 +12786,7 @@
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>84</v>
@@ -12795,30 +12795,30 @@
         <v>68</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H16" s="17" t="s">
         <v>434</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>435</v>
       </c>
       <c r="I16" s="13">
         <v>46477</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K16" s="15"/>
       <c r="L16" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="9"/>
@@ -12829,7 +12829,7 @@
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>84</v>
@@ -12838,16 +12838,16 @@
         <v>68</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G17" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>106</v>
@@ -12857,14 +12857,14 @@
       </c>
       <c r="J17" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K17" s="15" t="str">
         <f ca="1">IFERROR(IF(I17="","",IF(I17-TODAY()&lt;0,"OVERDUE",IF(I17-TODAY()&lt;=14,"DUE NOW",IF(I17-TODAY()&lt;=30,"Prepare","")))),"")</f>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="9"/>
@@ -12875,7 +12875,7 @@
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>84</v>
@@ -12884,16 +12884,16 @@
         <v>68</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E18" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G18" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>106</v>
@@ -12903,11 +12903,11 @@
       </c>
       <c r="J18" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K18" s="15" t="str">
         <f ca="1">IFERROR(IF(I18="","",IF(I18-TODAY()&lt;0,"OVERDUE",IF(I18-TODAY()&lt;=14,"DUE NOW",IF(I18-TODAY()&lt;=30,"Prepare","")))),"")</f>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L18" s="9" t="s">
         <v>61</v>
@@ -12921,7 +12921,7 @@
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>95</v>
@@ -12930,16 +12930,16 @@
         <v>68</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>106</v>
@@ -12949,11 +12949,11 @@
       </c>
       <c r="J19" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K19" s="15"/>
       <c r="L19" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M19" s="13"/>
       <c r="N19" s="9"/>
@@ -12964,7 +12964,7 @@
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>95</v>
@@ -12973,30 +12973,30 @@
         <v>68</v>
       </c>
       <c r="D20" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H20" s="17" t="s">
         <v>434</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>435</v>
       </c>
       <c r="I20" s="13">
         <v>46477</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K20" s="15"/>
       <c r="L20" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M20" s="13"/>
       <c r="N20" s="9"/>
@@ -13007,7 +13007,7 @@
     </row>
     <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>95</v>
@@ -13016,16 +13016,16 @@
         <v>68</v>
       </c>
       <c r="D21" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>106</v>
@@ -13035,14 +13035,14 @@
       </c>
       <c r="J21" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K21" s="15" t="str">
         <f ca="1">IFERROR(IF(I21="","",IF(I21-TODAY()&lt;0,"OVERDUE",IF(I21-TODAY()&lt;=14,"DUE NOW",IF(I21-TODAY()&lt;=30,"Prepare","")))),"")</f>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="9"/>
@@ -13053,7 +13053,7 @@
     </row>
     <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>95</v>
@@ -13062,16 +13062,16 @@
         <v>68</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E22" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G22" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>106</v>
@@ -13081,11 +13081,11 @@
       </c>
       <c r="J22" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K22" s="15" t="str">
         <f ca="1">IFERROR(IF(I22="","",IF(I22-TODAY()&lt;0,"OVERDUE",IF(I22-TODAY()&lt;=14,"DUE NOW",IF(I22-TODAY()&lt;=30,"Prepare","")))),"")</f>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>61</v>
@@ -13099,7 +13099,7 @@
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>99</v>
@@ -13108,16 +13108,16 @@
         <v>68</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>106</v>
@@ -13127,11 +13127,11 @@
       </c>
       <c r="J23" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K23" s="15"/>
       <c r="L23" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M23" s="13"/>
       <c r="N23" s="9"/>
@@ -13142,7 +13142,7 @@
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>99</v>
@@ -13151,30 +13151,30 @@
         <v>68</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H24" s="17" t="s">
         <v>434</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H24" s="17" t="s">
-        <v>435</v>
       </c>
       <c r="I24" s="13">
         <v>46477</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K24" s="15"/>
       <c r="L24" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M24" s="13"/>
       <c r="N24" s="9"/>
@@ -13185,7 +13185,7 @@
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>99</v>
@@ -13194,16 +13194,16 @@
         <v>68</v>
       </c>
       <c r="D25" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="F25" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G25" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>106</v>
@@ -13213,14 +13213,14 @@
       </c>
       <c r="J25" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K25" s="15" t="str">
         <f ca="1">IFERROR(IF(I25="","",IF(I25-TODAY()&lt;0,"OVERDUE",IF(I25-TODAY()&lt;=14,"DUE NOW",IF(I25-TODAY()&lt;=30,"Prepare","")))),"")</f>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M25" s="13"/>
       <c r="N25" s="9"/>
@@ -13231,7 +13231,7 @@
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>99</v>
@@ -13240,16 +13240,16 @@
         <v>68</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E26" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G26" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>106</v>
@@ -13259,11 +13259,11 @@
       </c>
       <c r="J26" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K26" s="15" t="str">
         <f ca="1">IFERROR(IF(I26="","",IF(I26-TODAY()&lt;0,"OVERDUE",IF(I26-TODAY()&lt;=14,"DUE NOW",IF(I26-TODAY()&lt;=30,"Prepare","")))),"")</f>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L26" s="9" t="s">
         <v>61</v>
@@ -13277,7 +13277,7 @@
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>80</v>
@@ -13286,16 +13286,16 @@
         <v>68</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>106</v>
@@ -13305,11 +13305,11 @@
       </c>
       <c r="J27" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K27" s="15"/>
       <c r="L27" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="9"/>
@@ -13320,7 +13320,7 @@
     </row>
     <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>80</v>
@@ -13329,30 +13329,30 @@
         <v>68</v>
       </c>
       <c r="D28" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H28" s="17" t="s">
         <v>434</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>435</v>
       </c>
       <c r="I28" s="13">
         <v>46477</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K28" s="15"/>
       <c r="L28" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="9"/>
@@ -13363,7 +13363,7 @@
     </row>
     <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>80</v>
@@ -13372,16 +13372,16 @@
         <v>68</v>
       </c>
       <c r="D29" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="F29" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G29" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>106</v>
@@ -13391,14 +13391,14 @@
       </c>
       <c r="J29" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K29" s="15" t="str">
         <f ca="1">IFERROR(IF(I29="","",IF(I29-TODAY()&lt;0,"OVERDUE",IF(I29-TODAY()&lt;=14,"DUE NOW",IF(I29-TODAY()&lt;=30,"Prepare","")))),"")</f>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="9"/>
@@ -13409,7 +13409,7 @@
     </row>
     <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>80</v>
@@ -13418,16 +13418,16 @@
         <v>68</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E30" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G30" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>106</v>
@@ -13437,11 +13437,11 @@
       </c>
       <c r="J30" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K30" s="15" t="str">
         <f ca="1">IFERROR(IF(I30="","",IF(I30-TODAY()&lt;0,"OVERDUE",IF(I30-TODAY()&lt;=14,"DUE NOW",IF(I30-TODAY()&lt;=30,"Prepare","")))),"")</f>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L30" s="9" t="s">
         <v>61</v>
@@ -13455,7 +13455,7 @@
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>103</v>
@@ -13464,30 +13464,30 @@
         <v>68</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I31" s="13">
         <v>46446</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K31" s="15"/>
       <c r="L31" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="9"/>
@@ -13495,12 +13495,12 @@
       <c r="P31" s="13"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>103</v>
@@ -13509,30 +13509,30 @@
         <v>68</v>
       </c>
       <c r="D32" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H32" s="17" t="s">
         <v>434</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>435</v>
       </c>
       <c r="I32" s="13">
         <v>46477</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K32" s="15"/>
       <c r="L32" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="9"/>
@@ -13543,7 +13543,7 @@
     </row>
     <row r="33" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>103</v>
@@ -13552,16 +13552,16 @@
         <v>68</v>
       </c>
       <c r="D33" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="F33" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>106</v>
@@ -13571,14 +13571,14 @@
       </c>
       <c r="J33" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K33" s="15" t="str">
         <f ca="1">IFERROR(IF(I33="","",IF(I33-TODAY()&lt;0,"OVERDUE",IF(I33-TODAY()&lt;=14,"DUE NOW",IF(I33-TODAY()&lt;=30,"Prepare","")))),"")</f>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="9"/>
@@ -13589,7 +13589,7 @@
     </row>
     <row r="34" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>103</v>
@@ -13598,16 +13598,16 @@
         <v>68</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E34" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G34" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>106</v>
@@ -13617,11 +13617,11 @@
       </c>
       <c r="J34" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K34" s="15" t="str">
         <f ca="1">IFERROR(IF(I34="","",IF(I34-TODAY()&lt;0,"OVERDUE",IF(I34-TODAY()&lt;=14,"DUE NOW",IF(I34-TODAY()&lt;=30,"Prepare","")))),"")</f>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L34" s="9" t="s">
         <v>61</v>
@@ -13635,7 +13635,7 @@
     </row>
     <row r="35" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>108</v>
@@ -13644,30 +13644,30 @@
         <v>68</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I35" s="13">
         <v>46446</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K35" s="15"/>
       <c r="L35" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="9"/>
@@ -13675,12 +13675,12 @@
       <c r="P35" s="13"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>108</v>
@@ -13689,30 +13689,30 @@
         <v>68</v>
       </c>
       <c r="D36" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H36" s="17" t="s">
         <v>434</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>435</v>
       </c>
       <c r="I36" s="13">
         <v>46477</v>
       </c>
       <c r="J36" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K36" s="15"/>
       <c r="L36" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="9"/>
@@ -13723,7 +13723,7 @@
     </row>
     <row r="37" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>108</v>
@@ -13732,16 +13732,16 @@
         <v>68</v>
       </c>
       <c r="D37" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="F37" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G37" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>106</v>
@@ -13751,14 +13751,14 @@
       </c>
       <c r="J37" s="15">
         <f t="shared" ref="J37:J65" ca="1" si="2">IFERROR(IF(I37="","",I37-TODAY()),"")</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K37" s="15" t="str">
         <f t="shared" ref="K37:K43" ca="1" si="3">IFERROR(IF(I37="","",IF(I37-TODAY()&lt;0,"OVERDUE",IF(I37-TODAY()&lt;=14,"DUE NOW",IF(I37-TODAY()&lt;=30,"Prepare","")))),"")</f>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="9"/>
@@ -13769,7 +13769,7 @@
     </row>
     <row r="38" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>108</v>
@@ -13778,16 +13778,16 @@
         <v>68</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E38" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G38" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>106</v>
@@ -13797,11 +13797,11 @@
       </c>
       <c r="J38" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K38" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L38" s="9" t="s">
         <v>61</v>
@@ -13815,7 +13815,7 @@
     </row>
     <row r="39" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>88</v>
@@ -13824,33 +13824,33 @@
         <v>90</v>
       </c>
       <c r="D39" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="F39" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H39" s="17" t="s">
         <v>469</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>470</v>
       </c>
       <c r="I39" s="13">
         <v>46265</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K39" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
+        <v>Prepare</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="9"/>
@@ -13861,7 +13861,7 @@
     </row>
     <row r="40" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>88</v>
@@ -13870,33 +13870,33 @@
         <v>90</v>
       </c>
       <c r="D40" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="E40" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="F40" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H40" s="17" t="s">
         <v>473</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H40" s="17" t="s">
-        <v>474</v>
       </c>
       <c r="I40" s="13">
         <v>46536</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="K40" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="L40" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="9"/>
@@ -13907,7 +13907,7 @@
     </row>
     <row r="41" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>88</v>
@@ -13916,33 +13916,33 @@
         <v>90</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I41" s="13">
         <v>46356</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="K41" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="L41" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="9"/>
@@ -13953,7 +13953,7 @@
     </row>
     <row r="42" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>88</v>
@@ -13962,16 +13962,16 @@
         <v>90</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>106</v>
@@ -13981,14 +13981,14 @@
       </c>
       <c r="J42" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K42" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>DUE NOW</v>
+        <v>OVERDUE</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="9"/>
@@ -13999,7 +13999,7 @@
     </row>
     <row r="43" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>88</v>
@@ -14008,33 +14008,33 @@
         <v>68</v>
       </c>
       <c r="D43" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H43" s="17" t="s">
         <v>428</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H43" s="17" t="s">
-        <v>429</v>
       </c>
       <c r="I43" s="13">
         <v>46366</v>
       </c>
       <c r="J43" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K43" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
       <c r="L43" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="9"/>
@@ -14045,7 +14045,7 @@
     </row>
     <row r="44" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>88</v>
@@ -14054,16 +14054,16 @@
         <v>68</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>106</v>
@@ -14073,11 +14073,11 @@
       </c>
       <c r="J44" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K44" s="15"/>
       <c r="L44" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="9"/>
@@ -14088,7 +14088,7 @@
     </row>
     <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>88</v>
@@ -14097,30 +14097,30 @@
         <v>68</v>
       </c>
       <c r="D45" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H45" s="17" t="s">
         <v>434</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H45" s="17" t="s">
-        <v>435</v>
       </c>
       <c r="I45" s="13">
         <v>46477</v>
       </c>
       <c r="J45" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K45" s="15"/>
       <c r="L45" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M45" s="13"/>
       <c r="N45" s="9"/>
@@ -14131,7 +14131,7 @@
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>88</v>
@@ -14140,30 +14140,30 @@
         <v>68</v>
       </c>
       <c r="D46" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H46" s="17" t="s">
         <v>437</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H46" s="17" t="s">
-        <v>438</v>
       </c>
       <c r="I46" s="13">
         <v>46477</v>
       </c>
       <c r="J46" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K46" s="15"/>
       <c r="L46" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M46" s="13"/>
       <c r="N46" s="9"/>
@@ -14174,7 +14174,7 @@
     </row>
     <row r="47" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>118</v>
@@ -14183,33 +14183,33 @@
         <v>120</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>120</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I47" s="13">
         <v>46295</v>
       </c>
       <c r="J47" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="K47" s="15" t="str">
         <f t="shared" ref="K47:K65" ca="1" si="4">IFERROR(IF(I47="","",IF(I47-TODAY()&lt;0,"OVERDUE",IF(I47-TODAY()&lt;=14,"DUE NOW",IF(I47-TODAY()&lt;=30,"Prepare","")))),"")</f>
         <v/>
       </c>
       <c r="L47" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M47" s="13"/>
       <c r="N47" s="9"/>
@@ -14220,7 +14220,7 @@
     </row>
     <row r="48" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>118</v>
@@ -14229,33 +14229,33 @@
         <v>120</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>120</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I48" s="13">
         <v>46265</v>
       </c>
       <c r="J48" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K48" s="15" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Prepare</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M48" s="13"/>
       <c r="N48" s="9"/>
@@ -14724,357 +14724,357 @@
   <sheetData>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="34" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="33" t="s">
-        <v>489</v>
-      </c>
-      <c r="C5" s="33"/>
+      <c r="C5" s="34"/>
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
+        <v>490</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>491</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="22" t="s">
+        <v>492</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>493</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="22" t="s">
+        <v>494</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>495</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="22" t="s">
+        <v>496</v>
+      </c>
+      <c r="C11" s="21" t="s">
         <v>497</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="22" t="s">
+        <v>498</v>
+      </c>
+      <c r="C12" s="21" t="s">
         <v>499</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="22" t="s">
+        <v>500</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>501</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="22" t="s">
+        <v>502</v>
+      </c>
+      <c r="C14" s="21" t="s">
         <v>503</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>506</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="23" t="s">
+        <v>507</v>
+      </c>
+      <c r="C18" s="21" t="s">
         <v>508</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="23" t="s">
+        <v>509</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>510</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="23" t="s">
+        <v>511</v>
+      </c>
+      <c r="C20" s="21" t="s">
         <v>512</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="23" t="s">
+        <v>513</v>
+      </c>
+      <c r="C21" s="21" t="s">
         <v>514</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="23" t="s">
+        <v>515</v>
+      </c>
+      <c r="C22" s="21" t="s">
         <v>516</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="23" t="s">
+        <v>517</v>
+      </c>
+      <c r="C23" s="21" t="s">
         <v>518</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="23" t="s">
+        <v>519</v>
+      </c>
+      <c r="C24" s="21" t="s">
         <v>520</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="23" t="s">
+        <v>521</v>
+      </c>
+      <c r="C25" s="21" t="s">
         <v>522</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="32" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C28" s="32"/>
     </row>
     <row r="29" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="32" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C29" s="32"/>
     </row>
     <row r="30" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="32" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C30" s="32"/>
     </row>
     <row r="31" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="32" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C31" s="32"/>
     </row>
     <row r="32" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="32" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C32" s="32"/>
     </row>
     <row r="33" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="32" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C33" s="32"/>
     </row>
     <row r="34" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="32" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C34" s="32"/>
     </row>
     <row r="36" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="4" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="33" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="37" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="34" t="s">
+      <c r="C37" s="33"/>
+    </row>
+    <row r="38" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="33" t="s">
         <v>533</v>
       </c>
-      <c r="C37" s="34"/>
-    </row>
-    <row r="38" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="34" t="s">
+      <c r="C38" s="33"/>
+    </row>
+    <row r="39" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="33" t="s">
         <v>534</v>
       </c>
-      <c r="C38" s="34"/>
-    </row>
-    <row r="39" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="34" t="s">
+      <c r="C39" s="33"/>
+    </row>
+    <row r="40" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="33" t="s">
         <v>535</v>
       </c>
-      <c r="C39" s="34"/>
-    </row>
-    <row r="40" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="34" t="s">
+      <c r="C40" s="33"/>
+    </row>
+    <row r="41" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="33" t="s">
         <v>536</v>
       </c>
-      <c r="C40" s="34"/>
-    </row>
-    <row r="41" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="34" t="s">
+      <c r="C41" s="33"/>
+    </row>
+    <row r="42" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="33" t="s">
         <v>537</v>
       </c>
-      <c r="C41" s="34"/>
-    </row>
-    <row r="42" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="34" t="s">
+      <c r="C42" s="33"/>
+    </row>
+    <row r="43" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="33" t="s">
         <v>538</v>
       </c>
-      <c r="C42" s="34"/>
-    </row>
-    <row r="43" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="34" t="s">
+      <c r="C43" s="33"/>
+    </row>
+    <row r="44" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="33" t="s">
         <v>539</v>
       </c>
-      <c r="C43" s="34"/>
-    </row>
-    <row r="44" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="34" t="s">
+      <c r="C44" s="33"/>
+    </row>
+    <row r="45" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="33" t="s">
         <v>540</v>
       </c>
-      <c r="C44" s="34"/>
-    </row>
-    <row r="45" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="34" t="s">
+      <c r="C45" s="33"/>
+    </row>
+    <row r="46" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="33" t="s">
         <v>541</v>
       </c>
-      <c r="C45" s="34"/>
-    </row>
-    <row r="46" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="34" t="s">
+      <c r="C46" s="33"/>
+    </row>
+    <row r="47" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="33" t="s">
         <v>542</v>
       </c>
-      <c r="C46" s="34"/>
-    </row>
-    <row r="47" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="34" t="s">
+      <c r="C47" s="33"/>
+    </row>
+    <row r="48" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="33" t="s">
         <v>543</v>
       </c>
-      <c r="C47" s="34"/>
-    </row>
-    <row r="48" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="34" t="s">
+      <c r="C48" s="33"/>
+    </row>
+    <row r="49" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="33" t="s">
         <v>544</v>
       </c>
-      <c r="C48" s="34"/>
-    </row>
-    <row r="49" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="34" t="s">
+      <c r="C49" s="33"/>
+    </row>
+    <row r="50" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="33" t="s">
         <v>545</v>
       </c>
-      <c r="C49" s="34"/>
-    </row>
-    <row r="50" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="34" t="s">
+      <c r="C50" s="33"/>
+    </row>
+    <row r="51" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="33" t="s">
         <v>546</v>
       </c>
-      <c r="C50" s="34"/>
-    </row>
-    <row r="51" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="34" t="s">
+      <c r="C51" s="33"/>
+    </row>
+    <row r="52" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="33" t="s">
         <v>547</v>
       </c>
-      <c r="C51" s="34"/>
-    </row>
-    <row r="52" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="34" t="s">
+      <c r="C52" s="33"/>
+    </row>
+    <row r="53" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="33" t="s">
         <v>548</v>
       </c>
-      <c r="C52" s="34"/>
-    </row>
-    <row r="53" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="34" t="s">
+      <c r="C53" s="33"/>
+    </row>
+    <row r="54" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="33" t="s">
         <v>549</v>
       </c>
-      <c r="C53" s="34"/>
-    </row>
-    <row r="54" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="34" t="s">
+      <c r="C54" s="33"/>
+    </row>
+    <row r="55" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="33" t="s">
         <v>550</v>
       </c>
-      <c r="C54" s="34"/>
-    </row>
-    <row r="55" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="34" t="s">
+      <c r="C55" s="33"/>
+    </row>
+    <row r="56" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="33" t="s">
         <v>551</v>
       </c>
-      <c r="C55" s="34"/>
-    </row>
-    <row r="56" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="34" t="s">
-        <v>552</v>
-      </c>
-      <c r="C56" s="34"/>
+      <c r="C56" s="33"/>
     </row>
     <row r="58" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="59" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="32" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C59" s="32"/>
     </row>
     <row r="60" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="32" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C60" s="32"/>
     </row>
     <row r="61" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="32" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C61" s="32"/>
     </row>
     <row r="62" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="32" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C62" s="32"/>
     </row>
@@ -15084,12 +15084,37 @@
     </row>
     <row r="64" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="32" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C64" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
     <mergeCell ref="B61:C61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="B63:C63"/>
@@ -15099,31 +15124,6 @@
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -15145,377 +15145,377 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>563</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>564</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>130</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
+        <v>683</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>684</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>685</v>
-      </c>
       <c r="C6" s="21" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E6" s="21" t="s">
+        <v>569</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>570</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
+        <v>571</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>572</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="C7" s="21" t="s">
         <v>573</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="E7" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="F7" s="21" t="s">
         <v>574</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>576</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="C8" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="F8" s="21" t="s">
         <v>577</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>567</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>579</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="C9" s="21" t="s">
         <v>580</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="E9" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="F9" s="21" t="s">
         <v>581</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="21" t="s">
+        <v>582</v>
+      </c>
+      <c r="B10" s="21" t="s">
         <v>583</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="C10" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E10" s="21" t="s">
         <v>584</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>574</v>
-      </c>
-      <c r="E10" s="21" t="s">
+      <c r="F10" s="21" t="s">
         <v>585</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="21" t="s">
+        <v>586</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>587</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="C11" s="21" t="s">
         <v>588</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="E11" s="21" t="s">
         <v>589</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="F11" s="21" t="s">
         <v>590</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="21" t="s">
+        <v>591</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>592</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="C12" s="21" t="s">
         <v>593</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="E12" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="F12" s="21" t="s">
         <v>594</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="21" t="s">
+        <v>595</v>
+      </c>
+      <c r="B13" s="21" t="s">
         <v>596</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="C13" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="E13" s="21" t="s">
         <v>597</v>
       </c>
-      <c r="C13" s="21" t="s">
-        <v>589</v>
-      </c>
-      <c r="E13" s="21" t="s">
+      <c r="F13" s="21" t="s">
         <v>598</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
+        <v>599</v>
+      </c>
+      <c r="B14" s="21" t="s">
         <v>600</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="C14" s="21" t="s">
         <v>601</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
+        <v>602</v>
+      </c>
+      <c r="B15" s="21" t="s">
         <v>603</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>604</v>
-      </c>
       <c r="C15" s="21" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="21" t="s">
+        <v>604</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>605</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="C16" s="21" t="s">
         <v>606</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="21" t="s">
+        <v>607</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>608</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="C17" s="21" t="s">
         <v>609</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="21" t="s">
+        <v>610</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>611</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>612</v>
-      </c>
       <c r="C18" s="21" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="21" t="s">
+        <v>612</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>613</v>
       </c>
-      <c r="B19" s="21" t="s">
-        <v>614</v>
-      </c>
       <c r="C19" s="21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="21" t="s">
+        <v>614</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>615</v>
       </c>
-      <c r="B20" s="21" t="s">
-        <v>616</v>
-      </c>
       <c r="C20" s="21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="21" t="s">
+        <v>616</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>617</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="C21" s="21" t="s">
         <v>618</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="21" t="s">
+        <v>619</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>620</v>
       </c>
-      <c r="B22" s="21" t="s">
-        <v>621</v>
-      </c>
       <c r="C22" s="21" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="21" t="s">
+        <v>621</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>622</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>623</v>
-      </c>
       <c r="C23" s="21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="21" t="s">
+        <v>623</v>
+      </c>
+      <c r="B24" s="21" t="s">
         <v>624</v>
       </c>
-      <c r="B24" s="21" t="s">
-        <v>625</v>
-      </c>
       <c r="C24" s="21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
+        <v>625</v>
+      </c>
+      <c r="B25" s="21" t="s">
         <v>626</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="C25" s="21" t="s">
         <v>627</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="21" t="s">
+        <v>628</v>
+      </c>
+      <c r="B26" s="21" t="s">
         <v>629</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="C26" s="21" t="s">
         <v>630</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="21" t="s">
+        <v>631</v>
+      </c>
+      <c r="B27" s="21" t="s">
         <v>632</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="C27" s="21" t="s">
         <v>633</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="21" t="s">
+        <v>634</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>482</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>635</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>483</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="21" t="s">
+        <v>636</v>
+      </c>
+      <c r="B29" s="21" t="s">
         <v>637</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="C29" s="21" t="s">
         <v>638</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="21" t="s">
+        <v>639</v>
+      </c>
+      <c r="B30" s="21" t="s">
         <v>640</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="C30" s="21" t="s">
         <v>641</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="21" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>61</v>
@@ -15523,57 +15523,57 @@
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="21" t="s">
+        <v>643</v>
+      </c>
+      <c r="B32" s="21" t="s">
         <v>644</v>
       </c>
-      <c r="B32" s="21" t="s">
-        <v>645</v>
-      </c>
       <c r="C32" s="21" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="21" t="s">
+        <v>645</v>
+      </c>
+      <c r="B33" s="21" t="s">
         <v>646</v>
       </c>
-      <c r="B33" s="21" t="s">
-        <v>647</v>
-      </c>
       <c r="C33" s="21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="21" t="s">
+        <v>647</v>
+      </c>
+      <c r="B34" s="21" t="s">
         <v>648</v>
       </c>
-      <c r="B34" s="21" t="s">
-        <v>649</v>
-      </c>
       <c r="C34" s="21" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="21" t="s">
+        <v>649</v>
+      </c>
+      <c r="B35" s="21" t="s">
         <v>650</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="C35" s="21" t="s">
         <v>651</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="21" t="s">
+        <v>652</v>
+      </c>
+      <c r="B36" s="21" t="s">
         <v>653</v>
       </c>
-      <c r="B36" s="21" t="s">
-        <v>654</v>
-      </c>
       <c r="C36" s="21" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
   </sheetData>

--- a/registers/NEK_Master_Registers.xlsx
+++ b/registers/NEK_Master_Registers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude Cowork\NEK\registers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34E587E-FDAE-48B6-BE8D-C3BA3A7EA494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16D8364-E29F-44AA-8477-E1A09F4D3C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -554,9 +554,6 @@
     <t>Sha Tin Riverpark</t>
   </si>
   <si>
-    <t>Chinese national</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
@@ -2166,6 +2163,9 @@
   </si>
   <si>
     <t>28-VC</t>
+  </si>
+  <si>
+    <t>吴娴娜</t>
   </si>
 </sst>
 </file>
@@ -2397,8 +2397,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2911,16 +2911,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
@@ -2929,6 +2919,16 @@
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2955,71 +2955,71 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>50</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>658</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>659</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>660</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>62</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="25" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B5" s="25" t="s">
         <v>66</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D5" s="25"/>
       <c r="E5" s="26" t="s">
+        <v>664</v>
+      </c>
+      <c r="F5" s="26" t="s">
         <v>665</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>666</v>
       </c>
       <c r="G5" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>77</v>
@@ -3029,26 +3029,26 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D6" s="25"/>
       <c r="E6" s="26" t="s">
+        <v>664</v>
+      </c>
+      <c r="F6" s="26" t="s">
         <v>665</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>666</v>
       </c>
       <c r="G6" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="I6" s="25" t="s">
         <v>77</v>
@@ -3058,20 +3058,20 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>80</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="26" t="s">
+        <v>664</v>
+      </c>
+      <c r="F7" s="26" t="s">
         <v>665</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>666</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>71</v>
@@ -3085,20 +3085,20 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>84</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="26" t="s">
+        <v>664</v>
+      </c>
+      <c r="F8" s="26" t="s">
         <v>665</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>666</v>
       </c>
       <c r="G8" s="25" t="s">
         <v>71</v>
@@ -3112,26 +3112,26 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>88</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="26" t="s">
+        <v>664</v>
+      </c>
+      <c r="F9" s="26" t="s">
         <v>665</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>666</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="I9" s="25" t="s">
         <v>77</v>
@@ -3141,20 +3141,20 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="26" t="s">
+        <v>664</v>
+      </c>
+      <c r="F10" s="26" t="s">
         <v>665</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>666</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>71</v>
@@ -3168,20 +3168,20 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="25" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>99</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="26" t="s">
+        <v>664</v>
+      </c>
+      <c r="F11" s="26" t="s">
         <v>665</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>666</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>71</v>
@@ -3195,20 +3195,20 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D12" s="25"/>
       <c r="E12" s="26" t="s">
+        <v>664</v>
+      </c>
+      <c r="F12" s="26" t="s">
         <v>665</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>666</v>
       </c>
       <c r="G12" s="25" t="s">
         <v>71</v>
@@ -3222,20 +3222,20 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="25" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B13" s="25" t="s">
         <v>108</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="26" t="s">
+        <v>664</v>
+      </c>
+      <c r="F13" s="26" t="s">
         <v>665</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>666</v>
       </c>
       <c r="G13" s="25" t="s">
         <v>71</v>
@@ -3249,26 +3249,26 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>112</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="26" t="s">
+        <v>664</v>
+      </c>
+      <c r="F14" s="26" t="s">
         <v>665</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>666</v>
       </c>
       <c r="G14" s="25" t="s">
         <v>92</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I14" s="25" t="s">
         <v>77</v>
@@ -3278,26 +3278,26 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B15" s="25" t="s">
         <v>118</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="26" t="s">
+        <v>664</v>
+      </c>
+      <c r="F15" s="26" t="s">
         <v>665</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>666</v>
       </c>
       <c r="G15" s="25" t="s">
         <v>121</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="I15" s="25" t="s">
         <v>77</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="35" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B24" s="35"/>
       <c r="C24" s="35"/>
@@ -3970,10 +3970,10 @@
         <v>114</v>
       </c>
       <c r="M14" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="N14" s="9" t="s">
         <v>703</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>704</v>
       </c>
       <c r="O14" s="9" t="s">
         <v>78</v>
@@ -4622,7 +4622,7 @@
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>112</v>
@@ -4637,7 +4637,7 @@
         <v>150</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>169</v>
+        <v>706</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>152</v>
@@ -4669,22 +4669,22 @@
         <v/>
       </c>
       <c r="P9" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q9" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="Q9" s="9" t="s">
+      <c r="R9" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="R9" s="14" t="s">
+      <c r="S9" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="T9" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="U9" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="S9" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="T9" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="U9" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="V9" s="13"/>
       <c r="W9" s="9" t="s">
@@ -4694,13 +4694,13 @@
     </row>
     <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" s="9">
         <v>28</v>
@@ -4709,7 +4709,7 @@
         <v>150</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>152</v>
@@ -4741,7 +4741,7 @@
         <v>Prepare</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q10" s="9"/>
       <c r="R10" s="14"/>
@@ -5873,62 +5873,62 @@
   <sheetData>
     <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>186</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>187</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="L4" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="M4" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>191</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>192</v>
       </c>
       <c r="Q4" s="8" t="s">
         <v>62</v>
@@ -5939,7 +5939,7 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>66</v>
@@ -5948,13 +5948,13 @@
         <v>113</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="G5" s="13">
         <v>42856</v>
@@ -5979,13 +5979,13 @@
         <v>300</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O5" s="13">
         <v>46419</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q5" s="9" t="s">
         <v>77</v>
@@ -5994,7 +5994,7 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>66</v>
@@ -6003,13 +6003,13 @@
         <v>98</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>201</v>
-      </c>
       <c r="F6" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G6" s="13">
         <v>42856</v>
@@ -6034,13 +6034,13 @@
         <v>300</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O6" s="13">
         <v>46419</v>
       </c>
       <c r="P6" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q6" s="9" t="s">
         <v>77</v>
@@ -6049,22 +6049,22 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C7" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>206</v>
-      </c>
       <c r="F7" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G7" s="13">
         <v>42856</v>
@@ -6089,13 +6089,13 @@
         <v>300</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O7" s="13">
         <v>46419</v>
       </c>
       <c r="P7" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q7" s="9" t="s">
         <v>77</v>
@@ -6104,22 +6104,22 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>210</v>
-      </c>
       <c r="F8" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G8" s="13">
         <v>44197</v>
@@ -6144,13 +6144,13 @@
         <v>100</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O8" s="13">
         <v>46419</v>
       </c>
       <c r="P8" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q8" s="9" t="s">
         <v>77</v>
@@ -6787,68 +6787,68 @@
   <sheetData>
     <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>217</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>218</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="H4" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>228</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>229</v>
       </c>
       <c r="S4" s="8" t="s">
         <v>62</v>
@@ -6859,22 +6859,22 @@
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>233</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>234</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>71</v>
@@ -6884,25 +6884,25 @@
         <v>15287.150000000001</v>
       </c>
       <c r="I5" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K5" s="9">
         <v>27</v>
       </c>
       <c r="L5" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M5" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="N5" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="O5" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P5" s="9"/>
       <c r="Q5" s="13"/>
@@ -6914,22 +6914,22 @@
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>243</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>244</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>71</v>
@@ -6939,25 +6939,25 @@
         <v>2949</v>
       </c>
       <c r="I6" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K6" s="9">
         <v>15</v>
       </c>
       <c r="L6" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M6" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="N6" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="O6" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P6" s="9"/>
       <c r="Q6" s="13"/>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>71</v>
@@ -6994,25 +6994,25 @@
         <v>368.75</v>
       </c>
       <c r="I7" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K7" s="9">
         <v>15</v>
       </c>
       <c r="L7" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M7" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="N7" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="O7" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="13"/>
@@ -7024,22 +7024,22 @@
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E8" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>249</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>250</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>71</v>
@@ -7049,25 +7049,25 @@
         <v>411.5</v>
       </c>
       <c r="I8" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K8" s="30">
         <v>15</v>
       </c>
       <c r="L8" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M8" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="N8" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="O8" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P8" s="9"/>
       <c r="Q8" s="13"/>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>253</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>254</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>71</v>
@@ -7103,25 +7103,25 @@
         <v>2700</v>
       </c>
       <c r="I9" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K9" s="30">
         <v>10</v>
       </c>
       <c r="L9" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M9" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="N9" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="O9" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P9" s="9"/>
       <c r="Q9" s="13"/>
@@ -7133,13 +7133,13 @@
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>61</v>
@@ -7148,7 +7148,7 @@
         <v>76</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>71</v>
@@ -7157,25 +7157,25 @@
         <v>2000</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K10" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L10" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M10" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="N10" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="O10" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P10" s="9"/>
       <c r="Q10" s="13"/>
@@ -7187,22 +7187,22 @@
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>71</v>
@@ -7211,25 +7211,25 @@
         <v>2000</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K11" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L11" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M11" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="N11" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N11" s="9" t="s">
+      <c r="O11" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P11" s="9"/>
       <c r="Q11" s="13"/>
@@ -7241,22 +7241,22 @@
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>71</v>
@@ -7265,25 +7265,25 @@
         <v>1200</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K12" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L12" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M12" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="N12" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="O12" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P12" s="9"/>
       <c r="Q12" s="13"/>
@@ -7295,22 +7295,22 @@
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>71</v>
@@ -7319,25 +7319,25 @@
         <v>1200</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K13" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L13" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M13" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="N13" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="O13" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P13" s="9"/>
       <c r="Q13" s="13"/>
@@ -7349,22 +7349,22 @@
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C14" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>270</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>271</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>71</v>
@@ -7373,25 +7373,25 @@
         <v>9000</v>
       </c>
       <c r="I14" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K14" s="30">
         <v>1</v>
       </c>
       <c r="L14" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M14" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M14" s="9" t="s">
+      <c r="N14" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N14" s="9" t="s">
+      <c r="O14" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P14" s="9"/>
       <c r="Q14" s="13"/>
@@ -7403,22 +7403,22 @@
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>269</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>71</v>
@@ -7427,25 +7427,25 @@
         <v>10000</v>
       </c>
       <c r="I15" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K15" s="30">
         <v>1</v>
       </c>
       <c r="L15" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M15" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="N15" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="O15" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P15" s="9"/>
       <c r="Q15" s="13"/>
@@ -7457,22 +7457,22 @@
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>269</v>
-      </c>
       <c r="E16" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>71</v>
@@ -7481,25 +7481,25 @@
         <v>8750</v>
       </c>
       <c r="I16" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K16" s="30">
         <v>1</v>
       </c>
       <c r="L16" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M16" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="N16" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N16" s="9" t="s">
+      <c r="O16" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P16" s="9"/>
       <c r="Q16" s="13"/>
@@ -7511,22 +7511,22 @@
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>269</v>
-      </c>
       <c r="E17" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>71</v>
@@ -7535,25 +7535,25 @@
         <v>8500</v>
       </c>
       <c r="I17" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K17" s="9">
         <v>1</v>
       </c>
       <c r="L17" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M17" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="N17" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N17" s="9" t="s">
+      <c r="O17" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P17" s="9"/>
       <c r="Q17" s="13"/>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>232</v>
-      </c>
       <c r="E18" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>71</v>
@@ -7589,25 +7589,25 @@
         <v>5321.85</v>
       </c>
       <c r="I18" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K18" s="9">
         <v>27</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M18" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="N18" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N18" s="9" t="s">
+      <c r="O18" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P18" s="9"/>
       <c r="Q18" s="13"/>
@@ -7619,22 +7619,22 @@
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D19" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="F19" s="9" t="s">
         <v>243</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>244</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>71</v>
@@ -7644,25 +7644,25 @@
         <v>945</v>
       </c>
       <c r="I19" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K19" s="9">
         <v>15</v>
       </c>
       <c r="L19" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M19" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M19" s="9" t="s">
+      <c r="N19" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N19" s="9" t="s">
+      <c r="O19" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P19" s="9"/>
       <c r="Q19" s="13"/>
@@ -7674,22 +7674,22 @@
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E20" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>71</v>
@@ -7698,25 +7698,25 @@
         <v>74.400000000000006</v>
       </c>
       <c r="I20" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K20" s="9">
         <v>15</v>
       </c>
       <c r="L20" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M20" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M20" s="9" t="s">
+      <c r="N20" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N20" s="9" t="s">
+      <c r="O20" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P20" s="9"/>
       <c r="Q20" s="13"/>
@@ -7728,22 +7728,22 @@
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E21" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>249</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>250</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>71</v>
@@ -7752,25 +7752,25 @@
         <v>240.5</v>
       </c>
       <c r="I21" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K21" s="9">
         <v>15</v>
       </c>
       <c r="L21" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M21" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M21" s="9" t="s">
+      <c r="N21" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="O21" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P21" s="9"/>
       <c r="Q21" s="13"/>
@@ -7782,22 +7782,22 @@
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>71</v>
@@ -7806,25 +7806,25 @@
         <v>6500</v>
       </c>
       <c r="I22" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K22" s="9">
         <v>15</v>
       </c>
       <c r="L22" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M22" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M22" s="9" t="s">
+      <c r="N22" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N22" s="9" t="s">
+      <c r="O22" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O22" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P22" s="9"/>
       <c r="Q22" s="13"/>
@@ -7836,22 +7836,22 @@
     </row>
     <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E23" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>287</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>288</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>71</v>
@@ -7860,25 +7860,25 @@
         <v>1017.6</v>
       </c>
       <c r="I23" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K23" s="9">
         <v>7</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M23" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="N23" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N23" s="9" t="s">
+      <c r="O23" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P23" s="9"/>
       <c r="Q23" s="13"/>
@@ -7890,49 +7890,49 @@
     </row>
     <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="F24" s="9" t="s">
         <v>291</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>292</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I24" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K24" s="9">
         <v>15</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M24" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="N24" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N24" s="9" t="s">
+      <c r="O24" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P24" s="9"/>
       <c r="Q24" s="13"/>
@@ -7944,22 +7944,22 @@
     </row>
     <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D25" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="F25" s="9" t="s">
         <v>296</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>297</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>71</v>
@@ -7968,25 +7968,25 @@
         <v>1296.58</v>
       </c>
       <c r="I25" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K25" s="9">
         <v>15</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M25" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="N25" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N25" s="9" t="s">
+      <c r="O25" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P25" s="9"/>
       <c r="Q25" s="13"/>
@@ -7998,22 +7998,22 @@
     </row>
     <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D26" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>296</v>
-      </c>
       <c r="F26" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>71</v>
@@ -8022,25 +8022,25 @@
         <v>1296.58</v>
       </c>
       <c r="I26" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K26" s="9">
         <v>15</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M26" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="N26" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N26" s="9" t="s">
+      <c r="O26" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O26" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P26" s="9"/>
       <c r="Q26" s="13"/>
@@ -8052,22 +8052,22 @@
     </row>
     <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D27" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>296</v>
-      </c>
       <c r="F27" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>71</v>
@@ -8076,25 +8076,25 @@
         <v>1296.58</v>
       </c>
       <c r="I27" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K27" s="9">
         <v>15</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M27" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="N27" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N27" s="9" t="s">
+      <c r="O27" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P27" s="9"/>
       <c r="Q27" s="13"/>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D28" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E28" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>296</v>
-      </c>
       <c r="F28" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>71</v>
@@ -8130,25 +8130,25 @@
         <v>1296.58</v>
       </c>
       <c r="I28" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J28" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K28" s="30">
         <v>15</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M28" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="N28" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N28" s="9" t="s">
+      <c r="O28" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O28" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P28" s="9"/>
       <c r="Q28" s="13"/>
@@ -8160,22 +8160,22 @@
     </row>
     <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D29" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>296</v>
-      </c>
       <c r="F29" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>71</v>
@@ -8184,25 +8184,25 @@
         <v>968.82</v>
       </c>
       <c r="I29" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K29" s="30">
         <v>15</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M29" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="N29" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N29" s="9" t="s">
+      <c r="O29" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P29" s="9"/>
       <c r="Q29" s="13"/>
@@ -8214,22 +8214,22 @@
     </row>
     <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D30" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="F30" s="9" t="s">
         <v>308</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>309</v>
       </c>
       <c r="G30" s="9" t="s">
         <v>71</v>
@@ -8239,25 +8239,25 @@
         <v>695</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K30" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M30" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="N30" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N30" s="9" t="s">
+      <c r="O30" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O30" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P30" s="9"/>
       <c r="Q30" s="13"/>
@@ -8269,22 +8269,22 @@
     </row>
     <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E31" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="F31" s="9" t="s">
         <v>311</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>312</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>71</v>
@@ -8294,25 +8294,25 @@
         <v>5041.2</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J31" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="K31" s="30" t="s">
         <v>313</v>
       </c>
-      <c r="K31" s="30" t="s">
-        <v>314</v>
-      </c>
       <c r="L31" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M31" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="N31" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N31" s="9" t="s">
+      <c r="O31" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O31" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P31" s="9"/>
       <c r="Q31" s="13"/>
@@ -8324,13 +8324,13 @@
     </row>
     <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>61</v>
@@ -8339,7 +8339,7 @@
         <v>76</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G32" s="9" t="s">
         <v>71</v>
@@ -8348,25 +8348,25 @@
         <v>2000</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K32" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L32" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M32" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M32" s="9" t="s">
+      <c r="N32" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N32" s="9" t="s">
+      <c r="O32" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O32" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P32" s="9"/>
       <c r="Q32" s="13"/>
@@ -8378,22 +8378,22 @@
     </row>
     <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>71</v>
@@ -8402,25 +8402,25 @@
         <v>2000</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K33" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L33" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M33" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M33" s="9" t="s">
+      <c r="N33" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N33" s="9" t="s">
+      <c r="O33" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O33" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P33" s="9"/>
       <c r="Q33" s="13"/>
@@ -8432,22 +8432,22 @@
     </row>
     <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G34" s="9" t="s">
         <v>71</v>
@@ -8456,25 +8456,25 @@
         <v>1200</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K34" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L34" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M34" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M34" s="9" t="s">
+      <c r="N34" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N34" s="9" t="s">
+      <c r="O34" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O34" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P34" s="9"/>
       <c r="Q34" s="13"/>
@@ -8486,22 +8486,22 @@
     </row>
     <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G35" s="9" t="s">
         <v>71</v>
@@ -8510,25 +8510,25 @@
         <v>1200</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K35" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L35" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M35" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M35" s="9" t="s">
+      <c r="N35" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N35" s="9" t="s">
+      <c r="O35" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P35" s="9"/>
       <c r="Q35" s="13"/>
@@ -8540,22 +8540,22 @@
     </row>
     <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E36" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="F36" s="9" t="s">
         <v>320</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>321</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>71</v>
@@ -8564,25 +8564,25 @@
         <v>104.95</v>
       </c>
       <c r="I36" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J36" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K36" s="30">
         <v>27</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N36" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O36" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O36" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P36" s="9"/>
       <c r="Q36" s="13"/>
@@ -8594,22 +8594,22 @@
     </row>
     <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D37" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="F37" s="9" t="s">
         <v>324</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>325</v>
       </c>
       <c r="G37" s="9" t="s">
         <v>71</v>
@@ -8618,25 +8618,25 @@
         <v>240</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K37" s="31" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N37" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O37" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P37" s="9"/>
       <c r="Q37" s="13"/>
@@ -8648,13 +8648,13 @@
     </row>
     <row r="38" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>61</v>
@@ -8663,7 +8663,7 @@
         <v>76</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>71</v>
@@ -8672,25 +8672,25 @@
         <v>2000</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K38" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N38" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O38" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O38" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P38" s="9"/>
       <c r="Q38" s="13"/>
@@ -8702,22 +8702,22 @@
     </row>
     <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>71</v>
@@ -8726,25 +8726,25 @@
         <v>2000</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K39" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N39" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O39" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O39" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P39" s="9"/>
       <c r="Q39" s="13"/>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>71</v>
@@ -8780,25 +8780,25 @@
         <v>1200</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K40" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N40" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O40" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O40" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P40" s="9"/>
       <c r="Q40" s="13"/>
@@ -8810,22 +8810,22 @@
     </row>
     <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>71</v>
@@ -8834,25 +8834,25 @@
         <v>1200</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K41" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L41" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N41" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O41" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O41" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P41" s="9"/>
       <c r="Q41" s="13"/>
@@ -8864,13 +8864,13 @@
     </row>
     <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>61</v>
@@ -8879,7 +8879,7 @@
         <v>76</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>71</v>
@@ -8888,25 +8888,25 @@
         <v>2000</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K42" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N42" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O42" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O42" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P42" s="9"/>
       <c r="Q42" s="13"/>
@@ -8918,22 +8918,22 @@
     </row>
     <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>71</v>
@@ -8942,25 +8942,25 @@
         <v>2000</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K43" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L43" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N43" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O43" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P43" s="9"/>
       <c r="Q43" s="13"/>
@@ -8972,22 +8972,22 @@
     </row>
     <row r="44" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G44" s="9" t="s">
         <v>71</v>
@@ -8996,25 +8996,25 @@
         <v>1200</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K44" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N44" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O44" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O44" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P44" s="9"/>
       <c r="Q44" s="13"/>
@@ -9026,22 +9026,22 @@
     </row>
     <row r="45" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>71</v>
@@ -9050,25 +9050,25 @@
         <v>1200</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K45" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N45" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O45" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O45" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P45" s="9"/>
       <c r="Q45" s="13"/>
@@ -9080,13 +9080,13 @@
     </row>
     <row r="46" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>61</v>
@@ -9095,7 +9095,7 @@
         <v>76</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>71</v>
@@ -9104,25 +9104,25 @@
         <v>2000</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K46" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L46" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N46" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O46" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O46" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P46" s="9"/>
       <c r="Q46" s="13"/>
@@ -9134,22 +9134,22 @@
     </row>
     <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G47" s="9" t="s">
         <v>71</v>
@@ -9158,25 +9158,25 @@
         <v>2000</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K47" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N47" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O47" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O47" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P47" s="9"/>
       <c r="Q47" s="13"/>
@@ -9188,22 +9188,22 @@
     </row>
     <row r="48" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G48" s="9" t="s">
         <v>71</v>
@@ -9212,25 +9212,25 @@
         <v>1200</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K48" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N48" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O48" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O48" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P48" s="9"/>
       <c r="Q48" s="13"/>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="49" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G49" s="9" t="s">
         <v>71</v>
@@ -9266,25 +9266,25 @@
         <v>1200</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K49" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N49" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O49" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O49" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P49" s="9"/>
       <c r="Q49" s="13"/>
@@ -9296,13 +9296,13 @@
     </row>
     <row r="50" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>61</v>
@@ -9311,7 +9311,7 @@
         <v>76</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G50" s="9" t="s">
         <v>71</v>
@@ -9320,25 +9320,25 @@
         <v>2000</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K50" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L50" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M50" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M50" s="9" t="s">
+      <c r="N50" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N50" s="9" t="s">
+      <c r="O50" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O50" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P50" s="9"/>
       <c r="Q50" s="13"/>
@@ -9350,22 +9350,22 @@
     </row>
     <row r="51" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G51" s="9" t="s">
         <v>71</v>
@@ -9374,25 +9374,25 @@
         <v>2000</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K51" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L51" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M51" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M51" s="9" t="s">
+      <c r="N51" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N51" s="9" t="s">
+      <c r="O51" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O51" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P51" s="9"/>
       <c r="Q51" s="13"/>
@@ -9404,22 +9404,22 @@
     </row>
     <row r="52" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>71</v>
@@ -9428,25 +9428,25 @@
         <v>1200</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K52" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L52" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M52" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M52" s="9" t="s">
+      <c r="N52" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N52" s="9" t="s">
+      <c r="O52" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O52" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P52" s="9"/>
       <c r="Q52" s="13"/>
@@ -9458,22 +9458,22 @@
     </row>
     <row r="53" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>71</v>
@@ -9482,25 +9482,25 @@
         <v>1200</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K53" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L53" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="M53" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M53" s="9" t="s">
+      <c r="N53" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N53" s="9" t="s">
+      <c r="O53" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O53" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P53" s="9"/>
       <c r="Q53" s="13"/>
@@ -9512,13 +9512,13 @@
     </row>
     <row r="54" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>61</v>
@@ -9527,7 +9527,7 @@
         <v>76</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>71</v>
@@ -9536,25 +9536,25 @@
         <v>2000</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K54" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N54" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O54" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O54" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P54" s="9"/>
       <c r="Q54" s="13"/>
@@ -9566,22 +9566,22 @@
     </row>
     <row r="55" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>71</v>
@@ -9590,25 +9590,25 @@
         <v>2000</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K55" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N55" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O55" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O55" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P55" s="9"/>
       <c r="Q55" s="13"/>
@@ -9620,22 +9620,22 @@
     </row>
     <row r="56" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>71</v>
@@ -9644,25 +9644,25 @@
         <v>1200</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K56" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N56" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O56" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O56" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P56" s="9"/>
       <c r="Q56" s="13"/>
@@ -9674,22 +9674,22 @@
     </row>
     <row r="57" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>71</v>
@@ -9698,25 +9698,25 @@
         <v>1200</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K57" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L57" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N57" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O57" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O57" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P57" s="9"/>
       <c r="Q57" s="13"/>
@@ -9728,13 +9728,13 @@
     </row>
     <row r="58" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>61</v>
@@ -9743,7 +9743,7 @@
         <v>76</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>71</v>
@@ -9752,25 +9752,25 @@
         <v>2000</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K58" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L58" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N58" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O58" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O58" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P58" s="9"/>
       <c r="Q58" s="13"/>
@@ -9782,22 +9782,22 @@
     </row>
     <row r="59" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>71</v>
@@ -9806,25 +9806,25 @@
         <v>2000</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K59" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L59" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N59" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O59" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O59" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P59" s="9"/>
       <c r="Q59" s="13"/>
@@ -9836,22 +9836,22 @@
     </row>
     <row r="60" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>71</v>
@@ -9860,25 +9860,25 @@
         <v>1200</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K60" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L60" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N60" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O60" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O60" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P60" s="9"/>
       <c r="Q60" s="13"/>
@@ -9890,22 +9890,22 @@
     </row>
     <row r="61" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>71</v>
@@ -9914,25 +9914,25 @@
         <v>1200</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K61" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L61" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N61" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O61" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O61" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="P61" s="9"/>
       <c r="Q61" s="13"/>
@@ -9944,22 +9944,22 @@
     </row>
     <row r="62" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D62" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="E62" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="E62" s="9" t="s">
+      <c r="F62" s="9" t="s">
         <v>354</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>92</v>
@@ -9969,25 +9969,25 @@
         <v>3280</v>
       </c>
       <c r="I62" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J62" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J62" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K62" s="9">
         <v>15</v>
       </c>
       <c r="L62" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M62" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N62" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O62" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P62" s="9"/>
       <c r="Q62" s="13"/>
@@ -9999,22 +9999,22 @@
     </row>
     <row r="63" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D63" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="E63" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="E63" s="9" t="s">
+      <c r="F63" s="9" t="s">
         <v>359</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>360</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>92</v>
@@ -10023,25 +10023,25 @@
         <v>1862</v>
       </c>
       <c r="I63" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J63" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J63" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K63" s="9">
         <v>15</v>
       </c>
       <c r="L63" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P63" s="9"/>
       <c r="Q63" s="13"/>
@@ -10053,22 +10053,22 @@
     </row>
     <row r="64" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E64" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="F64" s="9" t="s">
         <v>362</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>363</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>92</v>
@@ -10077,25 +10077,25 @@
         <v>2136</v>
       </c>
       <c r="I64" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J64" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J64" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K64" s="9">
         <v>15</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M64" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N64" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O64" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P64" s="9"/>
       <c r="Q64" s="13"/>
@@ -10107,22 +10107,22 @@
     </row>
     <row r="65" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D65" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="E65" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="F65" s="9" t="s">
         <v>366</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>367</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>92</v>
@@ -10132,25 +10132,25 @@
         <v>8946</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K65" s="9">
         <v>15</v>
       </c>
       <c r="L65" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P65" s="9"/>
       <c r="Q65" s="13"/>
@@ -10162,22 +10162,22 @@
     </row>
     <row r="66" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C66" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D66" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="D66" s="9" t="s">
-        <v>269</v>
-      </c>
       <c r="E66" s="9" t="s">
-        <v>169</v>
+        <v>706</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G66" s="9" t="s">
         <v>92</v>
@@ -10186,25 +10186,25 @@
         <v>25000</v>
       </c>
       <c r="I66" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J66" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J66" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K66" s="30">
         <v>15</v>
       </c>
       <c r="L66" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M66" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N66" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O66" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P66" s="9"/>
       <c r="Q66" s="13"/>
@@ -10216,22 +10216,22 @@
     </row>
     <row r="67" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C67" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D67" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="D67" s="9" t="s">
-        <v>269</v>
-      </c>
       <c r="E67" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G67" s="9" t="s">
         <v>92</v>
@@ -10240,25 +10240,25 @@
         <v>41000</v>
       </c>
       <c r="I67" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J67" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="J67" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="K67" s="30">
         <v>15</v>
       </c>
       <c r="L67" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M67" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P67" s="9"/>
       <c r="Q67" s="13"/>
@@ -10270,22 +10270,22 @@
     </row>
     <row r="68" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>118</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D68" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="E68" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="E68" s="9" t="s">
+      <c r="F68" s="9" t="s">
         <v>374</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>375</v>
       </c>
       <c r="G68" s="9" t="s">
         <v>121</v>
@@ -10294,25 +10294,25 @@
         <v>2377</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K68" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L68" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M68" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N68" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O68" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P68" s="9"/>
       <c r="Q68" s="13"/>
@@ -10324,22 +10324,22 @@
     </row>
     <row r="69" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>118</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D69" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="F69" s="9" t="s">
         <v>378</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>379</v>
       </c>
       <c r="G69" s="9" t="s">
         <v>121</v>
@@ -10348,25 +10348,25 @@
         <v>220</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K69" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L69" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M69" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P69" s="9"/>
       <c r="Q69" s="13"/>
@@ -10901,68 +10901,68 @@
   <sheetData>
     <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>384</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>385</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>387</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>388</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="K4" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>395</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>396</v>
       </c>
       <c r="S4" s="8" t="s">
         <v>62</v>
@@ -10973,13 +10973,13 @@
     </row>
     <row r="5" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>112</v>
@@ -11009,21 +11009,21 @@
         <v>77</v>
       </c>
       <c r="T5" s="19" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>73</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>68</v>
@@ -11050,18 +11050,18 @@
         <v>77</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>112</v>
@@ -11091,18 +11091,18 @@
         <v>77</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>88</v>
@@ -11132,12 +11132,12 @@
         <v>77</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>76</v>
@@ -11146,7 +11146,7 @@
         <v>61</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>68</v>
@@ -11173,21 +11173,21 @@
         <v>77</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>68</v>
@@ -11214,18 +11214,18 @@
         <v>77</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>66</v>
@@ -11255,21 +11255,21 @@
         <v>77</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>68</v>
@@ -11296,21 +11296,21 @@
         <v>77</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>68</v>
@@ -11337,21 +11337,21 @@
         <v>77</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C14" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>695</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>696</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>68</v>
@@ -11378,18 +11378,18 @@
         <v>77</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>112</v>
@@ -11419,21 +11419,21 @@
         <v>77</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>68</v>
@@ -11460,18 +11460,18 @@
         <v>77</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>88</v>
@@ -11501,18 +11501,18 @@
         <v>77</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>88</v>
@@ -11542,18 +11542,18 @@
         <v>77</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>112</v>
@@ -11583,18 +11583,18 @@
         <v>77</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>84</v>
@@ -11624,18 +11624,18 @@
         <v>77</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>88</v>
@@ -11665,7 +11665,7 @@
         <v>77</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -12229,65 +12229,65 @@
   <sheetData>
     <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>213</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>214</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>52</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>410</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>411</v>
       </c>
       <c r="R4" s="8" t="s">
         <v>63</v>
@@ -12295,7 +12295,7 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>66</v>
@@ -12304,19 +12304,19 @@
         <v>68</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>414</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>415</v>
       </c>
       <c r="I5" s="13">
         <v>46249</v>
@@ -12330,7 +12330,7 @@
         <v>DUE NOW</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M5" s="13"/>
       <c r="N5" s="9"/>
@@ -12341,7 +12341,7 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>66</v>
@@ -12350,19 +12350,19 @@
         <v>68</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>418</v>
-      </c>
       <c r="F6" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I6" s="13">
         <v>46249</v>
@@ -12376,7 +12376,7 @@
         <v>DUE NOW</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M6" s="13"/>
       <c r="N6" s="9"/>
@@ -12387,7 +12387,7 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>66</v>
@@ -12396,19 +12396,19 @@
         <v>68</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I7" s="13">
         <v>46249</v>
@@ -12422,7 +12422,7 @@
         <v>DUE NOW</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="9"/>
@@ -12433,7 +12433,7 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>66</v>
@@ -12442,16 +12442,16 @@
         <v>68</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>106</v>
@@ -12468,7 +12468,7 @@
         <v>OVERDUE</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M8" s="13"/>
       <c r="N8" s="9"/>
@@ -12479,7 +12479,7 @@
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>66</v>
@@ -12488,16 +12488,16 @@
         <v>68</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E9" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>106</v>
@@ -12525,7 +12525,7 @@
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>66</v>
@@ -12534,19 +12534,19 @@
         <v>68</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>427</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>428</v>
       </c>
       <c r="I10" s="13">
         <v>46366</v>
@@ -12560,7 +12560,7 @@
         <v/>
       </c>
       <c r="L10" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="9"/>
@@ -12571,7 +12571,7 @@
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>66</v>
@@ -12580,16 +12580,16 @@
         <v>68</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>106</v>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="K11" s="15"/>
       <c r="L11" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="9"/>
@@ -12614,7 +12614,7 @@
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>66</v>
@@ -12623,19 +12623,19 @@
         <v>68</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H12" s="17" t="s">
         <v>433</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>434</v>
       </c>
       <c r="I12" s="13">
         <v>46477</v>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="K12" s="15"/>
       <c r="L12" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M12" s="13"/>
       <c r="N12" s="9"/>
@@ -12657,7 +12657,7 @@
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>66</v>
@@ -12666,19 +12666,19 @@
         <v>68</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H13" s="17" t="s">
         <v>436</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>437</v>
       </c>
       <c r="I13" s="13">
         <v>46477</v>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="K13" s="15"/>
       <c r="L13" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M13" s="13"/>
       <c r="N13" s="9"/>
@@ -12700,7 +12700,7 @@
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>84</v>
@@ -12709,16 +12709,16 @@
         <v>68</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>70</v>
@@ -12732,7 +12732,7 @@
       </c>
       <c r="K14" s="15"/>
       <c r="L14" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M14" s="13"/>
       <c r="N14" s="9"/>
@@ -12743,7 +12743,7 @@
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>84</v>
@@ -12752,16 +12752,16 @@
         <v>68</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>106</v>
@@ -12775,7 +12775,7 @@
       </c>
       <c r="K15" s="15"/>
       <c r="L15" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="9"/>
@@ -12786,7 +12786,7 @@
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>84</v>
@@ -12795,19 +12795,19 @@
         <v>68</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H16" s="17" t="s">
         <v>433</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>434</v>
       </c>
       <c r="I16" s="13">
         <v>46477</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="K16" s="15"/>
       <c r="L16" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="9"/>
@@ -12829,7 +12829,7 @@
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>84</v>
@@ -12838,16 +12838,16 @@
         <v>68</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G17" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>106</v>
@@ -12864,7 +12864,7 @@
         <v>OVERDUE</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="9"/>
@@ -12875,7 +12875,7 @@
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>84</v>
@@ -12884,16 +12884,16 @@
         <v>68</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E18" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G18" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>106</v>
@@ -12921,7 +12921,7 @@
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>95</v>
@@ -12930,16 +12930,16 @@
         <v>68</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>106</v>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="K19" s="15"/>
       <c r="L19" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M19" s="13"/>
       <c r="N19" s="9"/>
@@ -12964,7 +12964,7 @@
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>95</v>
@@ -12973,19 +12973,19 @@
         <v>68</v>
       </c>
       <c r="D20" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H20" s="17" t="s">
         <v>433</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>434</v>
       </c>
       <c r="I20" s="13">
         <v>46477</v>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="K20" s="15"/>
       <c r="L20" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M20" s="13"/>
       <c r="N20" s="9"/>
@@ -13007,7 +13007,7 @@
     </row>
     <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>95</v>
@@ -13016,16 +13016,16 @@
         <v>68</v>
       </c>
       <c r="D21" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>106</v>
@@ -13042,7 +13042,7 @@
         <v>OVERDUE</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="9"/>
@@ -13053,7 +13053,7 @@
     </row>
     <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>95</v>
@@ -13062,16 +13062,16 @@
         <v>68</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E22" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G22" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>106</v>
@@ -13099,7 +13099,7 @@
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>99</v>
@@ -13108,16 +13108,16 @@
         <v>68</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>106</v>
@@ -13131,7 +13131,7 @@
       </c>
       <c r="K23" s="15"/>
       <c r="L23" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M23" s="13"/>
       <c r="N23" s="9"/>
@@ -13142,7 +13142,7 @@
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>99</v>
@@ -13151,19 +13151,19 @@
         <v>68</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H24" s="17" t="s">
         <v>433</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H24" s="17" t="s">
-        <v>434</v>
       </c>
       <c r="I24" s="13">
         <v>46477</v>
@@ -13174,7 +13174,7 @@
       </c>
       <c r="K24" s="15"/>
       <c r="L24" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M24" s="13"/>
       <c r="N24" s="9"/>
@@ -13185,7 +13185,7 @@
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>99</v>
@@ -13194,16 +13194,16 @@
         <v>68</v>
       </c>
       <c r="D25" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="F25" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G25" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>106</v>
@@ -13220,7 +13220,7 @@
         <v>OVERDUE</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M25" s="13"/>
       <c r="N25" s="9"/>
@@ -13231,7 +13231,7 @@
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>99</v>
@@ -13240,16 +13240,16 @@
         <v>68</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E26" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G26" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>106</v>
@@ -13277,7 +13277,7 @@
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>80</v>
@@ -13286,16 +13286,16 @@
         <v>68</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>106</v>
@@ -13309,7 +13309,7 @@
       </c>
       <c r="K27" s="15"/>
       <c r="L27" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="9"/>
@@ -13320,7 +13320,7 @@
     </row>
     <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>80</v>
@@ -13329,19 +13329,19 @@
         <v>68</v>
       </c>
       <c r="D28" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H28" s="17" t="s">
         <v>433</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>434</v>
       </c>
       <c r="I28" s="13">
         <v>46477</v>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="K28" s="15"/>
       <c r="L28" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="9"/>
@@ -13363,7 +13363,7 @@
     </row>
     <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>80</v>
@@ -13372,16 +13372,16 @@
         <v>68</v>
       </c>
       <c r="D29" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="F29" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G29" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>106</v>
@@ -13398,7 +13398,7 @@
         <v>OVERDUE</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="9"/>
@@ -13409,7 +13409,7 @@
     </row>
     <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>80</v>
@@ -13418,16 +13418,16 @@
         <v>68</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E30" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G30" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>106</v>
@@ -13455,7 +13455,7 @@
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>103</v>
@@ -13464,19 +13464,19 @@
         <v>68</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I31" s="13">
         <v>46446</v>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="K31" s="15"/>
       <c r="L31" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="9"/>
@@ -13495,12 +13495,12 @@
       <c r="P31" s="13"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>103</v>
@@ -13509,19 +13509,19 @@
         <v>68</v>
       </c>
       <c r="D32" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H32" s="17" t="s">
         <v>433</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>434</v>
       </c>
       <c r="I32" s="13">
         <v>46477</v>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="K32" s="15"/>
       <c r="L32" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="9"/>
@@ -13543,7 +13543,7 @@
     </row>
     <row r="33" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>103</v>
@@ -13552,16 +13552,16 @@
         <v>68</v>
       </c>
       <c r="D33" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="F33" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>106</v>
@@ -13578,7 +13578,7 @@
         <v>OVERDUE</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="9"/>
@@ -13589,7 +13589,7 @@
     </row>
     <row r="34" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>103</v>
@@ -13598,16 +13598,16 @@
         <v>68</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E34" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G34" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>106</v>
@@ -13635,7 +13635,7 @@
     </row>
     <row r="35" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>108</v>
@@ -13644,19 +13644,19 @@
         <v>68</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I35" s="13">
         <v>46446</v>
@@ -13667,7 +13667,7 @@
       </c>
       <c r="K35" s="15"/>
       <c r="L35" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="9"/>
@@ -13675,12 +13675,12 @@
       <c r="P35" s="13"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>108</v>
@@ -13689,19 +13689,19 @@
         <v>68</v>
       </c>
       <c r="D36" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H36" s="17" t="s">
         <v>433</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>434</v>
       </c>
       <c r="I36" s="13">
         <v>46477</v>
@@ -13712,7 +13712,7 @@
       </c>
       <c r="K36" s="15"/>
       <c r="L36" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="9"/>
@@ -13723,7 +13723,7 @@
     </row>
     <row r="37" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>108</v>
@@ -13732,16 +13732,16 @@
         <v>68</v>
       </c>
       <c r="D37" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="F37" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G37" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>106</v>
@@ -13758,7 +13758,7 @@
         <v>OVERDUE</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="9"/>
@@ -13769,7 +13769,7 @@
     </row>
     <row r="38" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>108</v>
@@ -13778,16 +13778,16 @@
         <v>68</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E38" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G38" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>106</v>
@@ -13815,7 +13815,7 @@
     </row>
     <row r="39" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>88</v>
@@ -13824,19 +13824,19 @@
         <v>90</v>
       </c>
       <c r="D39" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="F39" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H39" s="17" t="s">
         <v>468</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>469</v>
       </c>
       <c r="I39" s="13">
         <v>46265</v>
@@ -13850,7 +13850,7 @@
         <v>Prepare</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="9"/>
@@ -13861,7 +13861,7 @@
     </row>
     <row r="40" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>88</v>
@@ -13870,19 +13870,19 @@
         <v>90</v>
       </c>
       <c r="D40" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="E40" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="F40" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H40" s="17" t="s">
         <v>472</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H40" s="17" t="s">
-        <v>473</v>
       </c>
       <c r="I40" s="13">
         <v>46536</v>
@@ -13896,7 +13896,7 @@
         <v/>
       </c>
       <c r="L40" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="9"/>
@@ -13907,7 +13907,7 @@
     </row>
     <row r="41" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>88</v>
@@ -13916,19 +13916,19 @@
         <v>90</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I41" s="13">
         <v>46356</v>
@@ -13942,7 +13942,7 @@
         <v/>
       </c>
       <c r="L41" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="9"/>
@@ -13953,7 +13953,7 @@
     </row>
     <row r="42" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>88</v>
@@ -13962,16 +13962,16 @@
         <v>90</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>106</v>
@@ -13988,7 +13988,7 @@
         <v>OVERDUE</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="9"/>
@@ -13999,7 +13999,7 @@
     </row>
     <row r="43" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>88</v>
@@ -14008,19 +14008,19 @@
         <v>68</v>
       </c>
       <c r="D43" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H43" s="17" t="s">
         <v>427</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H43" s="17" t="s">
-        <v>428</v>
       </c>
       <c r="I43" s="13">
         <v>46366</v>
@@ -14034,7 +14034,7 @@
         <v/>
       </c>
       <c r="L43" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="9"/>
@@ -14045,7 +14045,7 @@
     </row>
     <row r="44" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>88</v>
@@ -14054,16 +14054,16 @@
         <v>68</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>106</v>
@@ -14077,7 +14077,7 @@
       </c>
       <c r="K44" s="15"/>
       <c r="L44" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="9"/>
@@ -14088,7 +14088,7 @@
     </row>
     <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>88</v>
@@ -14097,19 +14097,19 @@
         <v>68</v>
       </c>
       <c r="D45" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H45" s="17" t="s">
         <v>433</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H45" s="17" t="s">
-        <v>434</v>
       </c>
       <c r="I45" s="13">
         <v>46477</v>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="K45" s="15"/>
       <c r="L45" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M45" s="13"/>
       <c r="N45" s="9"/>
@@ -14131,7 +14131,7 @@
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>88</v>
@@ -14140,19 +14140,19 @@
         <v>68</v>
       </c>
       <c r="D46" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H46" s="17" t="s">
         <v>436</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H46" s="17" t="s">
-        <v>437</v>
       </c>
       <c r="I46" s="13">
         <v>46477</v>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="K46" s="15"/>
       <c r="L46" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M46" s="13"/>
       <c r="N46" s="9"/>
@@ -14174,7 +14174,7 @@
     </row>
     <row r="47" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>118</v>
@@ -14183,19 +14183,19 @@
         <v>120</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>120</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I47" s="13">
         <v>46295</v>
@@ -14209,7 +14209,7 @@
         <v/>
       </c>
       <c r="L47" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M47" s="13"/>
       <c r="N47" s="9"/>
@@ -14220,7 +14220,7 @@
     </row>
     <row r="48" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>118</v>
@@ -14229,19 +14229,19 @@
         <v>120</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>120</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I48" s="13">
         <v>46265</v>
@@ -14255,7 +14255,7 @@
         <v>Prepare</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M48" s="13"/>
       <c r="N48" s="9"/>
@@ -14724,357 +14724,357 @@
   <sheetData>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="33" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="34" t="s">
-        <v>488</v>
-      </c>
-      <c r="C5" s="34"/>
+      <c r="C5" s="33"/>
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
+        <v>489</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>491</v>
       </c>
       <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="22" t="s">
+        <v>491</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>492</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>494</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="C11" s="21" t="s">
         <v>496</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="C12" s="21" t="s">
         <v>498</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="22" t="s">
+        <v>499</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>500</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="C14" s="21" t="s">
         <v>502</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>505</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="23" t="s">
+        <v>506</v>
+      </c>
+      <c r="C18" s="21" t="s">
         <v>507</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="23" t="s">
+        <v>508</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>509</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="23" t="s">
+        <v>510</v>
+      </c>
+      <c r="C20" s="21" t="s">
         <v>511</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="23" t="s">
+        <v>512</v>
+      </c>
+      <c r="C21" s="21" t="s">
         <v>513</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="23" t="s">
+        <v>514</v>
+      </c>
+      <c r="C22" s="21" t="s">
         <v>515</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="23" t="s">
+        <v>516</v>
+      </c>
+      <c r="C23" s="21" t="s">
         <v>517</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="23" t="s">
+        <v>518</v>
+      </c>
+      <c r="C24" s="21" t="s">
         <v>519</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="23" t="s">
+        <v>520</v>
+      </c>
+      <c r="C25" s="21" t="s">
         <v>521</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="32" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C28" s="32"/>
     </row>
     <row r="29" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="32" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C29" s="32"/>
     </row>
     <row r="30" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="32" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C30" s="32"/>
     </row>
     <row r="31" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="32" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C31" s="32"/>
     </row>
     <row r="32" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="32" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C32" s="32"/>
     </row>
     <row r="33" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="32" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C33" s="32"/>
     </row>
     <row r="34" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="32" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C34" s="32"/>
     </row>
     <row r="36" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="34" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="37" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="33" t="s">
+      <c r="C37" s="34"/>
+    </row>
+    <row r="38" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="34" t="s">
         <v>532</v>
       </c>
-      <c r="C37" s="33"/>
-    </row>
-    <row r="38" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="33" t="s">
+      <c r="C38" s="34"/>
+    </row>
+    <row r="39" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="34" t="s">
         <v>533</v>
       </c>
-      <c r="C38" s="33"/>
-    </row>
-    <row r="39" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="33" t="s">
+      <c r="C39" s="34"/>
+    </row>
+    <row r="40" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="34" t="s">
         <v>534</v>
       </c>
-      <c r="C39" s="33"/>
-    </row>
-    <row r="40" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="33" t="s">
+      <c r="C40" s="34"/>
+    </row>
+    <row r="41" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="C40" s="33"/>
-    </row>
-    <row r="41" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="33" t="s">
+      <c r="C41" s="34"/>
+    </row>
+    <row r="42" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="34" t="s">
         <v>536</v>
       </c>
-      <c r="C41" s="33"/>
-    </row>
-    <row r="42" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="33" t="s">
+      <c r="C42" s="34"/>
+    </row>
+    <row r="43" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="34" t="s">
         <v>537</v>
       </c>
-      <c r="C42" s="33"/>
-    </row>
-    <row r="43" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="33" t="s">
+      <c r="C43" s="34"/>
+    </row>
+    <row r="44" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="C43" s="33"/>
-    </row>
-    <row r="44" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="33" t="s">
+      <c r="C44" s="34"/>
+    </row>
+    <row r="45" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="34" t="s">
         <v>539</v>
       </c>
-      <c r="C44" s="33"/>
-    </row>
-    <row r="45" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="33" t="s">
+      <c r="C45" s="34"/>
+    </row>
+    <row r="46" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="34" t="s">
         <v>540</v>
       </c>
-      <c r="C45" s="33"/>
-    </row>
-    <row r="46" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="33" t="s">
+      <c r="C46" s="34"/>
+    </row>
+    <row r="47" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="34" t="s">
         <v>541</v>
       </c>
-      <c r="C46" s="33"/>
-    </row>
-    <row r="47" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="33" t="s">
+      <c r="C47" s="34"/>
+    </row>
+    <row r="48" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="34" t="s">
         <v>542</v>
       </c>
-      <c r="C47" s="33"/>
-    </row>
-    <row r="48" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="33" t="s">
+      <c r="C48" s="34"/>
+    </row>
+    <row r="49" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="34" t="s">
         <v>543</v>
       </c>
-      <c r="C48" s="33"/>
-    </row>
-    <row r="49" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="33" t="s">
+      <c r="C49" s="34"/>
+    </row>
+    <row r="50" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="34" t="s">
         <v>544</v>
       </c>
-      <c r="C49" s="33"/>
-    </row>
-    <row r="50" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="33" t="s">
+      <c r="C50" s="34"/>
+    </row>
+    <row r="51" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="34" t="s">
         <v>545</v>
       </c>
-      <c r="C50" s="33"/>
-    </row>
-    <row r="51" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="33" t="s">
+      <c r="C51" s="34"/>
+    </row>
+    <row r="52" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="34" t="s">
         <v>546</v>
       </c>
-      <c r="C51" s="33"/>
-    </row>
-    <row r="52" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="33" t="s">
+      <c r="C52" s="34"/>
+    </row>
+    <row r="53" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="34" t="s">
         <v>547</v>
       </c>
-      <c r="C52" s="33"/>
-    </row>
-    <row r="53" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="33" t="s">
+      <c r="C53" s="34"/>
+    </row>
+    <row r="54" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="34" t="s">
         <v>548</v>
       </c>
-      <c r="C53" s="33"/>
-    </row>
-    <row r="54" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="33" t="s">
+      <c r="C54" s="34"/>
+    </row>
+    <row r="55" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="34" t="s">
         <v>549</v>
       </c>
-      <c r="C54" s="33"/>
-    </row>
-    <row r="55" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="33" t="s">
+      <c r="C55" s="34"/>
+    </row>
+    <row r="56" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="34" t="s">
         <v>550</v>
       </c>
-      <c r="C55" s="33"/>
-    </row>
-    <row r="56" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="33" t="s">
-        <v>551</v>
-      </c>
-      <c r="C56" s="33"/>
+      <c r="C56" s="34"/>
     </row>
     <row r="58" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="59" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="32" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C59" s="32"/>
     </row>
     <row r="60" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="32" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C60" s="32"/>
     </row>
     <row r="61" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="32" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C61" s="32"/>
     </row>
     <row r="62" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="32" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C62" s="32"/>
     </row>
@@ -15084,37 +15084,12 @@
     </row>
     <row r="64" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="32" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C64" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
     <mergeCell ref="B61:C61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="B63:C63"/>
@@ -15124,6 +15099,31 @@
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -15145,377 +15145,377 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>563</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>130</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
+        <v>682</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>683</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>684</v>
-      </c>
       <c r="C6" s="21" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E6" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>569</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>571</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="C7" s="21" t="s">
         <v>572</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="E7" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="F7" s="21" t="s">
         <v>573</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>575</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="C8" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="F8" s="21" t="s">
         <v>576</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>566</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>578</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="C9" s="21" t="s">
         <v>579</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="E9" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="F9" s="21" t="s">
         <v>580</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="21" t="s">
+        <v>581</v>
+      </c>
+      <c r="B10" s="21" t="s">
         <v>582</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="C10" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="E10" s="21" t="s">
         <v>583</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>573</v>
-      </c>
-      <c r="E10" s="21" t="s">
+      <c r="F10" s="21" t="s">
         <v>584</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>586</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="C11" s="21" t="s">
         <v>587</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="E11" s="21" t="s">
         <v>588</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="F11" s="21" t="s">
         <v>589</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="21" t="s">
+        <v>590</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>591</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="C12" s="21" t="s">
         <v>592</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="E12" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="F12" s="21" t="s">
         <v>593</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="21" t="s">
+        <v>594</v>
+      </c>
+      <c r="B13" s="21" t="s">
         <v>595</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="C13" s="21" t="s">
+        <v>587</v>
+      </c>
+      <c r="E13" s="21" t="s">
         <v>596</v>
       </c>
-      <c r="C13" s="21" t="s">
-        <v>588</v>
-      </c>
-      <c r="E13" s="21" t="s">
+      <c r="F13" s="21" t="s">
         <v>597</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
+        <v>598</v>
+      </c>
+      <c r="B14" s="21" t="s">
         <v>599</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="C14" s="21" t="s">
         <v>600</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
+        <v>601</v>
+      </c>
+      <c r="B15" s="21" t="s">
         <v>602</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>603</v>
-      </c>
       <c r="C15" s="21" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="21" t="s">
+        <v>603</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>604</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="C16" s="21" t="s">
         <v>605</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="21" t="s">
+        <v>606</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>607</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="C17" s="21" t="s">
         <v>608</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="21" t="s">
+        <v>609</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>610</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>611</v>
-      </c>
       <c r="C18" s="21" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="21" t="s">
+        <v>611</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>612</v>
       </c>
-      <c r="B19" s="21" t="s">
-        <v>613</v>
-      </c>
       <c r="C19" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="21" t="s">
+        <v>613</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>614</v>
       </c>
-      <c r="B20" s="21" t="s">
-        <v>615</v>
-      </c>
       <c r="C20" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>616</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="C21" s="21" t="s">
         <v>617</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="21" t="s">
+        <v>618</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>619</v>
       </c>
-      <c r="B22" s="21" t="s">
-        <v>620</v>
-      </c>
       <c r="C22" s="21" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="21" t="s">
+        <v>620</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>621</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>622</v>
-      </c>
       <c r="C23" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="21" t="s">
+        <v>622</v>
+      </c>
+      <c r="B24" s="21" t="s">
         <v>623</v>
       </c>
-      <c r="B24" s="21" t="s">
-        <v>624</v>
-      </c>
       <c r="C24" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
+        <v>624</v>
+      </c>
+      <c r="B25" s="21" t="s">
         <v>625</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="C25" s="21" t="s">
         <v>626</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="B26" s="21" t="s">
         <v>628</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="C26" s="21" t="s">
         <v>629</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="21" t="s">
+        <v>630</v>
+      </c>
+      <c r="B27" s="21" t="s">
         <v>631</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="C27" s="21" t="s">
         <v>632</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="21" t="s">
+        <v>633</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>634</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>482</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="21" t="s">
+        <v>635</v>
+      </c>
+      <c r="B29" s="21" t="s">
         <v>636</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="C29" s="21" t="s">
         <v>637</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="21" t="s">
+        <v>638</v>
+      </c>
+      <c r="B30" s="21" t="s">
         <v>639</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="C30" s="21" t="s">
         <v>640</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="21" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>61</v>
@@ -15523,57 +15523,57 @@
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="21" t="s">
+        <v>642</v>
+      </c>
+      <c r="B32" s="21" t="s">
         <v>643</v>
       </c>
-      <c r="B32" s="21" t="s">
-        <v>644</v>
-      </c>
       <c r="C32" s="21" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="21" t="s">
+        <v>644</v>
+      </c>
+      <c r="B33" s="21" t="s">
         <v>645</v>
       </c>
-      <c r="B33" s="21" t="s">
-        <v>646</v>
-      </c>
       <c r="C33" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="21" t="s">
+        <v>646</v>
+      </c>
+      <c r="B34" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="B34" s="21" t="s">
-        <v>648</v>
-      </c>
       <c r="C34" s="21" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="21" t="s">
+        <v>648</v>
+      </c>
+      <c r="B35" s="21" t="s">
         <v>649</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="C35" s="21" t="s">
         <v>650</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="21" t="s">
+        <v>651</v>
+      </c>
+      <c r="B36" s="21" t="s">
         <v>652</v>
       </c>
-      <c r="B36" s="21" t="s">
-        <v>653</v>
-      </c>
       <c r="C36" s="21" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
   </sheetData>

--- a/registers/NEK_Master_Registers.xlsx
+++ b/registers/NEK_Master_Registers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude Cowork\NEK\registers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16D8364-E29F-44AA-8477-E1A09F4D3C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4951F2AD-4B4B-42C1-8C6D-C3205156C998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00 README" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2219" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2248" uniqueCount="720">
   <si>
     <t>NEK GROUP — MASTER REGISTER WORKBOOK</t>
   </si>
@@ -710,9 +710,6 @@
     <t>Frequency</t>
   </si>
   <si>
-    <t>Due Day of the Month</t>
-  </si>
-  <si>
     <t>Payment Method</t>
   </si>
   <si>
@@ -923,9 +920,6 @@
     <t>Office electricity</t>
   </si>
   <si>
-    <t>Around 400</t>
-  </si>
-  <si>
     <t>RP-HHIL-012</t>
   </si>
   <si>
@@ -1145,9 +1139,6 @@
     <t>Rating and Valuation Department</t>
   </si>
   <si>
-    <t>Annual Government Rates</t>
-  </si>
-  <si>
     <t>RP-NCL-005</t>
   </si>
   <si>
@@ -1166,15 +1157,9 @@
     <t>Annual Renewal License</t>
   </si>
   <si>
-    <t>TM*</t>
-  </si>
-  <si>
     <t>Annual License Renewal</t>
   </si>
   <si>
-    <t>BN*</t>
-  </si>
-  <si>
     <t>RP-WT-002</t>
   </si>
   <si>
@@ -2166,6 +2151,60 @@
   </si>
   <si>
     <t>吴娴娜</t>
+  </si>
+  <si>
+    <t>Every 15 of the month</t>
+  </si>
+  <si>
+    <t>Every 27 of the month</t>
+  </si>
+  <si>
+    <t>Every 10 of the month</t>
+  </si>
+  <si>
+    <t>Every 1 of the month</t>
+  </si>
+  <si>
+    <t>Every 7 of the month</t>
+  </si>
+  <si>
+    <t>30 April, 31 July, 30 October, 31 January</t>
+  </si>
+  <si>
+    <t>30 April</t>
+  </si>
+  <si>
+    <t>Amount fluctuates every month based on usage. Need to be verified every month after utility bill is issued monthly</t>
+  </si>
+  <si>
+    <t>10 May</t>
+  </si>
+  <si>
+    <t>1 August</t>
+  </si>
+  <si>
+    <t>BN France</t>
+  </si>
+  <si>
+    <t>Bn France</t>
+  </si>
+  <si>
+    <t>TM* Group</t>
+  </si>
+  <si>
+    <t>31 May</t>
+  </si>
+  <si>
+    <t>31 January, 30 April, 31 July, 30 October</t>
+  </si>
+  <si>
+    <t>Annual Government Rates for Sha Tin and Victoria Center</t>
+  </si>
+  <si>
+    <t>Due Day of the Month/Year</t>
+  </si>
+  <si>
+    <t>No secretarial fees for foreign listed company in Malaysia. To delete off this payment</t>
   </si>
 </sst>
 </file>
@@ -2335,7 +2374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2390,15 +2429,12 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2688,38 +2724,38 @@
       </c>
     </row>
     <row r="6" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="32"/>
+      <c r="C6" s="31"/>
     </row>
     <row r="7" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="32"/>
+      <c r="C7" s="31"/>
     </row>
     <row r="8" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="32"/>
+      <c r="C8" s="31"/>
     </row>
     <row r="9" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="31"/>
     </row>
     <row r="10" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
     </row>
     <row r="11" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="32"/>
+      <c r="C11" s="31"/>
     </row>
     <row r="13" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="4" t="s">
@@ -2833,46 +2869,46 @@
       </c>
     </row>
     <row r="30" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="32"/>
+      <c r="C30" s="31"/>
     </row>
     <row r="31" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="32"/>
+      <c r="C31" s="31"/>
     </row>
     <row r="32" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="32"/>
+      <c r="C32" s="31"/>
     </row>
     <row r="33" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="32" t="s">
+      <c r="B33" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="32"/>
+      <c r="C33" s="31"/>
     </row>
     <row r="34" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="32" t="s">
+      <c r="B34" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="32"/>
+      <c r="C34" s="31"/>
     </row>
     <row r="35" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="32" t="s">
+      <c r="B35" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="32"/>
+      <c r="C35" s="31"/>
     </row>
     <row r="36" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="32" t="s">
+      <c r="B36" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="32"/>
+      <c r="C36" s="31"/>
     </row>
     <row r="38" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="4" t="s">
@@ -2880,37 +2916,47 @@
       </c>
     </row>
     <row r="39" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="32"/>
+      <c r="C39" s="31"/>
     </row>
     <row r="40" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="32" t="s">
+      <c r="B40" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="C40" s="32"/>
+      <c r="C40" s="31"/>
     </row>
     <row r="41" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="32" t="s">
+      <c r="B41" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="32"/>
+      <c r="C41" s="31"/>
     </row>
     <row r="42" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="32" t="s">
+      <c r="B42" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="32"/>
+      <c r="C42" s="31"/>
     </row>
     <row r="43" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="32" t="s">
+      <c r="B43" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="32"/>
+      <c r="C43" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
@@ -2919,16 +2965,6 @@
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2955,71 +2991,71 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>50</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>62</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="25" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="B5" s="25" t="s">
         <v>66</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="D5" s="25"/>
       <c r="E5" s="26" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G5" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>77</v>
@@ -3029,26 +3065,26 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="D6" s="25"/>
       <c r="E6" s="26" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G6" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="I6" s="25" t="s">
         <v>77</v>
@@ -3058,20 +3094,20 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>80</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="26" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>71</v>
@@ -3085,20 +3121,20 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>84</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="26" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G8" s="25" t="s">
         <v>71</v>
@@ -3112,26 +3148,26 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>88</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="26" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>71</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="I9" s="25" t="s">
         <v>77</v>
@@ -3141,20 +3177,20 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="26" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>71</v>
@@ -3168,20 +3204,20 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="25" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>99</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="26" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>71</v>
@@ -3195,20 +3231,20 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="D12" s="25"/>
       <c r="E12" s="26" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G12" s="25" t="s">
         <v>71</v>
@@ -3222,20 +3258,20 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="25" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="B13" s="25" t="s">
         <v>108</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="26" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G13" s="25" t="s">
         <v>71</v>
@@ -3249,26 +3285,26 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>112</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="26" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G14" s="25" t="s">
         <v>92</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="I14" s="25" t="s">
         <v>77</v>
@@ -3278,26 +3314,26 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="B15" s="25" t="s">
         <v>118</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="26" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G15" s="25" t="s">
         <v>121</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="I15" s="25" t="s">
         <v>77</v>
@@ -3397,16 +3433,16 @@
       <c r="K22" s="28"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A24" s="35" t="s">
-        <v>680</v>
-      </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
+      <c r="A24" s="34" t="s">
+        <v>675</v>
+      </c>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3970,10 +4006,10 @@
         <v>114</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="O14" s="9" t="s">
         <v>78</v>
@@ -4366,7 +4402,7 @@
       </c>
       <c r="N5" s="15">
         <f t="shared" ref="N5:N44" ca="1" si="0">IFERROR(IF(M5="","",M5-TODAY()),"")</f>
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O5" s="15" t="str">
         <f t="shared" ref="O5:O44" ca="1" si="1">IFERROR(IF(M5="","",IF(M5-TODAY()&lt;0,"EXPIRED",IF(M5-TODAY()&lt;=90,"RENEW NOW",IF(M5-TODAY()&lt;=180,"Prepare","")))),"")</f>
@@ -4440,7 +4476,7 @@
       </c>
       <c r="N6" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O6" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4514,7 +4550,7 @@
       </c>
       <c r="N7" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="O7" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4588,7 +4624,7 @@
       </c>
       <c r="N8" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="O8" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4622,7 +4658,7 @@
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>112</v>
@@ -4637,7 +4673,7 @@
         <v>150</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>152</v>
@@ -4662,7 +4698,7 @@
       </c>
       <c r="N9" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="O9" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4694,7 +4730,7 @@
     </row>
     <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>112</v>
@@ -4734,7 +4770,7 @@
       </c>
       <c r="N10" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O10" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -6827,28 +6863,28 @@
         <v>220</v>
       </c>
       <c r="K4" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>227</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>228</v>
       </c>
       <c r="S4" s="8" t="s">
         <v>62</v>
@@ -6859,22 +6895,22 @@
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>232</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>233</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>71</v>
@@ -6884,25 +6920,25 @@
         <v>15287.150000000001</v>
       </c>
       <c r="I5" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="K5" s="30" t="s">
+        <v>703</v>
+      </c>
+      <c r="L5" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K5" s="9">
-        <v>27</v>
-      </c>
-      <c r="L5" s="9" t="s">
+      <c r="M5" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="N5" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="O5" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P5" s="9"/>
       <c r="Q5" s="13"/>
@@ -6914,22 +6950,22 @@
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>242</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>243</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>71</v>
@@ -6939,25 +6975,25 @@
         <v>2949</v>
       </c>
       <c r="I6" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="K6" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="L6" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K6" s="9">
-        <v>15</v>
-      </c>
-      <c r="L6" s="9" t="s">
+      <c r="M6" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="N6" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="O6" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P6" s="9"/>
       <c r="Q6" s="13"/>
@@ -6969,22 +7005,22 @@
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>245</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>246</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>71</v>
@@ -6994,25 +7030,25 @@
         <v>368.75</v>
       </c>
       <c r="I7" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="K7" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="L7" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K7" s="9">
-        <v>15</v>
-      </c>
-      <c r="L7" s="9" t="s">
+      <c r="M7" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="N7" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="O7" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="13"/>
@@ -7024,22 +7060,22 @@
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E8" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>71</v>
@@ -7049,25 +7085,25 @@
         <v>411.5</v>
       </c>
       <c r="I8" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="K8" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="L8" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K8" s="30">
-        <v>15</v>
-      </c>
-      <c r="L8" s="9" t="s">
+      <c r="M8" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="N8" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="O8" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P8" s="9"/>
       <c r="Q8" s="13"/>
@@ -7079,22 +7115,22 @@
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>252</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>253</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>71</v>
@@ -7103,25 +7139,25 @@
         <v>2700</v>
       </c>
       <c r="I9" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="K9" s="30" t="s">
+        <v>704</v>
+      </c>
+      <c r="L9" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K9" s="30">
-        <v>10</v>
-      </c>
-      <c r="L9" s="9" t="s">
+      <c r="M9" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="N9" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="O9" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P9" s="9"/>
       <c r="Q9" s="13"/>
@@ -7133,13 +7169,13 @@
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>61</v>
@@ -7148,7 +7184,7 @@
         <v>76</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>71</v>
@@ -7157,25 +7193,25 @@
         <v>2000</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K10" s="30" t="s">
-        <v>114</v>
+        <v>463</v>
       </c>
       <c r="L10" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="M10" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="N10" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="O10" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P10" s="9"/>
       <c r="Q10" s="13"/>
@@ -7187,49 +7223,49 @@
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H11" s="14">
-        <v>2000</v>
+        <v>1620</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K11" s="30" t="s">
-        <v>114</v>
+        <v>463</v>
       </c>
       <c r="L11" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="M11" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="N11" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N11" s="9" t="s">
+      <c r="O11" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P11" s="9"/>
       <c r="Q11" s="13"/>
@@ -7241,49 +7277,49 @@
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H12" s="14">
-        <v>1200</v>
+        <v>270</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K12" s="30" t="s">
-        <v>114</v>
+        <v>707</v>
       </c>
       <c r="L12" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="M12" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="N12" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="O12" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P12" s="9"/>
       <c r="Q12" s="13"/>
@@ -7295,49 +7331,49 @@
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H13" s="14">
-        <v>1200</v>
+        <v>980</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K13" s="30" t="s">
-        <v>114</v>
+        <v>708</v>
       </c>
       <c r="L13" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="M13" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="N13" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="O13" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P13" s="9"/>
       <c r="Q13" s="13"/>
@@ -7349,22 +7385,22 @@
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C14" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>269</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>270</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>71</v>
@@ -7373,25 +7409,25 @@
         <v>9000</v>
       </c>
       <c r="I14" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="K14" s="30" t="s">
+        <v>705</v>
+      </c>
+      <c r="L14" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K14" s="30">
-        <v>1</v>
-      </c>
-      <c r="L14" s="9" t="s">
+      <c r="M14" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M14" s="9" t="s">
+      <c r="N14" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N14" s="9" t="s">
+      <c r="O14" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P14" s="9"/>
       <c r="Q14" s="13"/>
@@ -7403,22 +7439,22 @@
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>268</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>71</v>
@@ -7427,25 +7463,25 @@
         <v>10000</v>
       </c>
       <c r="I15" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="K15" s="30" t="s">
+        <v>705</v>
+      </c>
+      <c r="L15" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K15" s="30">
-        <v>1</v>
-      </c>
-      <c r="L15" s="9" t="s">
+      <c r="M15" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="N15" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="O15" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P15" s="9"/>
       <c r="Q15" s="13"/>
@@ -7457,22 +7493,22 @@
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>268</v>
-      </c>
       <c r="E16" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>71</v>
@@ -7481,25 +7517,25 @@
         <v>8750</v>
       </c>
       <c r="I16" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="K16" s="30" t="s">
+        <v>705</v>
+      </c>
+      <c r="L16" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K16" s="30">
-        <v>1</v>
-      </c>
-      <c r="L16" s="9" t="s">
+      <c r="M16" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="N16" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N16" s="9" t="s">
+      <c r="O16" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P16" s="9"/>
       <c r="Q16" s="13"/>
@@ -7511,22 +7547,22 @@
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>268</v>
-      </c>
       <c r="E17" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>71</v>
@@ -7535,25 +7571,25 @@
         <v>8500</v>
       </c>
       <c r="I17" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="K17" s="30" t="s">
+        <v>705</v>
+      </c>
+      <c r="L17" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K17" s="9">
-        <v>1</v>
-      </c>
-      <c r="L17" s="9" t="s">
+      <c r="M17" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="N17" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N17" s="9" t="s">
+      <c r="O17" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P17" s="9"/>
       <c r="Q17" s="13"/>
@@ -7565,22 +7601,22 @@
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>231</v>
-      </c>
       <c r="E18" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>71</v>
@@ -7589,25 +7625,25 @@
         <v>5321.85</v>
       </c>
       <c r="I18" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J18" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="K18" s="9">
-        <v>27</v>
+      <c r="K18" s="30" t="s">
+        <v>703</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M18" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="N18" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N18" s="9" t="s">
+      <c r="O18" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P18" s="9"/>
       <c r="Q18" s="13"/>
@@ -7619,22 +7655,22 @@
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D19" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="F19" s="9" t="s">
         <v>242</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>243</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>71</v>
@@ -7644,25 +7680,25 @@
         <v>945</v>
       </c>
       <c r="I19" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="K19" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="L19" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K19" s="9">
-        <v>15</v>
-      </c>
-      <c r="L19" s="9" t="s">
+      <c r="M19" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M19" s="9" t="s">
+      <c r="N19" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N19" s="9" t="s">
+      <c r="O19" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P19" s="9"/>
       <c r="Q19" s="13"/>
@@ -7674,22 +7710,22 @@
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E20" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>245</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>246</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>71</v>
@@ -7698,25 +7734,25 @@
         <v>74.400000000000006</v>
       </c>
       <c r="I20" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="K20" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="L20" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K20" s="9">
-        <v>15</v>
-      </c>
-      <c r="L20" s="9" t="s">
+      <c r="M20" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M20" s="9" t="s">
+      <c r="N20" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N20" s="9" t="s">
+      <c r="O20" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P20" s="9"/>
       <c r="Q20" s="13"/>
@@ -7728,22 +7764,22 @@
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E21" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>71</v>
@@ -7752,25 +7788,25 @@
         <v>240.5</v>
       </c>
       <c r="I21" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="K21" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="L21" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K21" s="9">
-        <v>15</v>
-      </c>
-      <c r="L21" s="9" t="s">
+      <c r="M21" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M21" s="9" t="s">
+      <c r="N21" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="O21" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P21" s="9"/>
       <c r="Q21" s="13"/>
@@ -7782,22 +7818,22 @@
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>71</v>
@@ -7806,25 +7842,25 @@
         <v>6500</v>
       </c>
       <c r="I22" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="K22" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="L22" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K22" s="9">
-        <v>15</v>
-      </c>
-      <c r="L22" s="9" t="s">
+      <c r="M22" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M22" s="9" t="s">
+      <c r="N22" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N22" s="9" t="s">
+      <c r="O22" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O22" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P22" s="9"/>
       <c r="Q22" s="13"/>
@@ -7836,22 +7872,22 @@
     </row>
     <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E23" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>286</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>287</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>71</v>
@@ -7860,25 +7896,25 @@
         <v>1017.6</v>
       </c>
       <c r="I23" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J23" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="K23" s="9">
-        <v>7</v>
+      <c r="K23" s="30" t="s">
+        <v>706</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M23" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="N23" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N23" s="9" t="s">
+      <c r="O23" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P23" s="9"/>
       <c r="Q23" s="13"/>
@@ -7890,49 +7926,49 @@
     </row>
     <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="F24" s="9" t="s">
         <v>290</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>291</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="H24" s="14" t="s">
-        <v>292</v>
+      <c r="H24" s="14">
+        <v>400</v>
       </c>
       <c r="I24" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J24" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="K24" s="9">
-        <v>15</v>
+      <c r="K24" s="30" t="s">
+        <v>702</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M24" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="N24" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N24" s="9" t="s">
+      <c r="O24" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P24" s="9"/>
       <c r="Q24" s="13"/>
@@ -7940,26 +7976,28 @@
       <c r="S24" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9" t="s">
+        <v>709</v>
+      </c>
     </row>
     <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D25" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="F25" s="9" t="s">
         <v>294</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>296</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>71</v>
@@ -7968,25 +8006,25 @@
         <v>1296.58</v>
       </c>
       <c r="I25" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J25" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="K25" s="9">
-        <v>15</v>
+      <c r="K25" s="30" t="s">
+        <v>702</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M25" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="N25" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N25" s="9" t="s">
+      <c r="O25" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P25" s="9"/>
       <c r="Q25" s="13"/>
@@ -7998,22 +8036,22 @@
     </row>
     <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>71</v>
@@ -8022,25 +8060,25 @@
         <v>1296.58</v>
       </c>
       <c r="I26" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J26" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="K26" s="9">
-        <v>15</v>
+      <c r="K26" s="30" t="s">
+        <v>702</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M26" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="N26" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N26" s="9" t="s">
+      <c r="O26" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O26" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P26" s="9"/>
       <c r="Q26" s="13"/>
@@ -8052,22 +8090,22 @@
     </row>
     <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>71</v>
@@ -8076,25 +8114,25 @@
         <v>1296.58</v>
       </c>
       <c r="I27" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J27" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="K27" s="9">
-        <v>15</v>
+      <c r="K27" s="30" t="s">
+        <v>702</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M27" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="N27" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N27" s="9" t="s">
+      <c r="O27" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P27" s="9"/>
       <c r="Q27" s="13"/>
@@ -8106,22 +8144,22 @@
     </row>
     <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>71</v>
@@ -8130,25 +8168,25 @@
         <v>1296.58</v>
       </c>
       <c r="I28" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J28" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J28" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="K28" s="30">
-        <v>15</v>
+      <c r="K28" s="30" t="s">
+        <v>702</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M28" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="N28" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N28" s="9" t="s">
+      <c r="O28" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O28" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P28" s="9"/>
       <c r="Q28" s="13"/>
@@ -8160,22 +8198,22 @@
     </row>
     <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>71</v>
@@ -8184,25 +8222,25 @@
         <v>968.82</v>
       </c>
       <c r="I29" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J29" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="K29" s="30">
-        <v>15</v>
+      <c r="K29" s="30" t="s">
+        <v>702</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M29" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="N29" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N29" s="9" t="s">
+      <c r="O29" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P29" s="9"/>
       <c r="Q29" s="13"/>
@@ -8214,50 +8252,49 @@
     </row>
     <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D30" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>306</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>308</v>
       </c>
       <c r="G30" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H30" s="14">
-        <f>146.5*4+109</f>
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K30" s="30" t="s">
-        <v>114</v>
+        <v>715</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M30" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="N30" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N30" s="9" t="s">
+      <c r="O30" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O30" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P30" s="9"/>
       <c r="Q30" s="13"/>
@@ -8269,22 +8306,22 @@
     </row>
     <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>71</v>
@@ -8294,25 +8331,25 @@
         <v>5041.2</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M31" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="N31" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N31" s="9" t="s">
+      <c r="O31" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O31" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P31" s="9"/>
       <c r="Q31" s="13"/>
@@ -8324,13 +8361,13 @@
     </row>
     <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>61</v>
@@ -8339,34 +8376,34 @@
         <v>76</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G32" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H32" s="14">
-        <v>2000</v>
+        <v>2273.4</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K32" s="30" t="s">
-        <v>114</v>
+        <v>463</v>
       </c>
       <c r="L32" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="M32" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M32" s="9" t="s">
+      <c r="N32" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N32" s="9" t="s">
+      <c r="O32" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O32" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P32" s="9"/>
       <c r="Q32" s="13"/>
@@ -8378,49 +8415,49 @@
     </row>
     <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H33" s="14">
-        <v>2000</v>
+        <v>1620</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K33" s="30" t="s">
-        <v>114</v>
+        <v>463</v>
       </c>
       <c r="L33" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="M33" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M33" s="9" t="s">
+      <c r="N33" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N33" s="9" t="s">
+      <c r="O33" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O33" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P33" s="9"/>
       <c r="Q33" s="13"/>
@@ -8432,49 +8469,49 @@
     </row>
     <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G34" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H34" s="14">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K34" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L34" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="M34" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M34" s="9" t="s">
+      <c r="N34" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N34" s="9" t="s">
+      <c r="O34" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O34" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P34" s="9"/>
       <c r="Q34" s="13"/>
@@ -8482,53 +8519,55 @@
       <c r="S34" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="T34" s="9"/>
+      <c r="T34" s="9" t="s">
+        <v>719</v>
+      </c>
     </row>
     <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G35" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H35" s="14">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K35" s="30" t="s">
-        <v>114</v>
+        <v>708</v>
       </c>
       <c r="L35" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="M35" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M35" s="9" t="s">
+      <c r="N35" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N35" s="9" t="s">
+      <c r="O35" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P35" s="9"/>
       <c r="Q35" s="13"/>
@@ -8540,22 +8579,22 @@
     </row>
     <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>71</v>
@@ -8564,25 +8603,25 @@
         <v>104.95</v>
       </c>
       <c r="I36" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J36" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J36" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="K36" s="30">
-        <v>27</v>
+      <c r="K36" s="30" t="s">
+        <v>703</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N36" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O36" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O36" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P36" s="9"/>
       <c r="Q36" s="13"/>
@@ -8594,22 +8633,22 @@
     </row>
     <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G37" s="9" t="s">
         <v>71</v>
@@ -8618,25 +8657,25 @@
         <v>240</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="K37" s="31" t="s">
-        <v>325</v>
+        <v>255</v>
+      </c>
+      <c r="K37" s="30" t="s">
+        <v>323</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N37" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O37" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P37" s="9"/>
       <c r="Q37" s="13"/>
@@ -8648,13 +8687,13 @@
     </row>
     <row r="38" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>61</v>
@@ -8663,34 +8702,34 @@
         <v>76</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H38" s="14">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K38" s="30" t="s">
-        <v>114</v>
+        <v>463</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N38" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O38" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O38" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P38" s="9"/>
       <c r="Q38" s="13"/>
@@ -8702,49 +8741,49 @@
     </row>
     <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H39" s="14">
-        <v>2000</v>
+        <v>2268</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K39" s="30" t="s">
-        <v>114</v>
+        <v>463</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N39" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O39" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O39" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P39" s="9"/>
       <c r="Q39" s="13"/>
@@ -8756,49 +8795,49 @@
     </row>
     <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H40" s="14">
-        <v>1200</v>
+        <v>210</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K40" s="30" t="s">
-        <v>114</v>
+        <v>716</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N40" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O40" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O40" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P40" s="9"/>
       <c r="Q40" s="13"/>
@@ -8810,49 +8849,49 @@
     </row>
     <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H41" s="14">
-        <v>1200</v>
+        <v>860</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K41" s="30" t="s">
-        <v>114</v>
+        <v>708</v>
       </c>
       <c r="L41" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N41" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O41" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O41" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P41" s="9"/>
       <c r="Q41" s="13"/>
@@ -8864,13 +8903,13 @@
     </row>
     <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>61</v>
@@ -8879,34 +8918,34 @@
         <v>76</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H42" s="14">
-        <v>2000</v>
+        <v>2667.6</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K42" s="30" t="s">
-        <v>114</v>
+        <v>463</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N42" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O42" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O42" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P42" s="9"/>
       <c r="Q42" s="13"/>
@@ -8918,49 +8957,49 @@
     </row>
     <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H43" s="14">
-        <v>2000</v>
+        <v>2268</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K43" s="30" t="s">
-        <v>114</v>
+        <v>463</v>
       </c>
       <c r="L43" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N43" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O43" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P43" s="9"/>
       <c r="Q43" s="13"/>
@@ -8972,49 +9011,49 @@
     </row>
     <row r="44" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G44" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H44" s="14">
-        <v>1200</v>
+        <v>270</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K44" s="30" t="s">
-        <v>114</v>
+        <v>716</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N44" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O44" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O44" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P44" s="9"/>
       <c r="Q44" s="13"/>
@@ -9026,49 +9065,49 @@
     </row>
     <row r="45" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H45" s="14">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K45" s="30" t="s">
-        <v>114</v>
+        <v>708</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N45" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O45" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O45" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P45" s="9"/>
       <c r="Q45" s="13"/>
@@ -9080,13 +9119,13 @@
     </row>
     <row r="46" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>61</v>
@@ -9095,34 +9134,34 @@
         <v>76</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="14">
-        <v>2000</v>
+        <v>1647</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K46" s="30" t="s">
-        <v>114</v>
+        <v>463</v>
       </c>
       <c r="L46" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="N46" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O46" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O46" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P46" s="9"/>
       <c r="Q46" s="13"/>
@@ -9134,49 +9173,49 @@
     </row>
     <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G47" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="14">
-        <v>2000</v>
+        <v>1134</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K47" s="30" t="s">
-        <v>114</v>
+        <v>463</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="N47" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O47" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O47" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P47" s="9"/>
       <c r="Q47" s="13"/>
@@ -9188,49 +9227,49 @@
     </row>
     <row r="48" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G48" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="14">
-        <v>1200</v>
+        <v>180</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K48" s="30" t="s">
-        <v>114</v>
+        <v>716</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="N48" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O48" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O48" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P48" s="9"/>
       <c r="Q48" s="13"/>
@@ -9242,49 +9281,49 @@
     </row>
     <row r="49" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G49" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H49" s="14">
-        <v>1200</v>
+        <v>680</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K49" s="30" t="s">
-        <v>114</v>
+        <v>708</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="N49" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O49" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O49" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P49" s="9"/>
       <c r="Q49" s="13"/>
@@ -9296,13 +9335,13 @@
     </row>
     <row r="50" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>61</v>
@@ -9311,34 +9350,34 @@
         <v>76</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G50" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H50" s="14">
-        <v>2000</v>
+        <v>1652.4</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K50" s="30" t="s">
-        <v>114</v>
+        <v>463</v>
       </c>
       <c r="L50" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="M50" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M50" s="9" t="s">
+      <c r="N50" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N50" s="9" t="s">
+      <c r="O50" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O50" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P50" s="9"/>
       <c r="Q50" s="13"/>
@@ -9350,49 +9389,49 @@
     </row>
     <row r="51" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G51" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H51" s="14">
-        <v>2000</v>
+        <v>1166.4000000000001</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K51" s="30" t="s">
-        <v>114</v>
+        <v>463</v>
       </c>
       <c r="L51" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="M51" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M51" s="9" t="s">
+      <c r="N51" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N51" s="9" t="s">
+      <c r="O51" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O51" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P51" s="9"/>
       <c r="Q51" s="13"/>
@@ -9404,49 +9443,49 @@
     </row>
     <row r="52" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H52" s="14">
-        <v>1200</v>
+        <v>180</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K52" s="30" t="s">
-        <v>114</v>
+        <v>716</v>
       </c>
       <c r="L52" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="M52" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M52" s="9" t="s">
+      <c r="N52" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N52" s="9" t="s">
+      <c r="O52" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O52" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P52" s="9"/>
       <c r="Q52" s="13"/>
@@ -9458,49 +9497,49 @@
     </row>
     <row r="53" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H53" s="14">
-        <v>1200</v>
+        <v>710</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K53" s="30" t="s">
-        <v>114</v>
+        <v>708</v>
       </c>
       <c r="L53" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="M53" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="M53" s="9" t="s">
+      <c r="N53" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="N53" s="9" t="s">
+      <c r="O53" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O53" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P53" s="9"/>
       <c r="Q53" s="13"/>
@@ -9512,13 +9551,13 @@
     </row>
     <row r="54" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>61</v>
@@ -9527,34 +9566,34 @@
         <v>76</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H54" s="14">
-        <v>2000</v>
+        <v>2343.6</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K54" s="30" t="s">
-        <v>114</v>
+        <v>431</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N54" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O54" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O54" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P54" s="9"/>
       <c r="Q54" s="13"/>
@@ -9566,49 +9605,49 @@
     </row>
     <row r="55" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H55" s="14">
-        <v>2000</v>
+        <v>1404</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K55" s="30" t="s">
-        <v>114</v>
+        <v>431</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N55" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O55" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O55" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P55" s="9"/>
       <c r="Q55" s="13"/>
@@ -9620,49 +9659,49 @@
     </row>
     <row r="56" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H56" s="14">
-        <v>1200</v>
+        <v>240</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K56" s="30" t="s">
-        <v>114</v>
+        <v>716</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N56" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O56" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O56" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P56" s="9"/>
       <c r="Q56" s="13"/>
@@ -9674,49 +9713,50 @@
     </row>
     <row r="57" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H57" s="14">
-        <v>1200</v>
+        <f>600+810</f>
+        <v>1410</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K57" s="30" t="s">
-        <v>114</v>
+        <v>708</v>
       </c>
       <c r="L57" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N57" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O57" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O57" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P57" s="9"/>
       <c r="Q57" s="13"/>
@@ -9728,13 +9768,13 @@
     </row>
     <row r="58" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>61</v>
@@ -9743,34 +9783,34 @@
         <v>76</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H58" s="14">
-        <v>2000</v>
+        <v>2484</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>114</v>
+        <v>431</v>
       </c>
       <c r="L58" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N58" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O58" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O58" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P58" s="9"/>
       <c r="Q58" s="13"/>
@@ -9782,49 +9822,49 @@
     </row>
     <row r="59" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H59" s="14">
-        <v>2000</v>
+        <v>1728</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K59" s="30" t="s">
-        <v>114</v>
+        <v>431</v>
       </c>
       <c r="L59" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N59" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O59" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O59" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P59" s="9"/>
       <c r="Q59" s="13"/>
@@ -9836,49 +9876,49 @@
     </row>
     <row r="60" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H60" s="14">
-        <v>1200</v>
+        <v>240</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K60" s="30" t="s">
-        <v>114</v>
+        <v>716</v>
       </c>
       <c r="L60" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N60" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O60" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O60" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P60" s="9"/>
       <c r="Q60" s="13"/>
@@ -9890,49 +9930,50 @@
     </row>
     <row r="61" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>73</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H61" s="14">
-        <v>1200</v>
+        <f>780+600</f>
+        <v>1380</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>114</v>
+        <v>708</v>
       </c>
       <c r="L61" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N61" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O61" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="O61" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P61" s="9"/>
       <c r="Q61" s="13"/>
@@ -9944,22 +9985,22 @@
     </row>
     <row r="62" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="9" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D62" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="F62" s="9" t="s">
         <v>352</v>
-      </c>
-      <c r="E62" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>354</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>92</v>
@@ -9969,22 +10010,22 @@
         <v>3280</v>
       </c>
       <c r="I62" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J62" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J62" s="9" t="s">
+      <c r="K62" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="L62" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K62" s="9">
-        <v>15</v>
-      </c>
-      <c r="L62" s="9" t="s">
-        <v>236</v>
-      </c>
       <c r="M62" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="N62" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O62" s="9" t="s">
         <v>204</v>
@@ -9999,22 +10040,22 @@
     </row>
     <row r="63" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D63" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="F63" s="9" t="s">
         <v>357</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>359</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>92</v>
@@ -10023,22 +10064,22 @@
         <v>1862</v>
       </c>
       <c r="I63" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J63" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J63" s="9" t="s">
+      <c r="K63" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="L63" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K63" s="9">
-        <v>15</v>
-      </c>
-      <c r="L63" s="9" t="s">
-        <v>236</v>
-      </c>
       <c r="M63" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>204</v>
@@ -10053,22 +10094,22 @@
     </row>
     <row r="64" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="9" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>92</v>
@@ -10077,22 +10118,22 @@
         <v>2136</v>
       </c>
       <c r="I64" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J64" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J64" s="9" t="s">
+      <c r="K64" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="L64" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K64" s="9">
-        <v>15</v>
-      </c>
-      <c r="L64" s="9" t="s">
-        <v>236</v>
-      </c>
       <c r="M64" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="N64" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O64" s="9" t="s">
         <v>204</v>
@@ -10107,22 +10148,22 @@
     </row>
     <row r="65" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>366</v>
+        <v>717</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>92</v>
@@ -10132,22 +10173,22 @@
         <v>8946</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="K65" s="9">
-        <v>15</v>
+        <v>262</v>
+      </c>
+      <c r="K65" s="30" t="s">
+        <v>716</v>
       </c>
       <c r="L65" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>204</v>
@@ -10162,22 +10203,22 @@
     </row>
     <row r="66" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C66" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="D66" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="D66" s="9" t="s">
-        <v>268</v>
-      </c>
       <c r="E66" s="9" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G66" s="9" t="s">
         <v>92</v>
@@ -10186,22 +10227,22 @@
         <v>25000</v>
       </c>
       <c r="I66" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J66" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J66" s="9" t="s">
+      <c r="K66" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="L66" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K66" s="30">
-        <v>15</v>
-      </c>
-      <c r="L66" s="9" t="s">
-        <v>236</v>
-      </c>
       <c r="M66" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="N66" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O66" s="9" t="s">
         <v>204</v>
@@ -10216,22 +10257,22 @@
     </row>
     <row r="67" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C67" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="D67" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>174</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G67" s="9" t="s">
         <v>92</v>
@@ -10240,22 +10281,22 @@
         <v>41000</v>
       </c>
       <c r="I67" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J67" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J67" s="9" t="s">
+      <c r="K67" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="L67" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K67" s="30">
-        <v>15</v>
-      </c>
-      <c r="L67" s="9" t="s">
-        <v>236</v>
-      </c>
       <c r="M67" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>204</v>
@@ -10270,22 +10311,22 @@
     </row>
     <row r="68" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>118</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>373</v>
+        <v>714</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="G68" s="9" t="s">
         <v>121</v>
@@ -10294,22 +10335,22 @@
         <v>2377</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K68" s="30" t="s">
-        <v>114</v>
+        <v>710</v>
       </c>
       <c r="L68" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M68" s="9" t="s">
-        <v>375</v>
+        <v>712</v>
       </c>
       <c r="N68" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O68" s="9" t="s">
         <v>204</v>
@@ -10324,22 +10365,22 @@
     </row>
     <row r="69" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>118</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E69" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="F69" s="9" t="s">
         <v>373</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>378</v>
       </c>
       <c r="G69" s="9" t="s">
         <v>121</v>
@@ -10348,22 +10389,22 @@
         <v>220</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K69" s="30" t="s">
-        <v>114</v>
+        <v>711</v>
       </c>
       <c r="L69" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M69" s="9" t="s">
-        <v>375</v>
+        <v>713</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>204</v>
@@ -10901,68 +10942,68 @@
   <sheetData>
     <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>215</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="K4" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="P4" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>390</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>392</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>395</v>
       </c>
       <c r="S4" s="8" t="s">
         <v>62</v>
@@ -10973,13 +11014,13 @@
     </row>
     <row r="5" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>112</v>
@@ -11009,21 +11050,21 @@
         <v>77</v>
       </c>
       <c r="T5" s="19" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>73</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>68</v>
@@ -11050,18 +11091,18 @@
         <v>77</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>112</v>
@@ -11091,18 +11132,18 @@
         <v>77</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>88</v>
@@ -11132,12 +11173,12 @@
         <v>77</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>76</v>
@@ -11146,7 +11187,7 @@
         <v>61</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>68</v>
@@ -11173,21 +11214,21 @@
         <v>77</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>68</v>
@@ -11214,18 +11255,18 @@
         <v>77</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>66</v>
@@ -11255,21 +11296,21 @@
         <v>77</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>68</v>
@@ -11296,21 +11337,21 @@
         <v>77</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>68</v>
@@ -11337,21 +11378,21 @@
         <v>77</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>68</v>
@@ -11378,18 +11419,18 @@
         <v>77</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>112</v>
@@ -11419,21 +11460,21 @@
         <v>77</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>68</v>
@@ -11460,18 +11501,18 @@
         <v>77</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>88</v>
@@ -11501,18 +11542,18 @@
         <v>77</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>88</v>
@@ -11542,18 +11583,18 @@
         <v>77</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>112</v>
@@ -11583,18 +11624,18 @@
         <v>77</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>84</v>
@@ -11624,18 +11665,18 @@
         <v>77</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>88</v>
@@ -11665,7 +11706,7 @@
         <v>77</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -12229,12 +12270,12 @@
   <sheetData>
     <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12248,46 +12289,46 @@
         <v>52</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>220</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>405</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>410</v>
       </c>
       <c r="R4" s="8" t="s">
         <v>63</v>
@@ -12295,7 +12336,7 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>66</v>
@@ -12304,26 +12345,26 @@
         <v>68</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="I5" s="13">
         <v>46249</v>
       </c>
       <c r="J5" s="15">
         <f t="shared" ref="J5:J36" ca="1" si="0">IFERROR(IF(I5="","",I5-TODAY()),"")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K5" s="15" t="str">
         <f t="shared" ref="K5:K10" ca="1" si="1">IFERROR(IF(I5="","",IF(I5-TODAY()&lt;0,"OVERDUE",IF(I5-TODAY()&lt;=14,"DUE NOW",IF(I5-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -12341,7 +12382,7 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>66</v>
@@ -12350,26 +12391,26 @@
         <v>68</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="I6" s="13">
         <v>46249</v>
       </c>
       <c r="J6" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K6" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -12387,7 +12428,7 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>66</v>
@@ -12396,26 +12437,26 @@
         <v>68</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="I7" s="13">
         <v>46249</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K7" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -12433,7 +12474,7 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>66</v>
@@ -12442,16 +12483,16 @@
         <v>68</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>106</v>
@@ -12461,7 +12502,7 @@
       </c>
       <c r="J8" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K8" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -12479,7 +12520,7 @@
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>66</v>
@@ -12488,16 +12529,16 @@
         <v>68</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>106</v>
@@ -12507,7 +12548,7 @@
       </c>
       <c r="J9" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K9" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -12525,7 +12566,7 @@
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>66</v>
@@ -12534,33 +12575,33 @@
         <v>68</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G10" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>422</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>427</v>
       </c>
       <c r="I10" s="13">
         <v>46366</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K10" s="15" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
       <c r="L10" s="9" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="9"/>
@@ -12571,7 +12612,7 @@
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>66</v>
@@ -12580,16 +12621,16 @@
         <v>68</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>106</v>
@@ -12599,11 +12640,11 @@
       </c>
       <c r="J11" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K11" s="15"/>
       <c r="L11" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="9"/>
@@ -12614,7 +12655,7 @@
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>66</v>
@@ -12623,30 +12664,30 @@
         <v>68</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="I12" s="13">
         <v>46477</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K12" s="15"/>
       <c r="L12" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M12" s="13"/>
       <c r="N12" s="9"/>
@@ -12657,7 +12698,7 @@
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>66</v>
@@ -12666,30 +12707,30 @@
         <v>68</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="I13" s="13">
         <v>46477</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K13" s="15"/>
       <c r="L13" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M13" s="13"/>
       <c r="N13" s="9"/>
@@ -12700,7 +12741,7 @@
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>84</v>
@@ -12709,16 +12750,16 @@
         <v>68</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>70</v>
@@ -12728,7 +12769,7 @@
       </c>
       <c r="J14" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K14" s="15"/>
       <c r="L14" s="9" t="s">
@@ -12743,7 +12784,7 @@
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>84</v>
@@ -12752,16 +12793,16 @@
         <v>68</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>106</v>
@@ -12771,11 +12812,11 @@
       </c>
       <c r="J15" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K15" s="15"/>
       <c r="L15" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="9"/>
@@ -12786,7 +12827,7 @@
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>84</v>
@@ -12795,30 +12836,30 @@
         <v>68</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="I16" s="13">
         <v>46477</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K16" s="15"/>
       <c r="L16" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="9"/>
@@ -12829,7 +12870,7 @@
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>84</v>
@@ -12838,16 +12879,16 @@
         <v>68</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>106</v>
@@ -12857,7 +12898,7 @@
       </c>
       <c r="J17" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K17" s="15" t="str">
         <f ca="1">IFERROR(IF(I17="","",IF(I17-TODAY()&lt;0,"OVERDUE",IF(I17-TODAY()&lt;=14,"DUE NOW",IF(I17-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -12875,7 +12916,7 @@
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>84</v>
@@ -12884,16 +12925,16 @@
         <v>68</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>106</v>
@@ -12903,7 +12944,7 @@
       </c>
       <c r="J18" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K18" s="15" t="str">
         <f ca="1">IFERROR(IF(I18="","",IF(I18-TODAY()&lt;0,"OVERDUE",IF(I18-TODAY()&lt;=14,"DUE NOW",IF(I18-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -12921,7 +12962,7 @@
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>95</v>
@@ -12930,16 +12971,16 @@
         <v>68</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>106</v>
@@ -12949,11 +12990,11 @@
       </c>
       <c r="J19" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K19" s="15"/>
       <c r="L19" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M19" s="13"/>
       <c r="N19" s="9"/>
@@ -12964,7 +13005,7 @@
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>95</v>
@@ -12973,30 +13014,30 @@
         <v>68</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="I20" s="13">
         <v>46477</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K20" s="15"/>
       <c r="L20" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M20" s="13"/>
       <c r="N20" s="9"/>
@@ -13007,7 +13048,7 @@
     </row>
     <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>95</v>
@@ -13016,16 +13057,16 @@
         <v>68</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>106</v>
@@ -13035,7 +13076,7 @@
       </c>
       <c r="J21" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K21" s="15" t="str">
         <f ca="1">IFERROR(IF(I21="","",IF(I21-TODAY()&lt;0,"OVERDUE",IF(I21-TODAY()&lt;=14,"DUE NOW",IF(I21-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13053,7 +13094,7 @@
     </row>
     <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>95</v>
@@ -13062,16 +13103,16 @@
         <v>68</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>106</v>
@@ -13081,7 +13122,7 @@
       </c>
       <c r="J22" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K22" s="15" t="str">
         <f ca="1">IFERROR(IF(I22="","",IF(I22-TODAY()&lt;0,"OVERDUE",IF(I22-TODAY()&lt;=14,"DUE NOW",IF(I22-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13099,7 +13140,7 @@
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>99</v>
@@ -13108,16 +13149,16 @@
         <v>68</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>106</v>
@@ -13127,11 +13168,11 @@
       </c>
       <c r="J23" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K23" s="15"/>
       <c r="L23" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M23" s="13"/>
       <c r="N23" s="9"/>
@@ -13142,7 +13183,7 @@
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>99</v>
@@ -13151,30 +13192,30 @@
         <v>68</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="I24" s="13">
         <v>46477</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K24" s="15"/>
       <c r="L24" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M24" s="13"/>
       <c r="N24" s="9"/>
@@ -13185,7 +13226,7 @@
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>99</v>
@@ -13194,16 +13235,16 @@
         <v>68</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>106</v>
@@ -13213,7 +13254,7 @@
       </c>
       <c r="J25" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K25" s="15" t="str">
         <f ca="1">IFERROR(IF(I25="","",IF(I25-TODAY()&lt;0,"OVERDUE",IF(I25-TODAY()&lt;=14,"DUE NOW",IF(I25-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13231,7 +13272,7 @@
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>99</v>
@@ -13240,16 +13281,16 @@
         <v>68</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>106</v>
@@ -13259,7 +13300,7 @@
       </c>
       <c r="J26" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K26" s="15" t="str">
         <f ca="1">IFERROR(IF(I26="","",IF(I26-TODAY()&lt;0,"OVERDUE",IF(I26-TODAY()&lt;=14,"DUE NOW",IF(I26-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13277,7 +13318,7 @@
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>80</v>
@@ -13286,16 +13327,16 @@
         <v>68</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>106</v>
@@ -13305,11 +13346,11 @@
       </c>
       <c r="J27" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K27" s="15"/>
       <c r="L27" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="9"/>
@@ -13320,7 +13361,7 @@
     </row>
     <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>80</v>
@@ -13329,30 +13370,30 @@
         <v>68</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="I28" s="13">
         <v>46477</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K28" s="15"/>
       <c r="L28" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="9"/>
@@ -13363,7 +13404,7 @@
     </row>
     <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>80</v>
@@ -13372,16 +13413,16 @@
         <v>68</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>106</v>
@@ -13391,7 +13432,7 @@
       </c>
       <c r="J29" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K29" s="15" t="str">
         <f ca="1">IFERROR(IF(I29="","",IF(I29-TODAY()&lt;0,"OVERDUE",IF(I29-TODAY()&lt;=14,"DUE NOW",IF(I29-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13409,7 +13450,7 @@
     </row>
     <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>80</v>
@@ -13418,16 +13459,16 @@
         <v>68</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>106</v>
@@ -13437,7 +13478,7 @@
       </c>
       <c r="J30" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K30" s="15" t="str">
         <f ca="1">IFERROR(IF(I30="","",IF(I30-TODAY()&lt;0,"OVERDUE",IF(I30-TODAY()&lt;=14,"DUE NOW",IF(I30-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13455,7 +13496,7 @@
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>103</v>
@@ -13464,30 +13505,30 @@
         <v>68</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="I31" s="13">
         <v>46446</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K31" s="15"/>
       <c r="L31" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="9"/>
@@ -13495,12 +13536,12 @@
       <c r="P31" s="13"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="9" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>103</v>
@@ -13509,30 +13550,30 @@
         <v>68</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="I32" s="13">
         <v>46477</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K32" s="15"/>
       <c r="L32" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="9"/>
@@ -13543,7 +13584,7 @@
     </row>
     <row r="33" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>103</v>
@@ -13552,16 +13593,16 @@
         <v>68</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>106</v>
@@ -13571,7 +13612,7 @@
       </c>
       <c r="J33" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K33" s="15" t="str">
         <f ca="1">IFERROR(IF(I33="","",IF(I33-TODAY()&lt;0,"OVERDUE",IF(I33-TODAY()&lt;=14,"DUE NOW",IF(I33-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13589,7 +13630,7 @@
     </row>
     <row r="34" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>103</v>
@@ -13598,16 +13639,16 @@
         <v>68</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>106</v>
@@ -13617,7 +13658,7 @@
       </c>
       <c r="J34" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K34" s="15" t="str">
         <f ca="1">IFERROR(IF(I34="","",IF(I34-TODAY()&lt;0,"OVERDUE",IF(I34-TODAY()&lt;=14,"DUE NOW",IF(I34-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13635,7 +13676,7 @@
     </row>
     <row r="35" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>108</v>
@@ -13644,30 +13685,30 @@
         <v>68</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="I35" s="13">
         <v>46446</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K35" s="15"/>
       <c r="L35" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="9"/>
@@ -13675,12 +13716,12 @@
       <c r="P35" s="13"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="9" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>108</v>
@@ -13689,30 +13730,30 @@
         <v>68</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="I36" s="13">
         <v>46477</v>
       </c>
       <c r="J36" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K36" s="15"/>
       <c r="L36" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="9"/>
@@ -13723,7 +13764,7 @@
     </row>
     <row r="37" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>108</v>
@@ -13732,16 +13773,16 @@
         <v>68</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>106</v>
@@ -13751,7 +13792,7 @@
       </c>
       <c r="J37" s="15">
         <f t="shared" ref="J37:J65" ca="1" si="2">IFERROR(IF(I37="","",I37-TODAY()),"")</f>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K37" s="15" t="str">
         <f t="shared" ref="K37:K43" ca="1" si="3">IFERROR(IF(I37="","",IF(I37-TODAY()&lt;0,"OVERDUE",IF(I37-TODAY()&lt;=14,"DUE NOW",IF(I37-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -13769,7 +13810,7 @@
     </row>
     <row r="38" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>108</v>
@@ -13778,16 +13819,16 @@
         <v>68</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>106</v>
@@ -13797,7 +13838,7 @@
       </c>
       <c r="J38" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K38" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -13815,7 +13856,7 @@
     </row>
     <row r="39" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>88</v>
@@ -13824,26 +13865,26 @@
         <v>90</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="I39" s="13">
         <v>46265</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K39" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -13861,7 +13902,7 @@
     </row>
     <row r="40" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>88</v>
@@ -13870,26 +13911,26 @@
         <v>90</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="I40" s="13">
         <v>46536</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K40" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -13907,7 +13948,7 @@
     </row>
     <row r="41" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>88</v>
@@ -13916,26 +13957,26 @@
         <v>90</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="I41" s="13">
         <v>46356</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K41" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -13953,7 +13994,7 @@
     </row>
     <row r="42" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>88</v>
@@ -13962,16 +14003,16 @@
         <v>90</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>106</v>
@@ -13981,7 +14022,7 @@
       </c>
       <c r="J42" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K42" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -13999,7 +14040,7 @@
     </row>
     <row r="43" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>88</v>
@@ -14008,26 +14049,26 @@
         <v>68</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="H43" s="17" t="s">
         <v>422</v>
-      </c>
-      <c r="H43" s="17" t="s">
-        <v>427</v>
       </c>
       <c r="I43" s="13">
         <v>46366</v>
       </c>
       <c r="J43" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K43" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -14045,7 +14086,7 @@
     </row>
     <row r="44" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>88</v>
@@ -14054,16 +14095,16 @@
         <v>68</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>106</v>
@@ -14073,7 +14114,7 @@
       </c>
       <c r="J44" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K44" s="15"/>
       <c r="L44" s="9" t="s">
@@ -14088,7 +14129,7 @@
     </row>
     <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>88</v>
@@ -14097,26 +14138,26 @@
         <v>68</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="I45" s="13">
         <v>46477</v>
       </c>
       <c r="J45" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K45" s="15"/>
       <c r="L45" s="9" t="s">
@@ -14131,7 +14172,7 @@
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>88</v>
@@ -14140,30 +14181,30 @@
         <v>68</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="I46" s="13">
         <v>46477</v>
       </c>
       <c r="J46" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K46" s="15"/>
       <c r="L46" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M46" s="13"/>
       <c r="N46" s="9"/>
@@ -14174,7 +14215,7 @@
     </row>
     <row r="47" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>118</v>
@@ -14183,26 +14224,26 @@
         <v>120</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>120</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I47" s="13">
         <v>46295</v>
       </c>
       <c r="J47" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K47" s="15" t="str">
         <f t="shared" ref="K47:K65" ca="1" si="4">IFERROR(IF(I47="","",IF(I47-TODAY()&lt;0,"OVERDUE",IF(I47-TODAY()&lt;=14,"DUE NOW",IF(I47-TODAY()&lt;=30,"Prepare","")))),"")</f>
@@ -14220,7 +14261,7 @@
     </row>
     <row r="48" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>118</v>
@@ -14229,26 +14270,26 @@
         <v>120</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>120</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="I48" s="13">
         <v>46265</v>
       </c>
       <c r="J48" s="15">
         <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K48" s="15" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14724,372 +14765,397 @@
   <sheetData>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="33" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C5" s="33"/>
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="22" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="22" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="22" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="22" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="22" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="22" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="8" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="23" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="23" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="23" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="23" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="23" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="23" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="23" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="23" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="31" t="s">
+        <v>518</v>
+      </c>
+      <c r="C28" s="31"/>
+    </row>
+    <row r="29" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="31" t="s">
+        <v>519</v>
+      </c>
+      <c r="C29" s="31"/>
+    </row>
+    <row r="30" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="31" t="s">
+        <v>520</v>
+      </c>
+      <c r="C30" s="31"/>
+    </row>
+    <row r="31" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="31" t="s">
+        <v>521</v>
+      </c>
+      <c r="C31" s="31"/>
+    </row>
+    <row r="32" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="31" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="28" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="32" t="s">
+      <c r="C32" s="31"/>
+    </row>
+    <row r="33" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="31" t="s">
         <v>523</v>
       </c>
-      <c r="C28" s="32"/>
-    </row>
-    <row r="29" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="32" t="s">
+      <c r="C33" s="31"/>
+    </row>
+    <row r="34" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="31" t="s">
         <v>524</v>
       </c>
-      <c r="C29" s="32"/>
-    </row>
-    <row r="30" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="32" t="s">
-        <v>525</v>
-      </c>
-      <c r="C30" s="32"/>
-    </row>
-    <row r="31" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="32" t="s">
-        <v>526</v>
-      </c>
-      <c r="C31" s="32"/>
-    </row>
-    <row r="32" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="32" t="s">
-        <v>527</v>
-      </c>
-      <c r="C32" s="32"/>
-    </row>
-    <row r="33" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="32" t="s">
-        <v>528</v>
-      </c>
-      <c r="C33" s="32"/>
-    </row>
-    <row r="34" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="32" t="s">
-        <v>529</v>
-      </c>
-      <c r="C34" s="32"/>
+      <c r="C34" s="31"/>
     </row>
     <row r="36" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="4" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="32" t="s">
+        <v>526</v>
+      </c>
+      <c r="C37" s="32"/>
+    </row>
+    <row r="38" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="32" t="s">
+        <v>527</v>
+      </c>
+      <c r="C38" s="32"/>
+    </row>
+    <row r="39" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="32" t="s">
+        <v>528</v>
+      </c>
+      <c r="C39" s="32"/>
+    </row>
+    <row r="40" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="32" t="s">
+        <v>529</v>
+      </c>
+      <c r="C40" s="32"/>
+    </row>
+    <row r="41" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="32" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="37" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="34" t="s">
+      <c r="C41" s="32"/>
+    </row>
+    <row r="42" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="32" t="s">
         <v>531</v>
       </c>
-      <c r="C37" s="34"/>
-    </row>
-    <row r="38" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="34" t="s">
+      <c r="C42" s="32"/>
+    </row>
+    <row r="43" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="32" t="s">
         <v>532</v>
       </c>
-      <c r="C38" s="34"/>
-    </row>
-    <row r="39" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="34" t="s">
+      <c r="C43" s="32"/>
+    </row>
+    <row r="44" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="32" t="s">
         <v>533</v>
       </c>
-      <c r="C39" s="34"/>
-    </row>
-    <row r="40" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="34" t="s">
+      <c r="C44" s="32"/>
+    </row>
+    <row r="45" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="32" t="s">
         <v>534</v>
       </c>
-      <c r="C40" s="34"/>
-    </row>
-    <row r="41" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="34" t="s">
+      <c r="C45" s="32"/>
+    </row>
+    <row r="46" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="32" t="s">
         <v>535</v>
       </c>
-      <c r="C41" s="34"/>
-    </row>
-    <row r="42" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="34" t="s">
+      <c r="C46" s="32"/>
+    </row>
+    <row r="47" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="32" t="s">
         <v>536</v>
       </c>
-      <c r="C42" s="34"/>
-    </row>
-    <row r="43" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="34" t="s">
+      <c r="C47" s="32"/>
+    </row>
+    <row r="48" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="32" t="s">
         <v>537</v>
       </c>
-      <c r="C43" s="34"/>
-    </row>
-    <row r="44" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="34" t="s">
+      <c r="C48" s="32"/>
+    </row>
+    <row r="49" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="32" t="s">
         <v>538</v>
       </c>
-      <c r="C44" s="34"/>
-    </row>
-    <row r="45" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="34" t="s">
+      <c r="C49" s="32"/>
+    </row>
+    <row r="50" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="32" t="s">
         <v>539</v>
       </c>
-      <c r="C45" s="34"/>
-    </row>
-    <row r="46" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="34" t="s">
+      <c r="C50" s="32"/>
+    </row>
+    <row r="51" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="32" t="s">
         <v>540</v>
       </c>
-      <c r="C46" s="34"/>
-    </row>
-    <row r="47" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="34" t="s">
+      <c r="C51" s="32"/>
+    </row>
+    <row r="52" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="32" t="s">
         <v>541</v>
       </c>
-      <c r="C47" s="34"/>
-    </row>
-    <row r="48" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="34" t="s">
+      <c r="C52" s="32"/>
+    </row>
+    <row r="53" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="32" t="s">
         <v>542</v>
       </c>
-      <c r="C48" s="34"/>
-    </row>
-    <row r="49" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="34" t="s">
+      <c r="C53" s="32"/>
+    </row>
+    <row r="54" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="32" t="s">
         <v>543</v>
       </c>
-      <c r="C49" s="34"/>
-    </row>
-    <row r="50" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="34" t="s">
+      <c r="C54" s="32"/>
+    </row>
+    <row r="55" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="32" t="s">
         <v>544</v>
       </c>
-      <c r="C50" s="34"/>
-    </row>
-    <row r="51" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="34" t="s">
+      <c r="C55" s="32"/>
+    </row>
+    <row r="56" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="32" t="s">
         <v>545</v>
       </c>
-      <c r="C51" s="34"/>
-    </row>
-    <row r="52" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="34" t="s">
-        <v>546</v>
-      </c>
-      <c r="C52" s="34"/>
-    </row>
-    <row r="53" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="34" t="s">
-        <v>547</v>
-      </c>
-      <c r="C53" s="34"/>
-    </row>
-    <row r="54" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="34" t="s">
-        <v>548</v>
-      </c>
-      <c r="C54" s="34"/>
-    </row>
-    <row r="55" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="34" t="s">
-        <v>549</v>
-      </c>
-      <c r="C55" s="34"/>
-    </row>
-    <row r="56" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="34" t="s">
-        <v>550</v>
-      </c>
-      <c r="C56" s="34"/>
+      <c r="C56" s="32"/>
     </row>
     <row r="58" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="4" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B59" s="31" t="s">
+        <v>547</v>
+      </c>
+      <c r="C59" s="31"/>
+    </row>
+    <row r="60" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="31" t="s">
+        <v>548</v>
+      </c>
+      <c r="C60" s="31"/>
+    </row>
+    <row r="61" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="31" t="s">
+        <v>549</v>
+      </c>
+      <c r="C61" s="31"/>
+    </row>
+    <row r="62" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="31" t="s">
+        <v>550</v>
+      </c>
+      <c r="C62" s="31"/>
+    </row>
+    <row r="63" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="31"/>
+      <c r="C63" s="31"/>
+    </row>
+    <row r="64" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B64" s="31" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="59" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="32" t="s">
-        <v>552</v>
-      </c>
-      <c r="C59" s="32"/>
-    </row>
-    <row r="60" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="32" t="s">
-        <v>553</v>
-      </c>
-      <c r="C60" s="32"/>
-    </row>
-    <row r="61" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="32" t="s">
-        <v>554</v>
-      </c>
-      <c r="C61" s="32"/>
-    </row>
-    <row r="62" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="32" t="s">
-        <v>555</v>
-      </c>
-      <c r="C62" s="32"/>
-    </row>
-    <row r="63" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="32"/>
-      <c r="C63" s="32"/>
-    </row>
-    <row r="64" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="32" t="s">
-        <v>556</v>
-      </c>
-      <c r="C64" s="32"/>
+      <c r="C64" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
     <mergeCell ref="B61:C61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="B63:C63"/>
@@ -15099,31 +15165,6 @@
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -15145,245 +15186,245 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>130</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>214</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="E8" s="21" t="s">
         <v>220</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>219</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="21" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="21" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="21" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="21" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="21" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="21" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="21" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="21" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="C19" s="21" t="s">
         <v>216</v>
@@ -15391,10 +15432,10 @@
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="21" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="C20" s="21" t="s">
         <v>216</v>
@@ -15402,32 +15443,32 @@
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="21" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="21" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="21" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C23" s="21" t="s">
         <v>216</v>
@@ -15435,10 +15476,10 @@
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="21" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C24" s="21" t="s">
         <v>216</v>
@@ -15446,76 +15487,76 @@
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="21" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="21" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="21" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="21" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="21" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="21" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>61</v>
@@ -15523,21 +15564,21 @@
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="21" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="21" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="C33" s="21" t="s">
         <v>216</v>
@@ -15545,35 +15586,35 @@
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="21" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="21" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="21" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>
